--- a/Recruiting_Workbook.xlsx
+++ b/Recruiting_Workbook.xlsx
@@ -9143,7 +9143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="C10" s="125" t="inlineStr">
         <is>
-          <t>John Weber</t>
+          <t>Peter Yorck</t>
         </is>
       </c>
       <c r="D10" s="125" t="inlineStr">
         <is>
-          <t>Investment Sales (Multifamily)</t>
+          <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
       <c r="E10" s="125" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="F10" s="125" t="inlineStr">
         <is>
-          <t>https://www.costar.com/article/1145252982/jll-hires-pair-from-colliers-to-oversee-multifamily-sales-in-the-southeast</t>
+          <t>https://www.jll.com/en-us/people/bio-broker/peter.yorck</t>
         </is>
       </c>
     </row>
@@ -9467,12 +9467,12 @@
       </c>
       <c r="C11" s="125" t="inlineStr">
         <is>
-          <t>William Shippen</t>
+          <t>Dennis Mitchell</t>
         </is>
       </c>
       <c r="D11" s="125" t="inlineStr">
         <is>
-          <t>Investment Sales (Multifamily)</t>
+          <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
       <c r="E11" s="125" t="inlineStr">
@@ -9482,27 +9482,27 @@
       </c>
       <c r="F11" s="125" t="inlineStr">
         <is>
-          <t>https://www.costar.com/article/1145252982/jll-hires-pair-from-colliers-to-oversee-multifamily-sales-in-the-southeast</t>
+          <t>https://www.jll.com/en-us/people/bio-broker/dennis.mitchell</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="125" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="B12" s="125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" s="125" t="inlineStr">
         <is>
-          <t>Marc Irvin</t>
+          <t>Michael Fox</t>
         </is>
       </c>
       <c r="D12" s="125" t="inlineStr">
         <is>
-          <t>Managing Director Investments</t>
+          <t>Managing Director, Capital Markets</t>
         </is>
       </c>
       <c r="E12" s="125" t="inlineStr">
@@ -9512,27 +9512,27 @@
       </c>
       <c r="F12" s="125" t="inlineStr">
         <is>
-          <t>https://www.marcusmillichap.com/about-us/offices/atlanta-georgia</t>
+          <t>https://www.jll.com/en-us/people/bio-broker/michael.fox</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="125" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="B13" s="125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" s="125" t="inlineStr">
         <is>
-          <t>Harold Shepard</t>
+          <t>John Weber</t>
         </is>
       </c>
       <c r="D13" s="125" t="inlineStr">
         <is>
-          <t>Investment Broker</t>
+          <t>Investment Sales (Multifamily)</t>
         </is>
       </c>
       <c r="E13" s="125" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="F13" s="125" t="inlineStr">
         <is>
-          <t>https://www.marcusmillichap.com/advisors/harold-shepard</t>
+          <t>https://www.costar.com/article/1145252982/jll-hires-pair-from-colliers-to-oversee-multifamily-sales-in-the-southeast</t>
         </is>
       </c>
     </row>
@@ -9553,16 +9553,16 @@
         </is>
       </c>
       <c r="B14" s="125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C14" s="125" t="inlineStr">
         <is>
-          <t>Joe Mitchell</t>
+          <t>Marc Irvin</t>
         </is>
       </c>
       <c r="D14" s="125" t="inlineStr">
         <is>
-          <t>Investment Sales</t>
+          <t>Managing Director Investments</t>
         </is>
       </c>
       <c r="E14" s="125" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="F14" s="125" t="inlineStr">
         <is>
-          <t>https://www.marcusmillichap.com/news-events/press/2024/01/marcus-millichap-expands-multi-housing-division-with-atlanta-based-multifamily-team</t>
+          <t>https://www.marcusmillichap.com/about-us/offices/atlanta-georgia</t>
         </is>
       </c>
     </row>
@@ -9583,16 +9583,16 @@
         </is>
       </c>
       <c r="B15" s="125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" s="125" t="inlineStr">
         <is>
-          <t>Marco Welch</t>
+          <t>Harold Shepard</t>
         </is>
       </c>
       <c r="D15" s="125" t="inlineStr">
         <is>
-          <t>Investment Sales</t>
+          <t>Investment Broker</t>
         </is>
       </c>
       <c r="E15" s="125" t="inlineStr">
@@ -9602,27 +9602,27 @@
       </c>
       <c r="F15" s="125" t="inlineStr">
         <is>
-          <t>https://www.marcusmillichap.com/news-events/press/2024/01/marcus-millichap-expands-multi-housing-division-with-atlanta-based-multifamily-team</t>
+          <t>https://www.marcusmillichap.com/advisors/harold-shepard</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="125" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="B16" s="125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16" s="125" t="inlineStr">
         <is>
-          <t>David Gutting</t>
+          <t>Joe Mitchell</t>
         </is>
       </c>
       <c r="D16" s="125" t="inlineStr">
         <is>
-          <t>Vice Chairman</t>
+          <t>Investment Sales</t>
         </is>
       </c>
       <c r="E16" s="125" t="inlineStr">
@@ -9632,27 +9632,27 @@
       </c>
       <c r="F16" s="125" t="inlineStr">
         <is>
-          <t>https://www.nmrk.com/insights/press-releases/newmark-continues-the-expansion-of-southeast-hiring-multifamily-capital-markets-team</t>
+          <t>https://www.marcusmillichap.com/news-events/press/2024/01/marcus-millichap-expands-multi-housing-division-with-atlanta-based-multifamily-team</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="125" t="inlineStr">
         <is>
-          <t>Newmark</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="B17" s="125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" s="125" t="inlineStr">
         <is>
-          <t>Derrick Bloom</t>
+          <t>Marco Welch</t>
         </is>
       </c>
       <c r="D17" s="125" t="inlineStr">
         <is>
-          <t>Vice Chairman, Multifamily Capital Markets</t>
+          <t>Investment Sales</t>
         </is>
       </c>
       <c r="E17" s="125" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="F17" s="125" t="inlineStr">
         <is>
-          <t>https://www.nmrk.com/offices/atlanta/people</t>
+          <t>https://www.marcusmillichap.com/news-events/press/2024/01/marcus-millichap-expands-multi-housing-division-with-atlanta-based-multifamily-team</t>
         </is>
       </c>
     </row>
@@ -9673,16 +9673,16 @@
         </is>
       </c>
       <c r="B18" s="125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="125" t="inlineStr">
         <is>
-          <t>Brooks Colquitt</t>
+          <t>David Gutting</t>
         </is>
       </c>
       <c r="D18" s="125" t="inlineStr">
         <is>
-          <t>Senior Managing Director</t>
+          <t>Vice Chairman</t>
         </is>
       </c>
       <c r="E18" s="125" t="inlineStr">
@@ -9703,16 +9703,16 @@
         </is>
       </c>
       <c r="B19" s="125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C19" s="125" t="inlineStr">
         <is>
-          <t>Hunter Amos</t>
+          <t>Derrick Bloom</t>
         </is>
       </c>
       <c r="D19" s="125" t="inlineStr">
         <is>
-          <t>Senior Managing Director, Multifamily Capital Markets</t>
+          <t>Vice Chairman, Multifamily Capital Markets</t>
         </is>
       </c>
       <c r="E19" s="125" t="inlineStr">
@@ -9729,28 +9729,88 @@
     <row r="20">
       <c r="A20" s="125" t="inlineStr">
         <is>
+          <t>Newmark</t>
+        </is>
+      </c>
+      <c r="B20" s="125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="125" t="inlineStr">
+        <is>
+          <t>Brooks Colquitt</t>
+        </is>
+      </c>
+      <c r="D20" s="125" t="inlineStr">
+        <is>
+          <t>Senior Managing Director</t>
+        </is>
+      </c>
+      <c r="E20" s="125" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F20" s="125" t="inlineStr">
+        <is>
+          <t>https://www.nmrk.com/insights/press-releases/newmark-continues-the-expansion-of-southeast-hiring-multifamily-capital-markets-team</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="125" t="inlineStr">
+        <is>
+          <t>Newmark</t>
+        </is>
+      </c>
+      <c r="B21" s="125" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="125" t="inlineStr">
+        <is>
+          <t>Hunter Amos</t>
+        </is>
+      </c>
+      <c r="D21" s="125" t="inlineStr">
+        <is>
+          <t>Senior Managing Director, Multifamily Capital Markets</t>
+        </is>
+      </c>
+      <c r="E21" s="125" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F21" s="125" t="inlineStr">
+        <is>
+          <t>https://www.nmrk.com/offices/atlanta/people</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="125" t="inlineStr">
+        <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="125" t="n">
+      <c r="B22" s="125" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="125" t="inlineStr">
+      <c r="C22" s="125" t="inlineStr">
         <is>
           <t>John Carr</t>
         </is>
       </c>
-      <c r="D20" s="125" t="inlineStr">
+      <c r="D22" s="125" t="inlineStr">
         <is>
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E20" s="125" t="inlineStr">
+      <c r="E22" s="125" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
       </c>
-      <c r="F20" s="125" t="inlineStr">
+      <c r="F22" s="125" t="inlineStr">
         <is>
           <t>https://www.walkerdunlop.com/news/investment-sales-southeast</t>
         </is>

--- a/Recruiting_Workbook.xlsx
+++ b/Recruiting_Workbook.xlsx
@@ -606,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -868,6 +868,9 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1200,15 +1203,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="128" t="inlineStr">
+      <c r="A3" s="130" t="inlineStr">
         <is>
           <t>BRG Realty Ventures</t>
         </is>
       </c>
-      <c r="B3" s="128" t="n">
+      <c r="B3" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="130" t="inlineStr">
         <is>
           <t>Beau Beery</t>
         </is>
@@ -1218,7 +1221,7 @@
           <t>Founder</t>
         </is>
       </c>
-      <c r="E3" s="128" t="inlineStr">
+      <c r="E3" s="130" t="inlineStr">
         <is>
           <t>Gainesville</t>
         </is>
@@ -1231,15 +1234,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="128" t="inlineStr">
+      <c r="A4" s="130" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="128" t="n">
+      <c r="B4" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="130" t="inlineStr">
         <is>
           <t>Jaret Turkell</t>
         </is>
@@ -1249,7 +1252,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="128" t="inlineStr">
+      <c r="E4" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1262,15 +1265,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="130" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="130" t="inlineStr">
         <is>
           <t>Jason Stanton</t>
         </is>
@@ -1280,7 +1283,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E5" s="128" t="inlineStr">
+      <c r="E5" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1293,15 +1296,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="130" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="130" t="inlineStr">
         <is>
           <t>Matthew Mitchell</t>
         </is>
@@ -1311,7 +1314,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1324,15 +1327,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="128" t="inlineStr">
+      <c r="A7" s="130" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B7" s="128" t="n">
+      <c r="B7" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="130" t="inlineStr">
         <is>
           <t>Mitch Sinberg</t>
         </is>
@@ -1342,7 +1345,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="128" t="inlineStr">
+      <c r="E7" s="130" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -1355,15 +1358,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B8" s="128" t="n">
+      <c r="B8" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>Denny St. Romain</t>
         </is>
@@ -1373,7 +1376,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="128" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1386,15 +1389,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B9" s="128" t="n">
+      <c r="B9" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="130" t="inlineStr">
         <is>
           <t>Jubeen Vaghefi</t>
         </is>
@@ -1404,7 +1407,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="128" t="inlineStr">
+      <c r="E9" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -1417,15 +1420,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="128" t="inlineStr">
+      <c r="A10" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B10" s="128" t="n">
+      <c r="B10" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Tony Ballard</t>
         </is>
@@ -1435,7 +1438,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E10" s="128" t="inlineStr">
+      <c r="E10" s="130" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1448,15 +1451,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="128" t="inlineStr">
+      <c r="A11" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B11" s="128" t="n">
+      <c r="B11" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="130" t="inlineStr">
         <is>
           <t>Bradley Capas</t>
         </is>
@@ -1466,7 +1469,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E11" s="128" t="inlineStr">
+      <c r="E11" s="130" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1479,15 +1482,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="128" t="inlineStr">
+      <c r="A12" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B12" s="128" t="n">
+      <c r="B12" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="130" t="inlineStr">
         <is>
           <t>Casey Babb</t>
         </is>
@@ -1497,7 +1500,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E12" s="128" t="inlineStr">
+      <c r="E12" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1510,15 +1513,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B13" s="128" t="n">
+      <c r="B13" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="128" t="inlineStr">
+      <c r="C13" s="130" t="inlineStr">
         <is>
           <t>Miles Tombrink</t>
         </is>
@@ -1528,7 +1531,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E13" s="128" t="inlineStr">
+      <c r="E13" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1541,15 +1544,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="130" t="inlineStr">
         <is>
           <t>Collison Captial</t>
         </is>
       </c>
-      <c r="B14" s="128" t="n">
+      <c r="B14" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="128" t="inlineStr">
+      <c r="C14" s="130" t="inlineStr">
         <is>
           <t>Carter Collison</t>
         </is>
@@ -1559,7 +1562,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E14" s="128" t="inlineStr">
+      <c r="E14" s="130" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -1572,21 +1575,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="128" t="inlineStr">
+      <c r="A15" s="130" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B15" s="128" t="n">
+      <c r="B15" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="130" t="inlineStr">
         <is>
           <t>Alexander Isaia</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="128" t="inlineStr">
+      <c r="E15" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1599,21 +1602,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="128" t="inlineStr">
+      <c r="A16" s="130" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B16" s="128" t="n">
+      <c r="B16" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="130" t="inlineStr">
         <is>
           <t>Jesse Spencer</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="128" t="inlineStr">
+      <c r="E16" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1626,15 +1629,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="128" t="inlineStr">
+      <c r="A17" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B17" s="128" t="n">
+      <c r="B17" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="130" t="inlineStr">
         <is>
           <t>Mike Donaldson</t>
         </is>
@@ -1644,7 +1647,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E17" s="128" t="inlineStr">
+      <c r="E17" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1657,15 +1660,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="128" t="inlineStr">
+      <c r="A18" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B18" s="128" t="n">
+      <c r="B18" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="130" t="inlineStr">
         <is>
           <t>Nick Meoli</t>
         </is>
@@ -1675,7 +1678,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E18" s="128" t="inlineStr">
+      <c r="E18" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1688,21 +1691,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="128" t="inlineStr">
+      <c r="A19" s="130" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B19" s="128" t="n">
+      <c r="B19" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="130" t="inlineStr">
         <is>
           <t>Carlos Fausto</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="128" t="inlineStr">
+      <c r="E19" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1711,21 +1714,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="130" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B20" s="128" t="n">
+      <c r="B20" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="130" t="inlineStr">
         <is>
           <t>Elior Levi</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="128" t="inlineStr">
+      <c r="E20" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1738,21 +1741,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="128" t="inlineStr">
+      <c r="A21" s="130" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B21" s="128" t="n">
+      <c r="B21" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="128" t="inlineStr">
+      <c r="C21" s="130" t="inlineStr">
         <is>
           <t>Mauricio Villasuso</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="128" t="inlineStr">
+      <c r="E21" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1761,15 +1764,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="128" t="inlineStr">
+      <c r="A22" s="130" t="inlineStr">
         <is>
           <t>Foundray</t>
         </is>
       </c>
-      <c r="B22" s="128" t="n">
+      <c r="B22" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="128" t="inlineStr">
+      <c r="C22" s="130" t="inlineStr">
         <is>
           <t>Andrew Green</t>
         </is>
@@ -1779,7 +1782,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E22" s="128" t="inlineStr">
+      <c r="E22" s="130" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -1792,15 +1795,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="128" t="inlineStr">
+      <c r="A23" s="130" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B23" s="128" t="n">
+      <c r="B23" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="128" t="inlineStr">
+      <c r="C23" s="130" t="inlineStr">
         <is>
           <t>Darron Kattan</t>
         </is>
@@ -1810,7 +1813,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="128" t="inlineStr">
+      <c r="E23" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1823,15 +1826,15 @@
       <c r="G23" s="129" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="128" t="inlineStr">
+      <c r="A24" s="130" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B24" s="128" t="n">
+      <c r="B24" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="128" t="inlineStr">
+      <c r="C24" s="130" t="inlineStr">
         <is>
           <t>Jonathan Barclay</t>
         </is>
@@ -1841,7 +1844,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E24" s="128" t="inlineStr">
+      <c r="E24" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1854,15 +1857,15 @@
       <c r="G24" s="129" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="128" t="inlineStr">
+      <c r="A25" s="130" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B25" s="128" t="n">
+      <c r="B25" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="128" t="inlineStr">
+      <c r="C25" s="130" t="inlineStr">
         <is>
           <t>Mark Savarese</t>
         </is>
@@ -1872,7 +1875,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E25" s="128" t="inlineStr">
+      <c r="E25" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1885,15 +1888,15 @@
       <c r="G25" s="129" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="128" t="inlineStr">
+      <c r="A26" s="130" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B26" s="128" t="n">
+      <c r="B26" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="128" t="inlineStr">
+      <c r="C26" s="130" t="inlineStr">
         <is>
           <t>Ryan Wold</t>
         </is>
@@ -1903,7 +1906,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E26" s="128" t="inlineStr">
+      <c r="E26" s="130" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1916,15 +1919,15 @@
       <c r="G26" s="129" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="128" t="inlineStr">
+      <c r="A27" s="130" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B27" s="128" t="n">
+      <c r="B27" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="128" t="inlineStr">
+      <c r="C27" s="130" t="inlineStr">
         <is>
           <t>Adam Podbelski</t>
         </is>
@@ -1934,7 +1937,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E27" s="128" t="inlineStr">
+      <c r="E27" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1947,15 +1950,15 @@
       <c r="G27" s="129" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="128" t="inlineStr">
+      <c r="A28" s="130" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B28" s="128" t="n">
+      <c r="B28" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="128" t="inlineStr">
+      <c r="C28" s="130" t="inlineStr">
         <is>
           <t>Alec Bashein</t>
         </is>
@@ -1965,7 +1968,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E28" s="128" t="inlineStr">
+      <c r="E28" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1978,15 +1981,15 @@
       <c r="G28" s="129" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="128" t="inlineStr">
+      <c r="A29" s="130" t="inlineStr">
         <is>
           <t>Hull Multifamily</t>
         </is>
       </c>
-      <c r="B29" s="128" t="n">
+      <c r="B29" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="128" t="inlineStr">
+      <c r="C29" s="130" t="inlineStr">
         <is>
           <t>Nick Hull</t>
         </is>
@@ -1996,7 +1999,7 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="E29" s="128" t="inlineStr">
+      <c r="E29" s="130" t="inlineStr">
         <is>
           <t>Naples</t>
         </is>
@@ -2009,15 +2012,15 @@
       <c r="G29" s="129" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="128" t="inlineStr">
+      <c r="A30" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B30" s="128" t="n">
+      <c r="B30" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="128" t="inlineStr">
+      <c r="C30" s="130" t="inlineStr">
         <is>
           <t>Cliff Taylor</t>
         </is>
@@ -2027,7 +2030,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E30" s="128" t="inlineStr">
+      <c r="E30" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2040,15 +2043,15 @@
       <c r="G30" s="129" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="128" t="inlineStr">
+      <c r="A31" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B31" s="128" t="n">
+      <c r="B31" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="128" t="inlineStr">
+      <c r="C31" s="130" t="inlineStr">
         <is>
           <t>Maurice Habif</t>
         </is>
@@ -2058,7 +2061,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E31" s="128" t="inlineStr">
+      <c r="E31" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2071,15 +2074,15 @@
       <c r="G31" s="129" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="128" t="inlineStr">
+      <c r="A32" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B32" s="128" t="n">
+      <c r="B32" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="128" t="inlineStr">
+      <c r="C32" s="130" t="inlineStr">
         <is>
           <t>Zach Nolan</t>
         </is>
@@ -2089,7 +2092,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E32" s="128" t="inlineStr">
+      <c r="E32" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2102,15 +2105,15 @@
       <c r="G32" s="129" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="128" t="inlineStr">
+      <c r="A33" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B33" s="128" t="n">
+      <c r="B33" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="128" t="inlineStr">
+      <c r="C33" s="130" t="inlineStr">
         <is>
           <t>Kyle Butler</t>
         </is>
@@ -2120,7 +2123,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E33" s="128" t="inlineStr">
+      <c r="E33" s="130" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2133,15 +2136,15 @@
       <c r="G33" s="129" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="128" t="inlineStr">
+      <c r="A34" s="130" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B34" s="128" t="n">
+      <c r="B34" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="128" t="inlineStr">
+      <c r="C34" s="130" t="inlineStr">
         <is>
           <t>Deme Mekras</t>
         </is>
@@ -2151,7 +2154,7 @@
           <t>Managing Partner, CEO</t>
         </is>
       </c>
-      <c r="E34" s="128" t="inlineStr">
+      <c r="E34" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2164,15 +2167,15 @@
       <c r="G34" s="129" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="128" t="inlineStr">
+      <c r="A35" s="130" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B35" s="128" t="n">
+      <c r="B35" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="128" t="inlineStr">
+      <c r="C35" s="130" t="inlineStr">
         <is>
           <t>Sam Mekras</t>
         </is>
@@ -2182,7 +2185,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E35" s="128" t="inlineStr">
+      <c r="E35" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2195,15 +2198,15 @@
       <c r="G35" s="129" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="128" t="inlineStr">
+      <c r="A36" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B36" s="128" t="n">
+      <c r="B36" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="128" t="inlineStr">
+      <c r="C36" s="130" t="inlineStr">
         <is>
           <t>Felipe Echarte</t>
         </is>
@@ -2213,7 +2216,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E36" s="128" t="inlineStr">
+      <c r="E36" s="130" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2226,15 +2229,15 @@
       <c r="G36" s="129" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="128" t="inlineStr">
+      <c r="A37" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B37" s="128" t="n">
+      <c r="B37" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="128" t="inlineStr">
+      <c r="C37" s="130" t="inlineStr">
         <is>
           <t>Joseph Thomas</t>
         </is>
@@ -2244,7 +2247,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E37" s="128" t="inlineStr">
+      <c r="E37" s="130" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2257,15 +2260,15 @@
       <c r="G37" s="129" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="128" t="inlineStr">
+      <c r="A38" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B38" s="128" t="n">
+      <c r="B38" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="128" t="inlineStr">
+      <c r="C38" s="130" t="inlineStr">
         <is>
           <t>Ray Turchi</t>
         </is>
@@ -2275,7 +2278,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E38" s="128" t="inlineStr">
+      <c r="E38" s="130" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2288,15 +2291,15 @@
       <c r="G38" s="129" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="128" t="inlineStr">
+      <c r="A39" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B39" s="128" t="n">
+      <c r="B39" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="128" t="inlineStr">
+      <c r="C39" s="130" t="inlineStr">
         <is>
           <t>Adam Marcuvitz</t>
         </is>
@@ -2306,7 +2309,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E39" s="128" t="inlineStr">
+      <c r="E39" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2319,15 +2322,15 @@
       <c r="G39" s="129" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="128" t="inlineStr">
+      <c r="A40" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B40" s="128" t="n">
+      <c r="B40" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="128" t="inlineStr">
+      <c r="C40" s="130" t="inlineStr">
         <is>
           <t>Erik Bjornson</t>
         </is>
@@ -2337,7 +2340,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E40" s="128" t="inlineStr">
+      <c r="E40" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2350,15 +2353,15 @@
       <c r="G40" s="129" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="128" t="inlineStr">
+      <c r="A41" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B41" s="128" t="n">
+      <c r="B41" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="128" t="inlineStr">
+      <c r="C41" s="130" t="inlineStr">
         <is>
           <t>Luke Wickham</t>
         </is>
@@ -2368,7 +2371,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E41" s="128" t="inlineStr">
+      <c r="E41" s="130" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2377,15 +2380,15 @@
       <c r="G41" s="129" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="128" t="inlineStr">
+      <c r="A42" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B42" s="128" t="n">
+      <c r="B42" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="128" t="inlineStr">
+      <c r="C42" s="130" t="inlineStr">
         <is>
           <t>Tyler Nilsson</t>
         </is>
@@ -2395,7 +2398,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E42" s="128" t="inlineStr">
+      <c r="E42" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2408,15 +2411,15 @@
       <c r="G42" s="129" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="128" t="inlineStr">
+      <c r="A43" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B43" s="128" t="n">
+      <c r="B43" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="128" t="inlineStr">
+      <c r="C43" s="130" t="inlineStr">
         <is>
           <t>Kyle Kundiger</t>
         </is>
@@ -2426,7 +2429,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E43" s="128" t="inlineStr">
+      <c r="E43" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2439,21 +2442,21 @@
       <c r="G43" s="129" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="128" t="inlineStr">
+      <c r="A44" s="130" t="inlineStr">
         <is>
           <t>Matthew</t>
         </is>
       </c>
-      <c r="B44" s="128" t="n">
+      <c r="B44" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="128" t="inlineStr">
+      <c r="C44" s="130" t="inlineStr">
         <is>
           <t>William Bruce</t>
         </is>
       </c>
       <c r="D44" s="129" t="inlineStr"/>
-      <c r="E44" s="128" t="inlineStr">
+      <c r="E44" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2466,15 +2469,15 @@
       <c r="G44" s="129" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="128" t="inlineStr">
+      <c r="A45" s="130" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B45" s="128" t="n">
+      <c r="B45" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="128" t="inlineStr">
+      <c r="C45" s="130" t="inlineStr">
         <is>
           <t>John Rutherford</t>
         </is>
@@ -2484,7 +2487,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E45" s="128" t="inlineStr">
+      <c r="E45" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2497,15 +2500,15 @@
       <c r="G45" s="129" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="128" t="inlineStr">
+      <c r="A46" s="130" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B46" s="128" t="n">
+      <c r="B46" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="128" t="inlineStr">
+      <c r="C46" s="130" t="inlineStr">
         <is>
           <t>Luke McCann</t>
         </is>
@@ -2515,7 +2518,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E46" s="128" t="inlineStr">
+      <c r="E46" s="130" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2528,15 +2531,15 @@
       <c r="G46" s="129" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="128" t="inlineStr">
+      <c r="A47" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B47" s="128" t="n">
+      <c r="B47" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="128" t="inlineStr">
+      <c r="C47" s="130" t="inlineStr">
         <is>
           <t>Avery Klann</t>
         </is>
@@ -2546,7 +2549,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E47" s="128" t="inlineStr">
+      <c r="E47" s="130" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2559,15 +2562,15 @@
       <c r="G47" s="129" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="128" t="inlineStr">
+      <c r="A48" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B48" s="128" t="n">
+      <c r="B48" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="128" t="inlineStr">
+      <c r="C48" s="130" t="inlineStr">
         <is>
           <t>Hampton Beebe</t>
         </is>
@@ -2577,7 +2580,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E48" s="128" t="inlineStr">
+      <c r="E48" s="130" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2590,15 +2593,15 @@
       <c r="G48" s="129" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="128" t="inlineStr">
+      <c r="A49" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B49" s="128" t="n">
+      <c r="B49" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C49" s="128" t="inlineStr">
+      <c r="C49" s="130" t="inlineStr">
         <is>
           <t>Patrick Dufour</t>
         </is>
@@ -2608,7 +2611,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E49" s="128" t="inlineStr">
+      <c r="E49" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2621,15 +2624,15 @@
       <c r="G49" s="129" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="128" t="inlineStr">
+      <c r="A50" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B50" s="128" t="n">
+      <c r="B50" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="128" t="inlineStr">
+      <c r="C50" s="130" t="inlineStr">
         <is>
           <t>Scott Ramey</t>
         </is>
@@ -2639,7 +2642,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E50" s="128" t="inlineStr">
+      <c r="E50" s="130" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2648,21 +2651,21 @@
       <c r="G50" s="129" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="128" t="inlineStr">
+      <c r="A51" s="130" t="inlineStr">
         <is>
           <t>One Commercial</t>
         </is>
       </c>
-      <c r="B51" s="128" t="n">
+      <c r="B51" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="128" t="inlineStr">
+      <c r="C51" s="130" t="inlineStr">
         <is>
           <t>Alexis Shapiro</t>
         </is>
       </c>
       <c r="D51" s="129" t="inlineStr"/>
-      <c r="E51" s="128" t="inlineStr">
+      <c r="E51" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2675,15 +2678,15 @@
       <c r="G51" s="129" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="128" t="inlineStr">
+      <c r="A52" s="130" t="inlineStr">
         <is>
           <t>ReMax</t>
         </is>
       </c>
-      <c r="B52" s="128" t="n">
+      <c r="B52" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="128" t="inlineStr">
+      <c r="C52" s="130" t="inlineStr">
         <is>
           <t>Roger Lohse</t>
         </is>
@@ -2693,7 +2696,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E52" s="128" t="inlineStr">
+      <c r="E52" s="130" t="inlineStr">
         <is>
           <t>Hollywood</t>
         </is>
@@ -2706,15 +2709,15 @@
       <c r="G52" s="129" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="128" t="inlineStr">
+      <c r="A53" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B53" s="128" t="n">
+      <c r="B53" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="128" t="inlineStr">
+      <c r="C53" s="130" t="inlineStr">
         <is>
           <t>Aaron Hargrove</t>
         </is>
@@ -2724,7 +2727,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E53" s="128" t="inlineStr">
+      <c r="E53" s="130" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2737,15 +2740,15 @@
       <c r="G53" s="129" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="128" t="inlineStr">
+      <c r="A54" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B54" s="128" t="n">
+      <c r="B54" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="128" t="inlineStr">
+      <c r="C54" s="130" t="inlineStr">
         <is>
           <t>Brian Moulder</t>
         </is>
@@ -2755,7 +2758,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E54" s="128" t="inlineStr">
+      <c r="E54" s="130" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -2768,15 +2771,15 @@
       <c r="G54" s="129" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="128" t="inlineStr">
+      <c r="A55" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B55" s="128" t="n">
+      <c r="B55" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C55" s="128" t="inlineStr">
+      <c r="C55" s="130" t="inlineStr">
         <is>
           <t>Chris Chadbourne</t>
         </is>
@@ -2786,7 +2789,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E55" s="128" t="inlineStr">
+      <c r="E55" s="130" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2799,15 +2802,15 @@
       <c r="G55" s="129" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="128" t="inlineStr">
+      <c r="A56" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B56" s="128" t="n">
+      <c r="B56" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="128" t="inlineStr">
+      <c r="C56" s="130" t="inlineStr">
         <is>
           <t>Still Hunter</t>
         </is>
@@ -2817,7 +2820,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E56" s="128" t="inlineStr">
+      <c r="E56" s="130" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -3818,15 +3821,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="128" t="inlineStr">
+      <c r="A3" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="128" t="n">
+      <c r="B3" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="130" t="inlineStr">
         <is>
           <t>John Phoenix</t>
         </is>
@@ -3836,7 +3839,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E3" s="128" t="inlineStr">
+      <c r="E3" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3849,15 +3852,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="128" t="inlineStr">
+      <c r="A4" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="128" t="n">
+      <c r="B4" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="130" t="inlineStr">
         <is>
           <t>Louis Smart</t>
         </is>
@@ -3867,7 +3870,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="128" t="inlineStr">
+      <c r="E4" s="130" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3880,15 +3883,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="130" t="inlineStr">
         <is>
           <t>Richard Gore</t>
         </is>
@@ -3898,7 +3901,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="128" t="inlineStr">
+      <c r="E5" s="130" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3911,15 +3914,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="130" t="inlineStr">
         <is>
           <t>Tyler Fish</t>
         </is>
@@ -3929,7 +3932,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3942,15 +3945,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="128" t="inlineStr">
+      <c r="A7" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="128" t="n">
+      <c r="B7" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="130" t="inlineStr">
         <is>
           <t>Kyle Chase</t>
         </is>
@@ -3960,7 +3963,7 @@
           <t>Executive Vice President</t>
         </is>
       </c>
-      <c r="E7" s="128" t="inlineStr">
+      <c r="E7" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3973,15 +3976,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="128" t="n">
+      <c r="B8" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>Paul Marley</t>
         </is>
@@ -3991,7 +3994,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="128" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4004,15 +4007,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="128" t="n">
+      <c r="B9" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="130" t="inlineStr">
         <is>
           <t>Jordan McCarley</t>
         </is>
@@ -4022,7 +4025,7 @@
           <t>Executive Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="128" t="inlineStr"/>
+      <c r="E9" s="130" t="inlineStr"/>
       <c r="F9" s="129" t="inlineStr">
         <is>
           <t>https://multifamily.cushwake.com/Offices/Charlotte/Team</t>
@@ -4031,15 +4034,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="128" t="inlineStr">
+      <c r="A10" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="128" t="n">
+      <c r="B10" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Alex McDermott</t>
         </is>
@@ -4049,7 +4052,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="128" t="inlineStr">
+      <c r="E10" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4062,15 +4065,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="128" t="inlineStr">
+      <c r="A11" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="128" t="n">
+      <c r="B11" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="130" t="inlineStr">
         <is>
           <t>Austin Green</t>
         </is>
@@ -4080,7 +4083,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E11" s="128" t="inlineStr">
+      <c r="E11" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4093,15 +4096,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="128" t="inlineStr">
+      <c r="A12" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="128" t="n">
+      <c r="B12" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="130" t="inlineStr">
         <is>
           <t>William Martin</t>
         </is>
@@ -4111,7 +4114,7 @@
           <t>Capital Markets Associate</t>
         </is>
       </c>
-      <c r="E12" s="128" t="inlineStr">
+      <c r="E12" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4124,15 +4127,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="128" t="n">
+      <c r="B13" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="128" t="inlineStr">
+      <c r="C13" s="130" t="inlineStr">
         <is>
           <t>Casey Sherman</t>
         </is>
@@ -4142,7 +4145,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="128" t="inlineStr">
+      <c r="E13" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4155,15 +4158,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="128" t="n">
+      <c r="B14" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="128" t="inlineStr">
+      <c r="C14" s="130" t="inlineStr">
         <is>
           <t>John Gavigan</t>
         </is>
@@ -4173,7 +4176,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E14" s="128" t="inlineStr">
+      <c r="E14" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4186,15 +4189,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="128" t="inlineStr">
+      <c r="A15" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="128" t="n">
+      <c r="B15" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="130" t="inlineStr">
         <is>
           <t>Dean Smith</t>
         </is>
@@ -4204,7 +4207,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E15" s="128" t="inlineStr">
+      <c r="E15" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4217,15 +4220,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="128" t="inlineStr">
+      <c r="A16" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B16" s="128" t="n">
+      <c r="B16" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="130" t="inlineStr">
         <is>
           <t>John Heimburger</t>
         </is>
@@ -4235,7 +4238,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E16" s="128" t="inlineStr">
+      <c r="E16" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4248,15 +4251,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="128" t="inlineStr">
+      <c r="A17" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B17" s="128" t="n">
+      <c r="B17" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="130" t="inlineStr">
         <is>
           <t>Sean Wood</t>
         </is>
@@ -4266,7 +4269,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E17" s="128" t="inlineStr">
+      <c r="E17" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4279,15 +4282,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="128" t="inlineStr">
+      <c r="A18" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="128" t="n">
+      <c r="B18" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="130" t="inlineStr">
         <is>
           <t>Alex Okulski</t>
         </is>
@@ -4297,7 +4300,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="128" t="inlineStr">
+      <c r="E18" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4310,15 +4313,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="128" t="inlineStr">
+      <c r="A19" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="128" t="n">
+      <c r="B19" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="130" t="inlineStr">
         <is>
           <t>Rob Coleman</t>
         </is>
@@ -4328,7 +4331,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E19" s="128" t="inlineStr">
+      <c r="E19" s="130" t="inlineStr">
         <is>
           <t>Raleigh</t>
         </is>
@@ -4341,15 +4344,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="128" t="n">
+      <c r="B20" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="130" t="inlineStr">
         <is>
           <t>Michael Saclarides</t>
         </is>
@@ -4359,7 +4362,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E20" s="128" t="inlineStr">
+      <c r="E20" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4372,15 +4375,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="128" t="inlineStr">
+      <c r="A21" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="128" t="n">
+      <c r="B21" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="128" t="inlineStr">
+      <c r="C21" s="130" t="inlineStr">
         <is>
           <t>Devin Bryan</t>
         </is>
@@ -4390,7 +4393,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E21" s="128" t="inlineStr">
+      <c r="E21" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4403,15 +4406,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="128" t="inlineStr">
+      <c r="A22" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B22" s="128" t="n">
+      <c r="B22" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="128" t="inlineStr">
+      <c r="C22" s="130" t="inlineStr">
         <is>
           <t>Fletcher Dunn</t>
         </is>
@@ -4421,7 +4424,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E22" s="128" t="inlineStr">
+      <c r="E22" s="130" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -5415,21 +5418,21 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="128" t="inlineStr">
+      <c r="A3" s="130" t="inlineStr">
         <is>
           <t>802 Property | Steadfast Group</t>
         </is>
       </c>
-      <c r="B3" s="128" t="n">
+      <c r="B3" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="130" t="inlineStr">
         <is>
           <t>Andy Hill</t>
         </is>
       </c>
       <c r="D3" s="129" t="inlineStr"/>
-      <c r="E3" s="128" t="inlineStr">
+      <c r="E3" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5438,21 +5441,21 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="128" t="inlineStr">
+      <c r="A4" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="128" t="n">
+      <c r="B4" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="130" t="inlineStr">
         <is>
           <t>Brett Carr</t>
         </is>
       </c>
       <c r="D4" s="129" t="inlineStr"/>
-      <c r="E4" s="128" t="inlineStr">
+      <c r="E4" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5461,21 +5464,21 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="130" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="130" t="inlineStr">
         <is>
           <t>David Dorris</t>
         </is>
       </c>
       <c r="D5" s="129" t="inlineStr"/>
-      <c r="E5" s="128" t="inlineStr">
+      <c r="E5" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5484,21 +5487,21 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="130" t="inlineStr">
         <is>
           <t>Tyler Mayo</t>
         </is>
       </c>
       <c r="D6" s="129" t="inlineStr"/>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5507,21 +5510,21 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="128" t="inlineStr">
+      <c r="A7" s="130" t="inlineStr">
         <is>
           <t>MRG Realty Partners</t>
         </is>
       </c>
-      <c r="B7" s="128" t="n">
+      <c r="B7" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="130" t="inlineStr">
         <is>
           <t>Drew Lekowski</t>
         </is>
       </c>
       <c r="D7" s="129" t="inlineStr"/>
-      <c r="E7" s="128" t="inlineStr">
+      <c r="E7" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5530,21 +5533,21 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B8" s="128" t="n">
+      <c r="B8" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>David Stollenwerk</t>
         </is>
       </c>
       <c r="D8" s="129" t="inlineStr"/>
-      <c r="E8" s="128" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5553,21 +5556,21 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B9" s="128" t="n">
+      <c r="B9" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="130" t="inlineStr">
         <is>
           <t>Patrick Cosgrove</t>
         </is>
       </c>
       <c r="D9" s="129" t="inlineStr"/>
-      <c r="E9" s="128" t="inlineStr">
+      <c r="E9" s="130" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5576,21 +5579,21 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="128" t="inlineStr">
+      <c r="A10" s="130" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B10" s="128" t="n">
+      <c r="B10" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Austin Fragoletti</t>
         </is>
       </c>
       <c r="D10" s="129" t="inlineStr"/>
-      <c r="E10" s="128" t="inlineStr">
+      <c r="E10" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5599,21 +5602,21 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="128" t="inlineStr">
+      <c r="A11" s="130" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B11" s="128" t="n">
+      <c r="B11" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="130" t="inlineStr">
         <is>
           <t>Sam Jackson</t>
         </is>
       </c>
       <c r="D11" s="129" t="inlineStr"/>
-      <c r="E11" s="128" t="inlineStr">
+      <c r="E11" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5622,21 +5625,21 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="128" t="inlineStr">
+      <c r="A12" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B12" s="128" t="n">
+      <c r="B12" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="130" t="inlineStr">
         <is>
           <t>Vince Lefler</t>
         </is>
       </c>
       <c r="D12" s="129" t="inlineStr"/>
-      <c r="E12" s="128" t="inlineStr">
+      <c r="E12" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5645,21 +5648,21 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="130" t="inlineStr">
         <is>
           <t>Redwood Collective Acquisitions, LLC | The Kirkland Company</t>
         </is>
       </c>
-      <c r="B13" s="128" t="n">
+      <c r="B13" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="128" t="inlineStr">
+      <c r="C13" s="130" t="inlineStr">
         <is>
           <t>William Kirkland</t>
         </is>
       </c>
       <c r="D13" s="129" t="inlineStr"/>
-      <c r="E13" s="128" t="inlineStr">
+      <c r="E13" s="130" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5668,21 +5671,21 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="130" t="inlineStr">
         <is>
           <t>Stevens Group, LLC</t>
         </is>
       </c>
-      <c r="B14" s="128" t="n">
+      <c r="B14" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="128" t="inlineStr">
+      <c r="C14" s="130" t="inlineStr">
         <is>
           <t>Rusty Rust</t>
         </is>
       </c>
       <c r="D14" s="129" t="inlineStr"/>
-      <c r="E14" s="128" t="inlineStr">
+      <c r="E14" s="130" t="inlineStr">
         <is>
           <t>Antioch</t>
         </is>
@@ -5691,21 +5694,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="128" t="inlineStr">
+      <c r="A15" s="130" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B15" s="128" t="n">
+      <c r="B15" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="130" t="inlineStr">
         <is>
           <t>Miller Harris</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="128" t="inlineStr">
+      <c r="E15" s="130" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5714,21 +5717,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="128" t="inlineStr">
+      <c r="A16" s="130" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B16" s="128" t="n">
+      <c r="B16" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="130" t="inlineStr">
         <is>
           <t>Zac Wracher</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="128" t="inlineStr">
+      <c r="E16" s="130" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5737,21 +5740,21 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="128" t="inlineStr">
+      <c r="A17" s="130" t="inlineStr">
         <is>
           <t>The Parks Group Commercial</t>
         </is>
       </c>
-      <c r="B17" s="128" t="n">
+      <c r="B17" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="130" t="inlineStr">
         <is>
           <t>John Harney</t>
         </is>
       </c>
       <c r="D17" s="129" t="inlineStr"/>
-      <c r="E17" s="128" t="inlineStr">
+      <c r="E17" s="130" t="inlineStr">
         <is>
           <t>Murfreesboro</t>
         </is>
@@ -5760,21 +5763,21 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="128" t="inlineStr">
+      <c r="A18" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B18" s="128" t="n">
+      <c r="B18" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="130" t="inlineStr">
         <is>
           <t>Anne McGinn</t>
         </is>
       </c>
       <c r="D18" s="129" t="inlineStr"/>
-      <c r="E18" s="128" t="inlineStr">
+      <c r="E18" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5783,21 +5786,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="128" t="inlineStr">
+      <c r="A19" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="128" t="n">
+      <c r="B19" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="130" t="inlineStr">
         <is>
           <t>Brad Boston</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="128" t="inlineStr">
+      <c r="E19" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5806,21 +5809,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="128" t="n">
+      <c r="B20" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="130" t="inlineStr">
         <is>
           <t>Brett Kingman</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="128" t="inlineStr">
+      <c r="E20" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5829,21 +5832,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="128" t="inlineStr">
+      <c r="A21" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="128" t="n">
+      <c r="B21" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="128" t="inlineStr">
+      <c r="C21" s="130" t="inlineStr">
         <is>
           <t>Robbie O'Bryan</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="128" t="inlineStr">
+      <c r="E21" s="130" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -7613,15 +7616,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="128" t="inlineStr">
+      <c r="A3" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="128" t="n">
+      <c r="B3" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="130" t="inlineStr">
         <is>
           <t>Calvin Griffith</t>
         </is>
@@ -7631,7 +7634,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E3" s="128" t="inlineStr">
+      <c r="E3" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7644,15 +7647,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="128" t="inlineStr">
+      <c r="A4" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="128" t="n">
+      <c r="B4" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="130" t="inlineStr">
         <is>
           <t>Peyton Cox</t>
         </is>
@@ -7662,7 +7665,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E4" s="128" t="inlineStr">
+      <c r="E4" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7675,15 +7678,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="130" t="inlineStr">
         <is>
           <t>Andrew Blackmon</t>
         </is>
@@ -7693,7 +7696,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E5" s="128" t="inlineStr">
+      <c r="E5" s="130" t="inlineStr">
         <is>
           <t>Hampton Roads/Richmond</t>
         </is>
@@ -7706,15 +7709,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="130" t="inlineStr">
         <is>
           <t>Garrison Gore</t>
         </is>
@@ -7724,7 +7727,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7737,15 +7740,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="128" t="inlineStr">
+      <c r="A7" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="128" t="n">
+      <c r="B7" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="130" t="inlineStr">
         <is>
           <t>Thomas Leachman</t>
         </is>
@@ -7755,7 +7758,7 @@
           <t>Senior Vice President, National Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="128" t="inlineStr">
+      <c r="E7" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7768,15 +7771,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="128" t="n">
+      <c r="B8" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -7786,7 +7789,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="128" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Richmond (Mid-Atlantic)</t>
         </is>
@@ -7799,15 +7802,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B9" s="128" t="n">
+      <c r="B9" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="130" t="inlineStr">
         <is>
           <t>William Dickinson</t>
         </is>
@@ -7817,7 +7820,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E9" s="128" t="inlineStr">
+      <c r="E9" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7830,15 +7833,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="128" t="inlineStr">
+      <c r="A10" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="128" t="n">
+      <c r="B10" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Jorge Rosa / Paul C. Norman, Jr.</t>
         </is>
@@ -7848,7 +7851,7 @@
           <t>Executive Managing Directors</t>
         </is>
       </c>
-      <c r="E10" s="128" t="inlineStr">
+      <c r="E10" s="130" t="inlineStr">
         <is>
           <t>Based DC, covers Richmond</t>
         </is>
@@ -7857,15 +7860,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="128" t="inlineStr">
+      <c r="A11" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B11" s="128" t="n">
+      <c r="B11" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="130" t="inlineStr">
         <is>
           <t>Christopher Chadwick</t>
         </is>
@@ -7875,7 +7878,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E11" s="128" t="inlineStr">
+      <c r="E11" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7888,15 +7891,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="128" t="inlineStr">
+      <c r="A12" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B12" s="128" t="n">
+      <c r="B12" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="130" t="inlineStr">
         <is>
           <t>Justin Ferguson</t>
         </is>
@@ -7906,7 +7909,7 @@
           <t>Multifamily Specialist</t>
         </is>
       </c>
-      <c r="E12" s="128" t="inlineStr">
+      <c r="E12" s="130" t="inlineStr">
         <is>
           <t>Richmond (Southern VA office)</t>
         </is>
@@ -7919,15 +7922,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B13" s="128" t="n">
+      <c r="B13" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="128" t="inlineStr">
+      <c r="C13" s="130" t="inlineStr">
         <is>
           <t>Martin Mooradian</t>
         </is>
@@ -7937,7 +7940,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="128" t="inlineStr">
+      <c r="E13" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7950,15 +7953,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B14" s="128" t="n">
+      <c r="B14" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="128" t="inlineStr">
+      <c r="C14" s="130" t="inlineStr">
         <is>
           <t>Mark Williford</t>
         </is>
@@ -7968,7 +7971,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E14" s="128" t="inlineStr">
+      <c r="E14" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7981,15 +7984,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="128" t="inlineStr">
+      <c r="A15" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="128" t="n">
+      <c r="B15" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="130" t="inlineStr">
         <is>
           <t>Will Bradley</t>
         </is>
@@ -7999,7 +8002,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="128" t="inlineStr">
+      <c r="E15" s="130" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -8872,15 +8875,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="128" t="inlineStr">
+      <c r="A3" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="128" t="n">
+      <c r="B3" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="130" t="inlineStr">
         <is>
           <t>Bob Dean (Robert G. Dean III)</t>
         </is>
@@ -8890,7 +8893,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E3" s="128" t="inlineStr">
+      <c r="E3" s="130" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA / Suburban MD</t>
         </is>
@@ -8903,15 +8906,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="128" t="inlineStr">
+      <c r="A4" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="128" t="n">
+      <c r="B4" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="130" t="inlineStr">
         <is>
           <t>John T. Sheridan, Jr.</t>
         </is>
@@ -8921,7 +8924,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="128" t="inlineStr">
+      <c r="E4" s="130" t="inlineStr">
         <is>
           <t>DC / VA / MD</t>
         </is>
@@ -8934,15 +8937,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="130" t="inlineStr">
         <is>
           <t>Michael Muldowney</t>
         </is>
@@ -8952,7 +8955,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E5" s="128" t="inlineStr">
+      <c r="E5" s="130" t="inlineStr">
         <is>
           <t>Washington, DC / MD suburbs</t>
         </is>
@@ -8965,15 +8968,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="130" t="inlineStr">
         <is>
           <t>Bill Roohan</t>
         </is>
@@ -8983,7 +8986,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="130" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
@@ -8996,15 +8999,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="128" t="inlineStr">
+      <c r="A7" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="128" t="n">
+      <c r="B7" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="130" t="inlineStr">
         <is>
           <t>Chandler Pace</t>
         </is>
@@ -9014,7 +9017,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E7" s="128" t="inlineStr">
+      <c r="E7" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9027,15 +9030,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="128" t="n">
+      <c r="B8" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -9045,7 +9048,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="128" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA</t>
         </is>
@@ -9058,15 +9061,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="128" t="n">
+      <c r="B9" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="130" t="inlineStr">
         <is>
           <t>Jorge Rosa</t>
         </is>
@@ -9076,7 +9079,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="128" t="inlineStr">
+      <c r="E9" s="130" t="inlineStr">
         <is>
           <t>Washington, DC / MD / VA</t>
         </is>
@@ -9089,15 +9092,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="128" t="inlineStr">
+      <c r="A10" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="128" t="n">
+      <c r="B10" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Paul C. Norman, Jr.</t>
         </is>
@@ -9107,7 +9110,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="128" t="inlineStr">
+      <c r="E10" s="130" t="inlineStr">
         <is>
           <t>Washington, DC metro</t>
         </is>
@@ -9120,15 +9123,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="128" t="inlineStr">
+      <c r="A11" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="128" t="n">
+      <c r="B11" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="130" t="inlineStr">
         <is>
           <t>Mac Hollensteiner</t>
         </is>
@@ -9138,7 +9141,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E11" s="128" t="inlineStr">
+      <c r="E11" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9151,15 +9154,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="128" t="inlineStr">
+      <c r="A12" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B12" s="128" t="n">
+      <c r="B12" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="130" t="inlineStr">
         <is>
           <t>Brooke Hanson</t>
         </is>
@@ -9169,7 +9172,7 @@
           <t>Capital Markets Group</t>
         </is>
       </c>
-      <c r="E12" s="128" t="inlineStr">
+      <c r="E12" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9182,15 +9185,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="128" t="n">
+      <c r="B13" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="128" t="inlineStr">
+      <c r="C13" s="130" t="inlineStr">
         <is>
           <t>Andrew Weir</t>
         </is>
@@ -9200,7 +9203,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E13" s="128" t="inlineStr">
+      <c r="E13" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9213,15 +9216,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="128" t="n">
+      <c r="B14" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="128" t="inlineStr">
+      <c r="C14" s="130" t="inlineStr">
         <is>
           <t>Jamie Leachman</t>
         </is>
@@ -9231,7 +9234,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E14" s="128" t="inlineStr">
+      <c r="E14" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9244,15 +9247,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="128" t="inlineStr">
+      <c r="A15" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B15" s="128" t="n">
+      <c r="B15" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="130" t="inlineStr">
         <is>
           <t>Robert Jenkins</t>
         </is>
@@ -9262,7 +9265,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="128" t="inlineStr">
+      <c r="E15" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9275,15 +9278,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="128" t="inlineStr">
+      <c r="A16" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B16" s="128" t="n">
+      <c r="B16" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="130" t="inlineStr">
         <is>
           <t>Bret Thompson</t>
         </is>
@@ -9293,7 +9296,7 @@
           <t>Senior Director</t>
         </is>
       </c>
-      <c r="E16" s="128" t="inlineStr">
+      <c r="E16" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9306,15 +9309,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="128" t="inlineStr">
+      <c r="A17" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="128" t="n">
+      <c r="B17" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="130" t="inlineStr">
         <is>
           <t>Lorenzo M. Wooten, Jr., CCIM</t>
         </is>
@@ -9324,7 +9327,7 @@
           <t>Senior Director of Investments</t>
         </is>
       </c>
-      <c r="E17" s="128" t="inlineStr">
+      <c r="E17" s="130" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9337,15 +9340,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="128" t="inlineStr">
+      <c r="A18" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="128" t="n">
+      <c r="B18" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="130" t="inlineStr">
         <is>
           <t>Christine Espenshade</t>
         </is>
@@ -9355,7 +9358,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E18" s="128" t="inlineStr">
+      <c r="E18" s="130" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9368,15 +9371,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="128" t="inlineStr">
+      <c r="A19" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="128" t="n">
+      <c r="B19" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="130" t="inlineStr">
         <is>
           <t>Christopher Doerr</t>
         </is>
@@ -9386,7 +9389,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E19" s="128" t="inlineStr">
+      <c r="E19" s="130" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9399,15 +9402,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="128" t="n">
+      <c r="B20" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="130" t="inlineStr">
         <is>
           <t>William Harvey</t>
         </is>
@@ -9417,7 +9420,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E20" s="128" t="inlineStr">
+      <c r="E20" s="130" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -10286,15 +10289,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="128" t="inlineStr">
+      <c r="A3" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="128" t="n">
+      <c r="B3" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="130" t="inlineStr">
         <is>
           <t>Andrew Burns</t>
         </is>
@@ -10304,7 +10307,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E3" s="128" t="inlineStr">
+      <c r="E3" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10317,15 +10320,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="128" t="inlineStr">
+      <c r="A4" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="128" t="n">
+      <c r="B4" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="130" t="inlineStr">
         <is>
           <t>Jake Reid</t>
         </is>
@@ -10335,7 +10338,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="128" t="inlineStr">
+      <c r="E4" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10348,15 +10351,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="130" t="inlineStr">
         <is>
           <t>Kurt McGarry</t>
         </is>
@@ -10366,7 +10369,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="128" t="inlineStr">
+      <c r="E5" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10379,15 +10382,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="130" t="inlineStr">
         <is>
           <t>Shea Campbell</t>
         </is>
@@ -10397,7 +10400,7 @@
           <t>Vice Chairman / Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10410,15 +10413,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="128" t="inlineStr">
+      <c r="A7" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B7" s="128" t="n">
+      <c r="B7" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="130" t="inlineStr">
         <is>
           <t>Craig Hey</t>
         </is>
@@ -10428,7 +10431,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="128" t="inlineStr">
+      <c r="E7" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10441,15 +10444,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="128" t="n">
+      <c r="B8" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>Mike Kemether</t>
         </is>
@@ -10459,7 +10462,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E8" s="128" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10472,15 +10475,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="128" t="n">
+      <c r="B9" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="130" t="inlineStr">
         <is>
           <t>Morgan Berg</t>
         </is>
@@ -10490,7 +10493,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E9" s="128" t="inlineStr">
+      <c r="E9" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10503,15 +10506,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="128" t="inlineStr">
+      <c r="A10" s="130" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="128" t="n">
+      <c r="B10" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Robert Stickel</t>
         </is>
@@ -10521,7 +10524,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E10" s="128" t="inlineStr">
+      <c r="E10" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10534,15 +10537,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="128" t="inlineStr">
+      <c r="A11" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B11" s="128" t="n">
+      <c r="B11" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="130" t="inlineStr">
         <is>
           <t>Peter Yorck</t>
         </is>
@@ -10552,7 +10555,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E11" s="128" t="inlineStr">
+      <c r="E11" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10565,15 +10568,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="128" t="inlineStr">
+      <c r="A12" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="128" t="n">
+      <c r="B12" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="130" t="inlineStr">
         <is>
           <t>Dennis Mitchell</t>
         </is>
@@ -10583,7 +10586,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E12" s="128" t="inlineStr">
+      <c r="E12" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10596,15 +10599,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="128" t="inlineStr">
+      <c r="A13" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="128" t="n">
+      <c r="B13" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="128" t="inlineStr">
+      <c r="C13" s="130" t="inlineStr">
         <is>
           <t>Michael Fox</t>
         </is>
@@ -10614,7 +10617,7 @@
           <t>Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E13" s="128" t="inlineStr">
+      <c r="E13" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10627,15 +10630,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="128" t="inlineStr">
+      <c r="A14" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="128" t="n">
+      <c r="B14" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="128" t="inlineStr">
+      <c r="C14" s="130" t="inlineStr">
         <is>
           <t>John Weber</t>
         </is>
@@ -10645,7 +10648,7 @@
           <t>Investment Sales (Multifamily)</t>
         </is>
       </c>
-      <c r="E14" s="128" t="inlineStr">
+      <c r="E14" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10658,15 +10661,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="128" t="inlineStr">
+      <c r="A15" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B15" s="128" t="n">
+      <c r="B15" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="130" t="inlineStr">
         <is>
           <t>Marc Irvin</t>
         </is>
@@ -10676,7 +10679,7 @@
           <t>Managing Director Investments</t>
         </is>
       </c>
-      <c r="E15" s="128" t="inlineStr">
+      <c r="E15" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10689,15 +10692,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="128" t="inlineStr">
+      <c r="A16" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B16" s="128" t="n">
+      <c r="B16" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="130" t="inlineStr">
         <is>
           <t>Harold Shepard</t>
         </is>
@@ -10707,7 +10710,7 @@
           <t>Investment Broker</t>
         </is>
       </c>
-      <c r="E16" s="128" t="inlineStr">
+      <c r="E16" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10720,15 +10723,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="128" t="inlineStr">
+      <c r="A17" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="128" t="n">
+      <c r="B17" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="130" t="inlineStr">
         <is>
           <t>Joe Mitchell</t>
         </is>
@@ -10738,7 +10741,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E17" s="128" t="inlineStr">
+      <c r="E17" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10751,15 +10754,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="128" t="inlineStr">
+      <c r="A18" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B18" s="128" t="n">
+      <c r="B18" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="130" t="inlineStr">
         <is>
           <t>Marco Welch</t>
         </is>
@@ -10769,7 +10772,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="128" t="inlineStr">
+      <c r="E18" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10782,15 +10785,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="128" t="inlineStr">
+      <c r="A19" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B19" s="128" t="n">
+      <c r="B19" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="130" t="inlineStr">
         <is>
           <t>David Gutting</t>
         </is>
@@ -10800,7 +10803,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E19" s="128" t="inlineStr">
+      <c r="E19" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10813,15 +10816,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="128" t="inlineStr">
+      <c r="A20" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B20" s="128" t="n">
+      <c r="B20" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="130" t="inlineStr">
         <is>
           <t>Derrick Bloom</t>
         </is>
@@ -10831,7 +10834,7 @@
           <t>Vice Chairman, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E20" s="128" t="inlineStr">
+      <c r="E20" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10844,15 +10847,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="128" t="inlineStr">
+      <c r="A21" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B21" s="128" t="n">
+      <c r="B21" s="130" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="128" t="inlineStr">
+      <c r="C21" s="130" t="inlineStr">
         <is>
           <t>Brooks Colquitt</t>
         </is>
@@ -10862,7 +10865,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E21" s="128" t="inlineStr">
+      <c r="E21" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10875,15 +10878,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="128" t="inlineStr">
+      <c r="A22" s="130" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B22" s="128" t="n">
+      <c r="B22" s="130" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="128" t="inlineStr">
+      <c r="C22" s="130" t="inlineStr">
         <is>
           <t>Hunter Amos</t>
         </is>
@@ -10893,7 +10896,7 @@
           <t>Senior Managing Director, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E22" s="128" t="inlineStr">
+      <c r="E22" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10906,15 +10909,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="128" t="inlineStr">
+      <c r="A23" s="130" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B23" s="128" t="n">
+      <c r="B23" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="128" t="inlineStr">
+      <c r="C23" s="130" t="inlineStr">
         <is>
           <t>John Carr</t>
         </is>
@@ -10924,7 +10927,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="128" t="inlineStr">
+      <c r="E23" s="130" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -11828,15 +11831,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="128" t="inlineStr">
+      <c r="A3" s="130" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B3" s="128" t="n">
+      <c r="B3" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="130" t="inlineStr">
         <is>
           <t>Chris Phaneuf</t>
         </is>
@@ -11846,7 +11849,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E3" s="128" t="inlineStr">
+      <c r="E3" s="130" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11859,15 +11862,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="128" t="inlineStr">
+      <c r="A4" s="130" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="128" t="n">
+      <c r="B4" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="130" t="inlineStr">
         <is>
           <t>Adam Dunn</t>
         </is>
@@ -11877,7 +11880,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="128" t="inlineStr">
+      <c r="E4" s="130" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11890,15 +11893,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="128" t="inlineStr">
+      <c r="A5" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="128" t="n">
+      <c r="B5" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="130" t="inlineStr">
         <is>
           <t>Biria St. John</t>
         </is>
@@ -11908,7 +11911,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E5" s="128" t="inlineStr">
+      <c r="E5" s="130" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11921,15 +11924,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="128" t="inlineStr">
+      <c r="A6" s="130" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="128" t="n">
+      <c r="B6" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="130" t="inlineStr">
         <is>
           <t>Simon Butler</t>
         </is>
@@ -11939,7 +11942,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E6" s="128" t="inlineStr">
+      <c r="E6" s="130" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11952,15 +11955,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="128" t="inlineStr">
+      <c r="A7" s="130" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="128" t="n">
+      <c r="B7" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="130" t="inlineStr">
         <is>
           <t>David Goodhue</t>
         </is>
@@ -11970,7 +11973,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="128" t="inlineStr">
+      <c r="E7" s="130" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11983,15 +11986,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="128" t="inlineStr">
+      <c r="A8" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B8" s="128" t="n">
+      <c r="B8" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="130" t="inlineStr">
         <is>
           <t>John Flaherty</t>
         </is>
@@ -12001,7 +12004,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E8" s="128" t="inlineStr">
+      <c r="E8" s="130" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12014,15 +12017,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="128" t="inlineStr">
+      <c r="A9" s="130" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B9" s="128" t="n">
+      <c r="B9" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="130" t="inlineStr">
         <is>
           <t>Jon Bryant</t>
         </is>
@@ -12032,7 +12035,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="128" t="inlineStr">
+      <c r="E9" s="130" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12045,15 +12048,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="128" t="inlineStr">
+      <c r="A10" s="130" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B10" s="128" t="n">
+      <c r="B10" s="130" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="130" t="inlineStr">
         <is>
           <t>Victor Nolletti</t>
         </is>
@@ -12063,7 +12066,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="128" t="inlineStr">
+      <c r="E10" s="130" t="inlineStr">
         <is>
           <t>Boston/Northeast</t>
         </is>

--- a/Recruiting_Workbook.xlsx
+++ b/Recruiting_Workbook.xlsx
@@ -606,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -868,6 +868,9 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -1203,15 +1206,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="130" t="inlineStr">
+      <c r="A3" s="131" t="inlineStr">
         <is>
           <t>BRG Realty Ventures</t>
         </is>
       </c>
-      <c r="B3" s="130" t="n">
+      <c r="B3" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="inlineStr">
+      <c r="C3" s="131" t="inlineStr">
         <is>
           <t>Beau Beery</t>
         </is>
@@ -1221,7 +1224,7 @@
           <t>Founder</t>
         </is>
       </c>
-      <c r="E3" s="130" t="inlineStr">
+      <c r="E3" s="131" t="inlineStr">
         <is>
           <t>Gainesville</t>
         </is>
@@ -1234,15 +1237,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="130" t="n">
+      <c r="B4" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="130" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>Jaret Turkell</t>
         </is>
@@ -1252,7 +1255,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="130" t="inlineStr">
+      <c r="E4" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1265,15 +1268,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="130" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B5" s="130" t="n">
+      <c r="B5" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="130" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Jason Stanton</t>
         </is>
@@ -1283,7 +1286,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E5" s="130" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1296,15 +1299,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="130" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B6" s="130" t="n">
+      <c r="B6" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="130" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Matthew Mitchell</t>
         </is>
@@ -1314,7 +1317,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="130" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1327,15 +1330,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="130" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B7" s="130" t="n">
+      <c r="B7" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="130" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>Mitch Sinberg</t>
         </is>
@@ -1345,7 +1348,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="130" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -1358,15 +1361,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="130" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B8" s="130" t="n">
+      <c r="B8" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Denny St. Romain</t>
         </is>
@@ -1376,7 +1379,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1389,15 +1392,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="130" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B9" s="130" t="n">
+      <c r="B9" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="130" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t>Jubeen Vaghefi</t>
         </is>
@@ -1407,7 +1410,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -1420,15 +1423,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="130" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B10" s="130" t="n">
+      <c r="B10" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="130" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Tony Ballard</t>
         </is>
@@ -1438,7 +1441,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E10" s="130" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1451,15 +1454,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="130" t="inlineStr">
+      <c r="A11" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B11" s="130" t="n">
+      <c r="B11" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="130" t="inlineStr">
+      <c r="C11" s="131" t="inlineStr">
         <is>
           <t>Bradley Capas</t>
         </is>
@@ -1469,7 +1472,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E11" s="130" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1482,15 +1485,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="130" t="inlineStr">
+      <c r="A12" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B12" s="130" t="n">
+      <c r="B12" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="130" t="inlineStr">
+      <c r="C12" s="131" t="inlineStr">
         <is>
           <t>Casey Babb</t>
         </is>
@@ -1500,7 +1503,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E12" s="130" t="inlineStr">
+      <c r="E12" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1513,15 +1516,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="130" t="inlineStr">
+      <c r="A13" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B13" s="130" t="n">
+      <c r="B13" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="130" t="inlineStr">
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>Miles Tombrink</t>
         </is>
@@ -1531,7 +1534,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E13" s="130" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1544,15 +1547,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="130" t="inlineStr">
+      <c r="A14" s="131" t="inlineStr">
         <is>
           <t>Collison Captial</t>
         </is>
       </c>
-      <c r="B14" s="130" t="n">
+      <c r="B14" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="130" t="inlineStr">
+      <c r="C14" s="131" t="inlineStr">
         <is>
           <t>Carter Collison</t>
         </is>
@@ -1562,7 +1565,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E14" s="130" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -1575,21 +1578,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="130" t="inlineStr">
+      <c r="A15" s="131" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B15" s="130" t="n">
+      <c r="B15" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="130" t="inlineStr">
+      <c r="C15" s="131" t="inlineStr">
         <is>
           <t>Alexander Isaia</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="130" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1602,21 +1605,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="130" t="inlineStr">
+      <c r="A16" s="131" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B16" s="130" t="n">
+      <c r="B16" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="130" t="inlineStr">
+      <c r="C16" s="131" t="inlineStr">
         <is>
           <t>Jesse Spencer</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="130" t="inlineStr">
+      <c r="E16" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1629,15 +1632,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="130" t="inlineStr">
+      <c r="A17" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B17" s="130" t="n">
+      <c r="B17" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="130" t="inlineStr">
+      <c r="C17" s="131" t="inlineStr">
         <is>
           <t>Mike Donaldson</t>
         </is>
@@ -1647,7 +1650,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E17" s="130" t="inlineStr">
+      <c r="E17" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1660,15 +1663,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="130" t="inlineStr">
+      <c r="A18" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B18" s="130" t="n">
+      <c r="B18" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="130" t="inlineStr">
+      <c r="C18" s="131" t="inlineStr">
         <is>
           <t>Nick Meoli</t>
         </is>
@@ -1678,7 +1681,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E18" s="130" t="inlineStr">
+      <c r="E18" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1691,21 +1694,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="130" t="inlineStr">
+      <c r="A19" s="131" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B19" s="130" t="n">
+      <c r="B19" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="130" t="inlineStr">
+      <c r="C19" s="131" t="inlineStr">
         <is>
           <t>Carlos Fausto</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="130" t="inlineStr">
+      <c r="E19" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1714,21 +1717,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="130" t="inlineStr">
+      <c r="A20" s="131" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B20" s="130" t="n">
+      <c r="B20" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="130" t="inlineStr">
+      <c r="C20" s="131" t="inlineStr">
         <is>
           <t>Elior Levi</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="130" t="inlineStr">
+      <c r="E20" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1741,21 +1744,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="130" t="inlineStr">
+      <c r="A21" s="131" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B21" s="130" t="n">
+      <c r="B21" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="130" t="inlineStr">
+      <c r="C21" s="131" t="inlineStr">
         <is>
           <t>Mauricio Villasuso</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="130" t="inlineStr">
+      <c r="E21" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1764,15 +1767,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="130" t="inlineStr">
+      <c r="A22" s="131" t="inlineStr">
         <is>
           <t>Foundray</t>
         </is>
       </c>
-      <c r="B22" s="130" t="n">
+      <c r="B22" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="130" t="inlineStr">
+      <c r="C22" s="131" t="inlineStr">
         <is>
           <t>Andrew Green</t>
         </is>
@@ -1782,7 +1785,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E22" s="130" t="inlineStr">
+      <c r="E22" s="131" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -1795,15 +1798,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="130" t="inlineStr">
+      <c r="A23" s="131" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B23" s="130" t="n">
+      <c r="B23" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="130" t="inlineStr">
+      <c r="C23" s="131" t="inlineStr">
         <is>
           <t>Darron Kattan</t>
         </is>
@@ -1813,7 +1816,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="130" t="inlineStr">
+      <c r="E23" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1826,15 +1829,15 @@
       <c r="G23" s="129" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="130" t="inlineStr">
+      <c r="A24" s="131" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B24" s="130" t="n">
+      <c r="B24" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="130" t="inlineStr">
+      <c r="C24" s="131" t="inlineStr">
         <is>
           <t>Jonathan Barclay</t>
         </is>
@@ -1844,7 +1847,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E24" s="130" t="inlineStr">
+      <c r="E24" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1857,15 +1860,15 @@
       <c r="G24" s="129" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="130" t="inlineStr">
+      <c r="A25" s="131" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B25" s="130" t="n">
+      <c r="B25" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="130" t="inlineStr">
+      <c r="C25" s="131" t="inlineStr">
         <is>
           <t>Mark Savarese</t>
         </is>
@@ -1875,7 +1878,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E25" s="130" t="inlineStr">
+      <c r="E25" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1888,15 +1891,15 @@
       <c r="G25" s="129" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="130" t="inlineStr">
+      <c r="A26" s="131" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B26" s="130" t="n">
+      <c r="B26" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="130" t="inlineStr">
+      <c r="C26" s="131" t="inlineStr">
         <is>
           <t>Ryan Wold</t>
         </is>
@@ -1906,7 +1909,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E26" s="130" t="inlineStr">
+      <c r="E26" s="131" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1919,15 +1922,15 @@
       <c r="G26" s="129" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="130" t="inlineStr">
+      <c r="A27" s="131" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B27" s="130" t="n">
+      <c r="B27" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="130" t="inlineStr">
+      <c r="C27" s="131" t="inlineStr">
         <is>
           <t>Adam Podbelski</t>
         </is>
@@ -1937,7 +1940,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E27" s="130" t="inlineStr">
+      <c r="E27" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1950,15 +1953,15 @@
       <c r="G27" s="129" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="130" t="inlineStr">
+      <c r="A28" s="131" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B28" s="130" t="n">
+      <c r="B28" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="130" t="inlineStr">
+      <c r="C28" s="131" t="inlineStr">
         <is>
           <t>Alec Bashein</t>
         </is>
@@ -1968,7 +1971,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E28" s="130" t="inlineStr">
+      <c r="E28" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1981,15 +1984,15 @@
       <c r="G28" s="129" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="130" t="inlineStr">
+      <c r="A29" s="131" t="inlineStr">
         <is>
           <t>Hull Multifamily</t>
         </is>
       </c>
-      <c r="B29" s="130" t="n">
+      <c r="B29" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="130" t="inlineStr">
+      <c r="C29" s="131" t="inlineStr">
         <is>
           <t>Nick Hull</t>
         </is>
@@ -1999,7 +2002,7 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="E29" s="130" t="inlineStr">
+      <c r="E29" s="131" t="inlineStr">
         <is>
           <t>Naples</t>
         </is>
@@ -2012,15 +2015,15 @@
       <c r="G29" s="129" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="130" t="inlineStr">
+      <c r="A30" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B30" s="130" t="n">
+      <c r="B30" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="130" t="inlineStr">
+      <c r="C30" s="131" t="inlineStr">
         <is>
           <t>Cliff Taylor</t>
         </is>
@@ -2030,7 +2033,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E30" s="130" t="inlineStr">
+      <c r="E30" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2043,15 +2046,15 @@
       <c r="G30" s="129" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="130" t="inlineStr">
+      <c r="A31" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B31" s="130" t="n">
+      <c r="B31" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="130" t="inlineStr">
+      <c r="C31" s="131" t="inlineStr">
         <is>
           <t>Maurice Habif</t>
         </is>
@@ -2061,7 +2064,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E31" s="130" t="inlineStr">
+      <c r="E31" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2074,15 +2077,15 @@
       <c r="G31" s="129" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="130" t="inlineStr">
+      <c r="A32" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B32" s="130" t="n">
+      <c r="B32" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="130" t="inlineStr">
+      <c r="C32" s="131" t="inlineStr">
         <is>
           <t>Zach Nolan</t>
         </is>
@@ -2092,7 +2095,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E32" s="130" t="inlineStr">
+      <c r="E32" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2105,15 +2108,15 @@
       <c r="G32" s="129" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="130" t="inlineStr">
+      <c r="A33" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B33" s="130" t="n">
+      <c r="B33" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="130" t="inlineStr">
+      <c r="C33" s="131" t="inlineStr">
         <is>
           <t>Kyle Butler</t>
         </is>
@@ -2123,7 +2126,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E33" s="130" t="inlineStr">
+      <c r="E33" s="131" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2136,15 +2139,15 @@
       <c r="G33" s="129" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="130" t="inlineStr">
+      <c r="A34" s="131" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B34" s="130" t="n">
+      <c r="B34" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="130" t="inlineStr">
+      <c r="C34" s="131" t="inlineStr">
         <is>
           <t>Deme Mekras</t>
         </is>
@@ -2154,7 +2157,7 @@
           <t>Managing Partner, CEO</t>
         </is>
       </c>
-      <c r="E34" s="130" t="inlineStr">
+      <c r="E34" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2167,15 +2170,15 @@
       <c r="G34" s="129" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="130" t="inlineStr">
+      <c r="A35" s="131" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B35" s="130" t="n">
+      <c r="B35" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="130" t="inlineStr">
+      <c r="C35" s="131" t="inlineStr">
         <is>
           <t>Sam Mekras</t>
         </is>
@@ -2185,7 +2188,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E35" s="130" t="inlineStr">
+      <c r="E35" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2198,15 +2201,15 @@
       <c r="G35" s="129" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="130" t="inlineStr">
+      <c r="A36" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B36" s="130" t="n">
+      <c r="B36" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="130" t="inlineStr">
+      <c r="C36" s="131" t="inlineStr">
         <is>
           <t>Felipe Echarte</t>
         </is>
@@ -2216,7 +2219,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E36" s="130" t="inlineStr">
+      <c r="E36" s="131" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2229,15 +2232,15 @@
       <c r="G36" s="129" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="130" t="inlineStr">
+      <c r="A37" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B37" s="130" t="n">
+      <c r="B37" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="130" t="inlineStr">
+      <c r="C37" s="131" t="inlineStr">
         <is>
           <t>Joseph Thomas</t>
         </is>
@@ -2247,7 +2250,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E37" s="130" t="inlineStr">
+      <c r="E37" s="131" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2260,15 +2263,15 @@
       <c r="G37" s="129" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="130" t="inlineStr">
+      <c r="A38" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B38" s="130" t="n">
+      <c r="B38" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="130" t="inlineStr">
+      <c r="C38" s="131" t="inlineStr">
         <is>
           <t>Ray Turchi</t>
         </is>
@@ -2278,7 +2281,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E38" s="130" t="inlineStr">
+      <c r="E38" s="131" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2291,15 +2294,15 @@
       <c r="G38" s="129" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="130" t="inlineStr">
+      <c r="A39" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B39" s="130" t="n">
+      <c r="B39" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="130" t="inlineStr">
+      <c r="C39" s="131" t="inlineStr">
         <is>
           <t>Adam Marcuvitz</t>
         </is>
@@ -2309,7 +2312,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E39" s="130" t="inlineStr">
+      <c r="E39" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2322,15 +2325,15 @@
       <c r="G39" s="129" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="130" t="inlineStr">
+      <c r="A40" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B40" s="130" t="n">
+      <c r="B40" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="130" t="inlineStr">
+      <c r="C40" s="131" t="inlineStr">
         <is>
           <t>Erik Bjornson</t>
         </is>
@@ -2340,7 +2343,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E40" s="130" t="inlineStr">
+      <c r="E40" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2353,15 +2356,15 @@
       <c r="G40" s="129" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="130" t="inlineStr">
+      <c r="A41" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B41" s="130" t="n">
+      <c r="B41" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="130" t="inlineStr">
+      <c r="C41" s="131" t="inlineStr">
         <is>
           <t>Luke Wickham</t>
         </is>
@@ -2371,7 +2374,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E41" s="130" t="inlineStr">
+      <c r="E41" s="131" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2380,15 +2383,15 @@
       <c r="G41" s="129" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="130" t="inlineStr">
+      <c r="A42" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B42" s="130" t="n">
+      <c r="B42" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="130" t="inlineStr">
+      <c r="C42" s="131" t="inlineStr">
         <is>
           <t>Tyler Nilsson</t>
         </is>
@@ -2398,7 +2401,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E42" s="130" t="inlineStr">
+      <c r="E42" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2411,15 +2414,15 @@
       <c r="G42" s="129" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="130" t="inlineStr">
+      <c r="A43" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B43" s="130" t="n">
+      <c r="B43" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="130" t="inlineStr">
+      <c r="C43" s="131" t="inlineStr">
         <is>
           <t>Kyle Kundiger</t>
         </is>
@@ -2429,7 +2432,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E43" s="130" t="inlineStr">
+      <c r="E43" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2442,21 +2445,21 @@
       <c r="G43" s="129" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="130" t="inlineStr">
+      <c r="A44" s="131" t="inlineStr">
         <is>
           <t>Matthew</t>
         </is>
       </c>
-      <c r="B44" s="130" t="n">
+      <c r="B44" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="130" t="inlineStr">
+      <c r="C44" s="131" t="inlineStr">
         <is>
           <t>William Bruce</t>
         </is>
       </c>
       <c r="D44" s="129" t="inlineStr"/>
-      <c r="E44" s="130" t="inlineStr">
+      <c r="E44" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2469,15 +2472,15 @@
       <c r="G44" s="129" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="130" t="inlineStr">
+      <c r="A45" s="131" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B45" s="130" t="n">
+      <c r="B45" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="130" t="inlineStr">
+      <c r="C45" s="131" t="inlineStr">
         <is>
           <t>John Rutherford</t>
         </is>
@@ -2487,7 +2490,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E45" s="130" t="inlineStr">
+      <c r="E45" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2500,15 +2503,15 @@
       <c r="G45" s="129" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="130" t="inlineStr">
+      <c r="A46" s="131" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B46" s="130" t="n">
+      <c r="B46" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="130" t="inlineStr">
+      <c r="C46" s="131" t="inlineStr">
         <is>
           <t>Luke McCann</t>
         </is>
@@ -2518,7 +2521,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E46" s="130" t="inlineStr">
+      <c r="E46" s="131" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2531,15 +2534,15 @@
       <c r="G46" s="129" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="130" t="inlineStr">
+      <c r="A47" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B47" s="130" t="n">
+      <c r="B47" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="130" t="inlineStr">
+      <c r="C47" s="131" t="inlineStr">
         <is>
           <t>Avery Klann</t>
         </is>
@@ -2549,7 +2552,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E47" s="130" t="inlineStr">
+      <c r="E47" s="131" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2562,15 +2565,15 @@
       <c r="G47" s="129" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="130" t="inlineStr">
+      <c r="A48" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B48" s="130" t="n">
+      <c r="B48" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="130" t="inlineStr">
+      <c r="C48" s="131" t="inlineStr">
         <is>
           <t>Hampton Beebe</t>
         </is>
@@ -2580,7 +2583,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E48" s="130" t="inlineStr">
+      <c r="E48" s="131" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2593,15 +2596,15 @@
       <c r="G48" s="129" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="130" t="inlineStr">
+      <c r="A49" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B49" s="130" t="n">
+      <c r="B49" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C49" s="130" t="inlineStr">
+      <c r="C49" s="131" t="inlineStr">
         <is>
           <t>Patrick Dufour</t>
         </is>
@@ -2611,7 +2614,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E49" s="130" t="inlineStr">
+      <c r="E49" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2624,15 +2627,15 @@
       <c r="G49" s="129" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="130" t="inlineStr">
+      <c r="A50" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B50" s="130" t="n">
+      <c r="B50" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="130" t="inlineStr">
+      <c r="C50" s="131" t="inlineStr">
         <is>
           <t>Scott Ramey</t>
         </is>
@@ -2642,7 +2645,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E50" s="130" t="inlineStr">
+      <c r="E50" s="131" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2651,21 +2654,21 @@
       <c r="G50" s="129" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="130" t="inlineStr">
+      <c r="A51" s="131" t="inlineStr">
         <is>
           <t>One Commercial</t>
         </is>
       </c>
-      <c r="B51" s="130" t="n">
+      <c r="B51" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="130" t="inlineStr">
+      <c r="C51" s="131" t="inlineStr">
         <is>
           <t>Alexis Shapiro</t>
         </is>
       </c>
       <c r="D51" s="129" t="inlineStr"/>
-      <c r="E51" s="130" t="inlineStr">
+      <c r="E51" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2678,15 +2681,15 @@
       <c r="G51" s="129" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="130" t="inlineStr">
+      <c r="A52" s="131" t="inlineStr">
         <is>
           <t>ReMax</t>
         </is>
       </c>
-      <c r="B52" s="130" t="n">
+      <c r="B52" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="130" t="inlineStr">
+      <c r="C52" s="131" t="inlineStr">
         <is>
           <t>Roger Lohse</t>
         </is>
@@ -2696,7 +2699,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E52" s="130" t="inlineStr">
+      <c r="E52" s="131" t="inlineStr">
         <is>
           <t>Hollywood</t>
         </is>
@@ -2709,15 +2712,15 @@
       <c r="G52" s="129" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="130" t="inlineStr">
+      <c r="A53" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B53" s="130" t="n">
+      <c r="B53" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="130" t="inlineStr">
+      <c r="C53" s="131" t="inlineStr">
         <is>
           <t>Aaron Hargrove</t>
         </is>
@@ -2727,7 +2730,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E53" s="130" t="inlineStr">
+      <c r="E53" s="131" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2740,15 +2743,15 @@
       <c r="G53" s="129" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="130" t="inlineStr">
+      <c r="A54" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B54" s="130" t="n">
+      <c r="B54" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="130" t="inlineStr">
+      <c r="C54" s="131" t="inlineStr">
         <is>
           <t>Brian Moulder</t>
         </is>
@@ -2758,7 +2761,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E54" s="130" t="inlineStr">
+      <c r="E54" s="131" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -2771,15 +2774,15 @@
       <c r="G54" s="129" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="130" t="inlineStr">
+      <c r="A55" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B55" s="130" t="n">
+      <c r="B55" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C55" s="130" t="inlineStr">
+      <c r="C55" s="131" t="inlineStr">
         <is>
           <t>Chris Chadbourne</t>
         </is>
@@ -2789,7 +2792,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E55" s="130" t="inlineStr">
+      <c r="E55" s="131" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2802,15 +2805,15 @@
       <c r="G55" s="129" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="130" t="inlineStr">
+      <c r="A56" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B56" s="130" t="n">
+      <c r="B56" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="130" t="inlineStr">
+      <c r="C56" s="131" t="inlineStr">
         <is>
           <t>Still Hunter</t>
         </is>
@@ -2820,7 +2823,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E56" s="130" t="inlineStr">
+      <c r="E56" s="131" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -3821,15 +3824,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="130" t="inlineStr">
+      <c r="A3" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="130" t="n">
+      <c r="B3" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="inlineStr">
+      <c r="C3" s="131" t="inlineStr">
         <is>
           <t>John Phoenix</t>
         </is>
@@ -3839,7 +3842,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E3" s="130" t="inlineStr">
+      <c r="E3" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3852,15 +3855,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="130" t="n">
+      <c r="B4" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="130" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>Louis Smart</t>
         </is>
@@ -3870,7 +3873,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="130" t="inlineStr">
+      <c r="E4" s="131" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3883,15 +3886,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="130" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="130" t="n">
+      <c r="B5" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="130" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Richard Gore</t>
         </is>
@@ -3901,7 +3904,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="130" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3914,15 +3917,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="130" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="130" t="n">
+      <c r="B6" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="130" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Tyler Fish</t>
         </is>
@@ -3932,7 +3935,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="130" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3945,15 +3948,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="130" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="130" t="n">
+      <c r="B7" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="130" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>Kyle Chase</t>
         </is>
@@ -3963,7 +3966,7 @@
           <t>Executive Vice President</t>
         </is>
       </c>
-      <c r="E7" s="130" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3976,15 +3979,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="130" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="130" t="n">
+      <c r="B8" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Paul Marley</t>
         </is>
@@ -3994,7 +3997,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4007,15 +4010,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="130" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="130" t="n">
+      <c r="B9" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="130" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t>Jordan McCarley</t>
         </is>
@@ -4025,7 +4028,7 @@
           <t>Executive Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr"/>
+      <c r="E9" s="131" t="inlineStr"/>
       <c r="F9" s="129" t="inlineStr">
         <is>
           <t>https://multifamily.cushwake.com/Offices/Charlotte/Team</t>
@@ -4034,15 +4037,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="130" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="130" t="n">
+      <c r="B10" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="130" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Alex McDermott</t>
         </is>
@@ -4052,7 +4055,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="130" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4065,15 +4068,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="130" t="inlineStr">
+      <c r="A11" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="130" t="n">
+      <c r="B11" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="130" t="inlineStr">
+      <c r="C11" s="131" t="inlineStr">
         <is>
           <t>Austin Green</t>
         </is>
@@ -4083,7 +4086,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E11" s="130" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4096,15 +4099,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="130" t="inlineStr">
+      <c r="A12" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="130" t="n">
+      <c r="B12" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="130" t="inlineStr">
+      <c r="C12" s="131" t="inlineStr">
         <is>
           <t>William Martin</t>
         </is>
@@ -4114,7 +4117,7 @@
           <t>Capital Markets Associate</t>
         </is>
       </c>
-      <c r="E12" s="130" t="inlineStr">
+      <c r="E12" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4127,15 +4130,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="130" t="inlineStr">
+      <c r="A13" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="130" t="n">
+      <c r="B13" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="130" t="inlineStr">
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>Casey Sherman</t>
         </is>
@@ -4145,7 +4148,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="130" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4158,15 +4161,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="130" t="inlineStr">
+      <c r="A14" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="130" t="n">
+      <c r="B14" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="130" t="inlineStr">
+      <c r="C14" s="131" t="inlineStr">
         <is>
           <t>John Gavigan</t>
         </is>
@@ -4176,7 +4179,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E14" s="130" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4189,15 +4192,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="130" t="inlineStr">
+      <c r="A15" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="130" t="n">
+      <c r="B15" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="130" t="inlineStr">
+      <c r="C15" s="131" t="inlineStr">
         <is>
           <t>Dean Smith</t>
         </is>
@@ -4207,7 +4210,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E15" s="130" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4220,15 +4223,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="130" t="inlineStr">
+      <c r="A16" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B16" s="130" t="n">
+      <c r="B16" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="130" t="inlineStr">
+      <c r="C16" s="131" t="inlineStr">
         <is>
           <t>John Heimburger</t>
         </is>
@@ -4238,7 +4241,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E16" s="130" t="inlineStr">
+      <c r="E16" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4251,15 +4254,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="130" t="inlineStr">
+      <c r="A17" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B17" s="130" t="n">
+      <c r="B17" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="130" t="inlineStr">
+      <c r="C17" s="131" t="inlineStr">
         <is>
           <t>Sean Wood</t>
         </is>
@@ -4269,7 +4272,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E17" s="130" t="inlineStr">
+      <c r="E17" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4282,15 +4285,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="130" t="inlineStr">
+      <c r="A18" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="130" t="n">
+      <c r="B18" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="130" t="inlineStr">
+      <c r="C18" s="131" t="inlineStr">
         <is>
           <t>Alex Okulski</t>
         </is>
@@ -4300,7 +4303,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="130" t="inlineStr">
+      <c r="E18" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4313,15 +4316,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="130" t="inlineStr">
+      <c r="A19" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="130" t="n">
+      <c r="B19" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="130" t="inlineStr">
+      <c r="C19" s="131" t="inlineStr">
         <is>
           <t>Rob Coleman</t>
         </is>
@@ -4331,7 +4334,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E19" s="130" t="inlineStr">
+      <c r="E19" s="131" t="inlineStr">
         <is>
           <t>Raleigh</t>
         </is>
@@ -4344,15 +4347,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="130" t="inlineStr">
+      <c r="A20" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="130" t="n">
+      <c r="B20" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="130" t="inlineStr">
+      <c r="C20" s="131" t="inlineStr">
         <is>
           <t>Michael Saclarides</t>
         </is>
@@ -4362,7 +4365,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E20" s="130" t="inlineStr">
+      <c r="E20" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4375,15 +4378,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="130" t="inlineStr">
+      <c r="A21" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="130" t="n">
+      <c r="B21" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="130" t="inlineStr">
+      <c r="C21" s="131" t="inlineStr">
         <is>
           <t>Devin Bryan</t>
         </is>
@@ -4393,7 +4396,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E21" s="130" t="inlineStr">
+      <c r="E21" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4406,15 +4409,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="130" t="inlineStr">
+      <c r="A22" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B22" s="130" t="n">
+      <c r="B22" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="130" t="inlineStr">
+      <c r="C22" s="131" t="inlineStr">
         <is>
           <t>Fletcher Dunn</t>
         </is>
@@ -4424,7 +4427,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E22" s="130" t="inlineStr">
+      <c r="E22" s="131" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -5418,21 +5421,21 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="130" t="inlineStr">
+      <c r="A3" s="131" t="inlineStr">
         <is>
           <t>802 Property | Steadfast Group</t>
         </is>
       </c>
-      <c r="B3" s="130" t="n">
+      <c r="B3" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="inlineStr">
+      <c r="C3" s="131" t="inlineStr">
         <is>
           <t>Andy Hill</t>
         </is>
       </c>
       <c r="D3" s="129" t="inlineStr"/>
-      <c r="E3" s="130" t="inlineStr">
+      <c r="E3" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5441,21 +5444,21 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="130" t="n">
+      <c r="B4" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="130" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>Brett Carr</t>
         </is>
       </c>
       <c r="D4" s="129" t="inlineStr"/>
-      <c r="E4" s="130" t="inlineStr">
+      <c r="E4" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5464,21 +5467,21 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="130" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B5" s="130" t="n">
+      <c r="B5" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="130" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>David Dorris</t>
         </is>
       </c>
       <c r="D5" s="129" t="inlineStr"/>
-      <c r="E5" s="130" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5487,21 +5490,21 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="130" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B6" s="130" t="n">
+      <c r="B6" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="130" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Tyler Mayo</t>
         </is>
       </c>
       <c r="D6" s="129" t="inlineStr"/>
-      <c r="E6" s="130" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5510,21 +5513,21 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="130" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>MRG Realty Partners</t>
         </is>
       </c>
-      <c r="B7" s="130" t="n">
+      <c r="B7" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="130" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>Drew Lekowski</t>
         </is>
       </c>
       <c r="D7" s="129" t="inlineStr"/>
-      <c r="E7" s="130" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5533,21 +5536,21 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="130" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B8" s="130" t="n">
+      <c r="B8" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>David Stollenwerk</t>
         </is>
       </c>
       <c r="D8" s="129" t="inlineStr"/>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5556,21 +5559,21 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="130" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B9" s="130" t="n">
+      <c r="B9" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="130" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t>Patrick Cosgrove</t>
         </is>
       </c>
       <c r="D9" s="129" t="inlineStr"/>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5579,21 +5582,21 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="130" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B10" s="130" t="n">
+      <c r="B10" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="130" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Austin Fragoletti</t>
         </is>
       </c>
       <c r="D10" s="129" t="inlineStr"/>
-      <c r="E10" s="130" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5602,21 +5605,21 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="130" t="inlineStr">
+      <c r="A11" s="131" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B11" s="130" t="n">
+      <c r="B11" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="130" t="inlineStr">
+      <c r="C11" s="131" t="inlineStr">
         <is>
           <t>Sam Jackson</t>
         </is>
       </c>
       <c r="D11" s="129" t="inlineStr"/>
-      <c r="E11" s="130" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5625,21 +5628,21 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="130" t="inlineStr">
+      <c r="A12" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B12" s="130" t="n">
+      <c r="B12" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="130" t="inlineStr">
+      <c r="C12" s="131" t="inlineStr">
         <is>
           <t>Vince Lefler</t>
         </is>
       </c>
       <c r="D12" s="129" t="inlineStr"/>
-      <c r="E12" s="130" t="inlineStr">
+      <c r="E12" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5648,21 +5651,21 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="130" t="inlineStr">
+      <c r="A13" s="131" t="inlineStr">
         <is>
           <t>Redwood Collective Acquisitions, LLC | The Kirkland Company</t>
         </is>
       </c>
-      <c r="B13" s="130" t="n">
+      <c r="B13" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="130" t="inlineStr">
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>William Kirkland</t>
         </is>
       </c>
       <c r="D13" s="129" t="inlineStr"/>
-      <c r="E13" s="130" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5671,21 +5674,21 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="130" t="inlineStr">
+      <c r="A14" s="131" t="inlineStr">
         <is>
           <t>Stevens Group, LLC</t>
         </is>
       </c>
-      <c r="B14" s="130" t="n">
+      <c r="B14" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="130" t="inlineStr">
+      <c r="C14" s="131" t="inlineStr">
         <is>
           <t>Rusty Rust</t>
         </is>
       </c>
       <c r="D14" s="129" t="inlineStr"/>
-      <c r="E14" s="130" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>Antioch</t>
         </is>
@@ -5694,21 +5697,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="130" t="inlineStr">
+      <c r="A15" s="131" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B15" s="130" t="n">
+      <c r="B15" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="130" t="inlineStr">
+      <c r="C15" s="131" t="inlineStr">
         <is>
           <t>Miller Harris</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="130" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5717,21 +5720,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="130" t="inlineStr">
+      <c r="A16" s="131" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B16" s="130" t="n">
+      <c r="B16" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="130" t="inlineStr">
+      <c r="C16" s="131" t="inlineStr">
         <is>
           <t>Zac Wracher</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="130" t="inlineStr">
+      <c r="E16" s="131" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5740,21 +5743,21 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="130" t="inlineStr">
+      <c r="A17" s="131" t="inlineStr">
         <is>
           <t>The Parks Group Commercial</t>
         </is>
       </c>
-      <c r="B17" s="130" t="n">
+      <c r="B17" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="130" t="inlineStr">
+      <c r="C17" s="131" t="inlineStr">
         <is>
           <t>John Harney</t>
         </is>
       </c>
       <c r="D17" s="129" t="inlineStr"/>
-      <c r="E17" s="130" t="inlineStr">
+      <c r="E17" s="131" t="inlineStr">
         <is>
           <t>Murfreesboro</t>
         </is>
@@ -5763,21 +5766,21 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="130" t="inlineStr">
+      <c r="A18" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B18" s="130" t="n">
+      <c r="B18" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="130" t="inlineStr">
+      <c r="C18" s="131" t="inlineStr">
         <is>
           <t>Anne McGinn</t>
         </is>
       </c>
       <c r="D18" s="129" t="inlineStr"/>
-      <c r="E18" s="130" t="inlineStr">
+      <c r="E18" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5786,21 +5789,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="130" t="inlineStr">
+      <c r="A19" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="130" t="n">
+      <c r="B19" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="130" t="inlineStr">
+      <c r="C19" s="131" t="inlineStr">
         <is>
           <t>Brad Boston</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="130" t="inlineStr">
+      <c r="E19" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5809,21 +5812,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="130" t="inlineStr">
+      <c r="A20" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="130" t="n">
+      <c r="B20" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="130" t="inlineStr">
+      <c r="C20" s="131" t="inlineStr">
         <is>
           <t>Brett Kingman</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="130" t="inlineStr">
+      <c r="E20" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5832,21 +5835,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="130" t="inlineStr">
+      <c r="A21" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="130" t="n">
+      <c r="B21" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="130" t="inlineStr">
+      <c r="C21" s="131" t="inlineStr">
         <is>
           <t>Robbie O'Bryan</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="130" t="inlineStr">
+      <c r="E21" s="131" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -7616,15 +7619,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="130" t="inlineStr">
+      <c r="A3" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="130" t="n">
+      <c r="B3" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="inlineStr">
+      <c r="C3" s="131" t="inlineStr">
         <is>
           <t>Calvin Griffith</t>
         </is>
@@ -7634,7 +7637,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E3" s="130" t="inlineStr">
+      <c r="E3" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7647,15 +7650,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="130" t="n">
+      <c r="B4" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="130" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>Peyton Cox</t>
         </is>
@@ -7665,7 +7668,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E4" s="130" t="inlineStr">
+      <c r="E4" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7678,15 +7681,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="130" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="130" t="n">
+      <c r="B5" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="130" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Andrew Blackmon</t>
         </is>
@@ -7696,7 +7699,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E5" s="130" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Hampton Roads/Richmond</t>
         </is>
@@ -7709,15 +7712,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="130" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B6" s="130" t="n">
+      <c r="B6" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="130" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Garrison Gore</t>
         </is>
@@ -7727,7 +7730,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="130" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7740,15 +7743,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="130" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="130" t="n">
+      <c r="B7" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="130" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>Thomas Leachman</t>
         </is>
@@ -7758,7 +7761,7 @@
           <t>Senior Vice President, National Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="130" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7771,15 +7774,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="130" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="130" t="n">
+      <c r="B8" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -7789,7 +7792,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Richmond (Mid-Atlantic)</t>
         </is>
@@ -7802,15 +7805,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="130" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B9" s="130" t="n">
+      <c r="B9" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="130" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t>William Dickinson</t>
         </is>
@@ -7820,7 +7823,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7833,15 +7836,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="130" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="130" t="n">
+      <c r="B10" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="130" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Jorge Rosa / Paul C. Norman, Jr.</t>
         </is>
@@ -7851,7 +7854,7 @@
           <t>Executive Managing Directors</t>
         </is>
       </c>
-      <c r="E10" s="130" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>Based DC, covers Richmond</t>
         </is>
@@ -7860,15 +7863,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="130" t="inlineStr">
+      <c r="A11" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B11" s="130" t="n">
+      <c r="B11" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="130" t="inlineStr">
+      <c r="C11" s="131" t="inlineStr">
         <is>
           <t>Christopher Chadwick</t>
         </is>
@@ -7878,7 +7881,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E11" s="130" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7891,15 +7894,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="130" t="inlineStr">
+      <c r="A12" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B12" s="130" t="n">
+      <c r="B12" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="130" t="inlineStr">
+      <c r="C12" s="131" t="inlineStr">
         <is>
           <t>Justin Ferguson</t>
         </is>
@@ -7909,7 +7912,7 @@
           <t>Multifamily Specialist</t>
         </is>
       </c>
-      <c r="E12" s="130" t="inlineStr">
+      <c r="E12" s="131" t="inlineStr">
         <is>
           <t>Richmond (Southern VA office)</t>
         </is>
@@ -7922,15 +7925,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="130" t="inlineStr">
+      <c r="A13" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B13" s="130" t="n">
+      <c r="B13" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="130" t="inlineStr">
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>Martin Mooradian</t>
         </is>
@@ -7940,7 +7943,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="130" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7953,15 +7956,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="130" t="inlineStr">
+      <c r="A14" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B14" s="130" t="n">
+      <c r="B14" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="130" t="inlineStr">
+      <c r="C14" s="131" t="inlineStr">
         <is>
           <t>Mark Williford</t>
         </is>
@@ -7971,7 +7974,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E14" s="130" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7984,15 +7987,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="130" t="inlineStr">
+      <c r="A15" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="130" t="n">
+      <c r="B15" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="130" t="inlineStr">
+      <c r="C15" s="131" t="inlineStr">
         <is>
           <t>Will Bradley</t>
         </is>
@@ -8002,7 +8005,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="130" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -8875,15 +8878,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="130" t="inlineStr">
+      <c r="A3" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="130" t="n">
+      <c r="B3" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="inlineStr">
+      <c r="C3" s="131" t="inlineStr">
         <is>
           <t>Bob Dean (Robert G. Dean III)</t>
         </is>
@@ -8893,7 +8896,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E3" s="130" t="inlineStr">
+      <c r="E3" s="131" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA / Suburban MD</t>
         </is>
@@ -8906,15 +8909,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="130" t="n">
+      <c r="B4" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="130" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>John T. Sheridan, Jr.</t>
         </is>
@@ -8924,7 +8927,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="130" t="inlineStr">
+      <c r="E4" s="131" t="inlineStr">
         <is>
           <t>DC / VA / MD</t>
         </is>
@@ -8937,15 +8940,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="130" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="130" t="n">
+      <c r="B5" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="130" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Michael Muldowney</t>
         </is>
@@ -8955,7 +8958,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E5" s="130" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Washington, DC / MD suburbs</t>
         </is>
@@ -8968,15 +8971,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="130" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="130" t="n">
+      <c r="B6" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="130" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Bill Roohan</t>
         </is>
@@ -8986,7 +8989,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="130" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
@@ -8999,15 +9002,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="130" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="130" t="n">
+      <c r="B7" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="130" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>Chandler Pace</t>
         </is>
@@ -9017,7 +9020,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E7" s="130" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9030,15 +9033,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="130" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="130" t="n">
+      <c r="B8" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -9048,7 +9051,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA</t>
         </is>
@@ -9061,15 +9064,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="130" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="130" t="n">
+      <c r="B9" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="130" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t>Jorge Rosa</t>
         </is>
@@ -9079,7 +9082,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>Washington, DC / MD / VA</t>
         </is>
@@ -9092,15 +9095,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="130" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="130" t="n">
+      <c r="B10" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="130" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Paul C. Norman, Jr.</t>
         </is>
@@ -9110,7 +9113,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="130" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>Washington, DC metro</t>
         </is>
@@ -9123,15 +9126,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="130" t="inlineStr">
+      <c r="A11" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="130" t="n">
+      <c r="B11" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="130" t="inlineStr">
+      <c r="C11" s="131" t="inlineStr">
         <is>
           <t>Mac Hollensteiner</t>
         </is>
@@ -9141,7 +9144,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E11" s="130" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9154,15 +9157,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="130" t="inlineStr">
+      <c r="A12" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B12" s="130" t="n">
+      <c r="B12" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="130" t="inlineStr">
+      <c r="C12" s="131" t="inlineStr">
         <is>
           <t>Brooke Hanson</t>
         </is>
@@ -9172,7 +9175,7 @@
           <t>Capital Markets Group</t>
         </is>
       </c>
-      <c r="E12" s="130" t="inlineStr">
+      <c r="E12" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9185,15 +9188,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="130" t="inlineStr">
+      <c r="A13" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="130" t="n">
+      <c r="B13" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="130" t="inlineStr">
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>Andrew Weir</t>
         </is>
@@ -9203,7 +9206,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E13" s="130" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9216,15 +9219,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="130" t="inlineStr">
+      <c r="A14" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="130" t="n">
+      <c r="B14" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="130" t="inlineStr">
+      <c r="C14" s="131" t="inlineStr">
         <is>
           <t>Jamie Leachman</t>
         </is>
@@ -9234,7 +9237,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E14" s="130" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9247,15 +9250,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="130" t="inlineStr">
+      <c r="A15" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B15" s="130" t="n">
+      <c r="B15" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="130" t="inlineStr">
+      <c r="C15" s="131" t="inlineStr">
         <is>
           <t>Robert Jenkins</t>
         </is>
@@ -9265,7 +9268,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="130" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9278,15 +9281,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="130" t="inlineStr">
+      <c r="A16" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B16" s="130" t="n">
+      <c r="B16" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="130" t="inlineStr">
+      <c r="C16" s="131" t="inlineStr">
         <is>
           <t>Bret Thompson</t>
         </is>
@@ -9296,7 +9299,7 @@
           <t>Senior Director</t>
         </is>
       </c>
-      <c r="E16" s="130" t="inlineStr">
+      <c r="E16" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9309,15 +9312,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="130" t="inlineStr">
+      <c r="A17" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="130" t="n">
+      <c r="B17" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="130" t="inlineStr">
+      <c r="C17" s="131" t="inlineStr">
         <is>
           <t>Lorenzo M. Wooten, Jr., CCIM</t>
         </is>
@@ -9327,7 +9330,7 @@
           <t>Senior Director of Investments</t>
         </is>
       </c>
-      <c r="E17" s="130" t="inlineStr">
+      <c r="E17" s="131" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9340,15 +9343,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="130" t="inlineStr">
+      <c r="A18" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="130" t="n">
+      <c r="B18" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="130" t="inlineStr">
+      <c r="C18" s="131" t="inlineStr">
         <is>
           <t>Christine Espenshade</t>
         </is>
@@ -9358,7 +9361,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E18" s="130" t="inlineStr">
+      <c r="E18" s="131" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9371,15 +9374,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="130" t="inlineStr">
+      <c r="A19" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="130" t="n">
+      <c r="B19" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="130" t="inlineStr">
+      <c r="C19" s="131" t="inlineStr">
         <is>
           <t>Christopher Doerr</t>
         </is>
@@ -9389,7 +9392,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E19" s="130" t="inlineStr">
+      <c r="E19" s="131" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9402,15 +9405,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="130" t="inlineStr">
+      <c r="A20" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="130" t="n">
+      <c r="B20" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="130" t="inlineStr">
+      <c r="C20" s="131" t="inlineStr">
         <is>
           <t>William Harvey</t>
         </is>
@@ -9420,7 +9423,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E20" s="130" t="inlineStr">
+      <c r="E20" s="131" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -10289,15 +10292,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="130" t="inlineStr">
+      <c r="A3" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="130" t="n">
+      <c r="B3" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="inlineStr">
+      <c r="C3" s="131" t="inlineStr">
         <is>
           <t>Andrew Burns</t>
         </is>
@@ -10307,7 +10310,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E3" s="130" t="inlineStr">
+      <c r="E3" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10320,15 +10323,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="130" t="n">
+      <c r="B4" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="130" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>Jake Reid</t>
         </is>
@@ -10338,7 +10341,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="130" t="inlineStr">
+      <c r="E4" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10351,15 +10354,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="130" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="130" t="n">
+      <c r="B5" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="130" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Kurt McGarry</t>
         </is>
@@ -10369,7 +10372,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="130" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10382,15 +10385,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="130" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="130" t="n">
+      <c r="B6" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="130" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Shea Campbell</t>
         </is>
@@ -10400,7 +10403,7 @@
           <t>Vice Chairman / Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="130" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10413,15 +10416,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="130" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B7" s="130" t="n">
+      <c r="B7" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="130" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>Craig Hey</t>
         </is>
@@ -10431,7 +10434,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="130" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10444,15 +10447,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="130" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="130" t="n">
+      <c r="B8" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>Mike Kemether</t>
         </is>
@@ -10462,7 +10465,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10475,15 +10478,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="130" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="130" t="n">
+      <c r="B9" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="130" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t>Morgan Berg</t>
         </is>
@@ -10493,7 +10496,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10506,15 +10509,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="130" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="130" t="n">
+      <c r="B10" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="130" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Robert Stickel</t>
         </is>
@@ -10524,7 +10527,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E10" s="130" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10537,15 +10540,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="130" t="inlineStr">
+      <c r="A11" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B11" s="130" t="n">
+      <c r="B11" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="130" t="inlineStr">
+      <c r="C11" s="131" t="inlineStr">
         <is>
           <t>Peter Yorck</t>
         </is>
@@ -10555,7 +10558,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E11" s="130" t="inlineStr">
+      <c r="E11" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10568,15 +10571,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="130" t="inlineStr">
+      <c r="A12" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="130" t="n">
+      <c r="B12" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="130" t="inlineStr">
+      <c r="C12" s="131" t="inlineStr">
         <is>
           <t>Dennis Mitchell</t>
         </is>
@@ -10586,7 +10589,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E12" s="130" t="inlineStr">
+      <c r="E12" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10599,15 +10602,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="130" t="inlineStr">
+      <c r="A13" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="130" t="n">
+      <c r="B13" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="130" t="inlineStr">
+      <c r="C13" s="131" t="inlineStr">
         <is>
           <t>Michael Fox</t>
         </is>
@@ -10617,7 +10620,7 @@
           <t>Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E13" s="130" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10630,15 +10633,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="130" t="inlineStr">
+      <c r="A14" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="130" t="n">
+      <c r="B14" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="130" t="inlineStr">
+      <c r="C14" s="131" t="inlineStr">
         <is>
           <t>John Weber</t>
         </is>
@@ -10648,7 +10651,7 @@
           <t>Investment Sales (Multifamily)</t>
         </is>
       </c>
-      <c r="E14" s="130" t="inlineStr">
+      <c r="E14" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10661,15 +10664,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="130" t="inlineStr">
+      <c r="A15" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B15" s="130" t="n">
+      <c r="B15" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="130" t="inlineStr">
+      <c r="C15" s="131" t="inlineStr">
         <is>
           <t>Marc Irvin</t>
         </is>
@@ -10679,7 +10682,7 @@
           <t>Managing Director Investments</t>
         </is>
       </c>
-      <c r="E15" s="130" t="inlineStr">
+      <c r="E15" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10692,15 +10695,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="130" t="inlineStr">
+      <c r="A16" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B16" s="130" t="n">
+      <c r="B16" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="130" t="inlineStr">
+      <c r="C16" s="131" t="inlineStr">
         <is>
           <t>Harold Shepard</t>
         </is>
@@ -10710,7 +10713,7 @@
           <t>Investment Broker</t>
         </is>
       </c>
-      <c r="E16" s="130" t="inlineStr">
+      <c r="E16" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10723,15 +10726,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="130" t="inlineStr">
+      <c r="A17" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="130" t="n">
+      <c r="B17" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="130" t="inlineStr">
+      <c r="C17" s="131" t="inlineStr">
         <is>
           <t>Joe Mitchell</t>
         </is>
@@ -10741,7 +10744,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E17" s="130" t="inlineStr">
+      <c r="E17" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10754,15 +10757,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="130" t="inlineStr">
+      <c r="A18" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B18" s="130" t="n">
+      <c r="B18" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="130" t="inlineStr">
+      <c r="C18" s="131" t="inlineStr">
         <is>
           <t>Marco Welch</t>
         </is>
@@ -10772,7 +10775,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="130" t="inlineStr">
+      <c r="E18" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10785,15 +10788,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="130" t="inlineStr">
+      <c r="A19" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B19" s="130" t="n">
+      <c r="B19" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="130" t="inlineStr">
+      <c r="C19" s="131" t="inlineStr">
         <is>
           <t>David Gutting</t>
         </is>
@@ -10803,7 +10806,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E19" s="130" t="inlineStr">
+      <c r="E19" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10816,15 +10819,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="130" t="inlineStr">
+      <c r="A20" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B20" s="130" t="n">
+      <c r="B20" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="130" t="inlineStr">
+      <c r="C20" s="131" t="inlineStr">
         <is>
           <t>Derrick Bloom</t>
         </is>
@@ -10834,7 +10837,7 @@
           <t>Vice Chairman, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E20" s="130" t="inlineStr">
+      <c r="E20" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10847,15 +10850,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="130" t="inlineStr">
+      <c r="A21" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B21" s="130" t="n">
+      <c r="B21" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="130" t="inlineStr">
+      <c r="C21" s="131" t="inlineStr">
         <is>
           <t>Brooks Colquitt</t>
         </is>
@@ -10865,7 +10868,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E21" s="130" t="inlineStr">
+      <c r="E21" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10878,15 +10881,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="130" t="inlineStr">
+      <c r="A22" s="131" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B22" s="130" t="n">
+      <c r="B22" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="130" t="inlineStr">
+      <c r="C22" s="131" t="inlineStr">
         <is>
           <t>Hunter Amos</t>
         </is>
@@ -10896,7 +10899,7 @@
           <t>Senior Managing Director, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E22" s="130" t="inlineStr">
+      <c r="E22" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10909,15 +10912,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="130" t="inlineStr">
+      <c r="A23" s="131" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B23" s="130" t="n">
+      <c r="B23" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="130" t="inlineStr">
+      <c r="C23" s="131" t="inlineStr">
         <is>
           <t>John Carr</t>
         </is>
@@ -10927,7 +10930,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="130" t="inlineStr">
+      <c r="E23" s="131" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -11831,15 +11834,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="130" t="inlineStr">
+      <c r="A3" s="131" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B3" s="130" t="n">
+      <c r="B3" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="130" t="inlineStr">
+      <c r="C3" s="131" t="inlineStr">
         <is>
           <t>Chris Phaneuf</t>
         </is>
@@ -11849,7 +11852,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E3" s="130" t="inlineStr">
+      <c r="E3" s="131" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11862,15 +11865,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="130" t="inlineStr">
+      <c r="A4" s="131" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="130" t="n">
+      <c r="B4" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="130" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>Adam Dunn</t>
         </is>
@@ -11880,7 +11883,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="130" t="inlineStr">
+      <c r="E4" s="131" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11893,15 +11896,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="130" t="inlineStr">
+      <c r="A5" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="130" t="n">
+      <c r="B5" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="130" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Biria St. John</t>
         </is>
@@ -11911,7 +11914,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E5" s="130" t="inlineStr">
+      <c r="E5" s="131" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11924,15 +11927,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="130" t="inlineStr">
+      <c r="A6" s="131" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="130" t="n">
+      <c r="B6" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="130" t="inlineStr">
+      <c r="C6" s="131" t="inlineStr">
         <is>
           <t>Simon Butler</t>
         </is>
@@ -11942,7 +11945,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E6" s="130" t="inlineStr">
+      <c r="E6" s="131" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11955,15 +11958,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="130" t="inlineStr">
+      <c r="A7" s="131" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="130" t="n">
+      <c r="B7" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="130" t="inlineStr">
+      <c r="C7" s="131" t="inlineStr">
         <is>
           <t>David Goodhue</t>
         </is>
@@ -11973,7 +11976,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="130" t="inlineStr">
+      <c r="E7" s="131" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11986,15 +11989,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="130" t="inlineStr">
+      <c r="A8" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B8" s="130" t="n">
+      <c r="B8" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="130" t="inlineStr">
+      <c r="C8" s="131" t="inlineStr">
         <is>
           <t>John Flaherty</t>
         </is>
@@ -12004,7 +12007,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E8" s="130" t="inlineStr">
+      <c r="E8" s="131" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12017,15 +12020,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="130" t="inlineStr">
+      <c r="A9" s="131" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B9" s="130" t="n">
+      <c r="B9" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="130" t="inlineStr">
+      <c r="C9" s="131" t="inlineStr">
         <is>
           <t>Jon Bryant</t>
         </is>
@@ -12035,7 +12038,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="130" t="inlineStr">
+      <c r="E9" s="131" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12048,15 +12051,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="130" t="inlineStr">
+      <c r="A10" s="131" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B10" s="130" t="n">
+      <c r="B10" s="131" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="130" t="inlineStr">
+      <c r="C10" s="131" t="inlineStr">
         <is>
           <t>Victor Nolletti</t>
         </is>
@@ -12066,7 +12069,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="130" t="inlineStr">
+      <c r="E10" s="131" t="inlineStr">
         <is>
           <t>Boston/Northeast</t>
         </is>

--- a/Recruiting_Workbook.xlsx
+++ b/Recruiting_Workbook.xlsx
@@ -606,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -868,6 +868,9 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -1206,15 +1209,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>BRG Realty Ventures</t>
         </is>
       </c>
-      <c r="B3" s="131" t="n">
+      <c r="B3" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="131" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>Beau Beery</t>
         </is>
@@ -1224,7 +1227,7 @@
           <t>Founder</t>
         </is>
       </c>
-      <c r="E3" s="131" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>Gainesville</t>
         </is>
@@ -1237,15 +1240,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n">
+      <c r="B4" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>Jaret Turkell</t>
         </is>
@@ -1255,7 +1258,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="131" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1268,15 +1271,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="132" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B5" s="131" t="n">
+      <c r="B5" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="132" t="inlineStr">
         <is>
           <t>Jason Stanton</t>
         </is>
@@ -1286,7 +1289,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1299,15 +1302,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B6" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="132" t="inlineStr">
         <is>
           <t>Matthew Mitchell</t>
         </is>
@@ -1317,7 +1320,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1330,15 +1333,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="132" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B7" s="131" t="n">
+      <c r="B7" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>Mitch Sinberg</t>
         </is>
@@ -1348,7 +1351,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="132" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -1361,15 +1364,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B8" s="131" t="n">
+      <c r="B8" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="132" t="inlineStr">
         <is>
           <t>Denny St. Romain</t>
         </is>
@@ -1379,7 +1382,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="132" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1392,15 +1395,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B9" s="131" t="n">
+      <c r="B9" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="132" t="inlineStr">
         <is>
           <t>Jubeen Vaghefi</t>
         </is>
@@ -1410,7 +1413,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -1423,15 +1426,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B10" s="131" t="n">
+      <c r="B10" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="132" t="inlineStr">
         <is>
           <t>Tony Ballard</t>
         </is>
@@ -1441,7 +1444,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="132" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1454,15 +1457,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B11" s="131" t="n">
+      <c r="B11" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="131" t="inlineStr">
+      <c r="C11" s="132" t="inlineStr">
         <is>
           <t>Bradley Capas</t>
         </is>
@@ -1472,7 +1475,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="132" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1485,15 +1488,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B12" s="131" t="n">
+      <c r="B12" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="131" t="inlineStr">
+      <c r="C12" s="132" t="inlineStr">
         <is>
           <t>Casey Babb</t>
         </is>
@@ -1503,7 +1506,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E12" s="131" t="inlineStr">
+      <c r="E12" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1516,15 +1519,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B13" s="131" t="n">
+      <c r="B13" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C13" s="132" t="inlineStr">
         <is>
           <t>Miles Tombrink</t>
         </is>
@@ -1534,7 +1537,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1547,15 +1550,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="inlineStr">
+      <c r="A14" s="132" t="inlineStr">
         <is>
           <t>Collison Captial</t>
         </is>
       </c>
-      <c r="B14" s="131" t="n">
+      <c r="B14" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="131" t="inlineStr">
+      <c r="C14" s="132" t="inlineStr">
         <is>
           <t>Carter Collison</t>
         </is>
@@ -1565,7 +1568,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="132" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -1578,21 +1581,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="inlineStr">
+      <c r="A15" s="132" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B15" s="131" t="n">
+      <c r="B15" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="132" t="inlineStr">
         <is>
           <t>Alexander Isaia</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1605,21 +1608,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="131" t="inlineStr">
+      <c r="A16" s="132" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B16" s="131" t="n">
+      <c r="B16" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="131" t="inlineStr">
+      <c r="C16" s="132" t="inlineStr">
         <is>
           <t>Jesse Spencer</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="131" t="inlineStr">
+      <c r="E16" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1632,15 +1635,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="131" t="inlineStr">
+      <c r="A17" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B17" s="131" t="n">
+      <c r="B17" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="131" t="inlineStr">
+      <c r="C17" s="132" t="inlineStr">
         <is>
           <t>Mike Donaldson</t>
         </is>
@@ -1650,7 +1653,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E17" s="131" t="inlineStr">
+      <c r="E17" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1663,15 +1666,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="131" t="inlineStr">
+      <c r="A18" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B18" s="131" t="n">
+      <c r="B18" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="131" t="inlineStr">
+      <c r="C18" s="132" t="inlineStr">
         <is>
           <t>Nick Meoli</t>
         </is>
@@ -1681,7 +1684,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E18" s="131" t="inlineStr">
+      <c r="E18" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1694,21 +1697,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="131" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B19" s="131" t="n">
+      <c r="B19" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="131" t="inlineStr">
+      <c r="C19" s="132" t="inlineStr">
         <is>
           <t>Carlos Fausto</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="131" t="inlineStr">
+      <c r="E19" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1717,21 +1720,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="131" t="inlineStr">
+      <c r="A20" s="132" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B20" s="131" t="n">
+      <c r="B20" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="131" t="inlineStr">
+      <c r="C20" s="132" t="inlineStr">
         <is>
           <t>Elior Levi</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="131" t="inlineStr">
+      <c r="E20" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1744,21 +1747,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="131" t="inlineStr">
+      <c r="A21" s="132" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B21" s="131" t="n">
+      <c r="B21" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="131" t="inlineStr">
+      <c r="C21" s="132" t="inlineStr">
         <is>
           <t>Mauricio Villasuso</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="131" t="inlineStr">
+      <c r="E21" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1767,15 +1770,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="131" t="inlineStr">
+      <c r="A22" s="132" t="inlineStr">
         <is>
           <t>Foundray</t>
         </is>
       </c>
-      <c r="B22" s="131" t="n">
+      <c r="B22" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="131" t="inlineStr">
+      <c r="C22" s="132" t="inlineStr">
         <is>
           <t>Andrew Green</t>
         </is>
@@ -1785,7 +1788,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E22" s="131" t="inlineStr">
+      <c r="E22" s="132" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -1798,15 +1801,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="131" t="inlineStr">
+      <c r="A23" s="132" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B23" s="131" t="n">
+      <c r="B23" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="131" t="inlineStr">
+      <c r="C23" s="132" t="inlineStr">
         <is>
           <t>Darron Kattan</t>
         </is>
@@ -1816,7 +1819,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="131" t="inlineStr">
+      <c r="E23" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1829,15 +1832,15 @@
       <c r="G23" s="129" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="131" t="inlineStr">
+      <c r="A24" s="132" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B24" s="131" t="n">
+      <c r="B24" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="131" t="inlineStr">
+      <c r="C24" s="132" t="inlineStr">
         <is>
           <t>Jonathan Barclay</t>
         </is>
@@ -1847,7 +1850,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E24" s="131" t="inlineStr">
+      <c r="E24" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1860,15 +1863,15 @@
       <c r="G24" s="129" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="131" t="inlineStr">
+      <c r="A25" s="132" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B25" s="131" t="n">
+      <c r="B25" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="131" t="inlineStr">
+      <c r="C25" s="132" t="inlineStr">
         <is>
           <t>Mark Savarese</t>
         </is>
@@ -1878,7 +1881,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E25" s="131" t="inlineStr">
+      <c r="E25" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1891,15 +1894,15 @@
       <c r="G25" s="129" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="131" t="inlineStr">
+      <c r="A26" s="132" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B26" s="131" t="n">
+      <c r="B26" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="131" t="inlineStr">
+      <c r="C26" s="132" t="inlineStr">
         <is>
           <t>Ryan Wold</t>
         </is>
@@ -1909,7 +1912,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E26" s="131" t="inlineStr">
+      <c r="E26" s="132" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1922,15 +1925,15 @@
       <c r="G26" s="129" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="131" t="inlineStr">
+      <c r="A27" s="132" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B27" s="131" t="n">
+      <c r="B27" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="131" t="inlineStr">
+      <c r="C27" s="132" t="inlineStr">
         <is>
           <t>Adam Podbelski</t>
         </is>
@@ -1940,7 +1943,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E27" s="131" t="inlineStr">
+      <c r="E27" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1953,15 +1956,15 @@
       <c r="G27" s="129" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="131" t="inlineStr">
+      <c r="A28" s="132" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B28" s="131" t="n">
+      <c r="B28" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="131" t="inlineStr">
+      <c r="C28" s="132" t="inlineStr">
         <is>
           <t>Alec Bashein</t>
         </is>
@@ -1971,7 +1974,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E28" s="131" t="inlineStr">
+      <c r="E28" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1984,15 +1987,15 @@
       <c r="G28" s="129" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="131" t="inlineStr">
+      <c r="A29" s="132" t="inlineStr">
         <is>
           <t>Hull Multifamily</t>
         </is>
       </c>
-      <c r="B29" s="131" t="n">
+      <c r="B29" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="131" t="inlineStr">
+      <c r="C29" s="132" t="inlineStr">
         <is>
           <t>Nick Hull</t>
         </is>
@@ -2002,7 +2005,7 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="E29" s="131" t="inlineStr">
+      <c r="E29" s="132" t="inlineStr">
         <is>
           <t>Naples</t>
         </is>
@@ -2015,15 +2018,15 @@
       <c r="G29" s="129" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="131" t="inlineStr">
+      <c r="A30" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B30" s="131" t="n">
+      <c r="B30" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="131" t="inlineStr">
+      <c r="C30" s="132" t="inlineStr">
         <is>
           <t>Cliff Taylor</t>
         </is>
@@ -2033,7 +2036,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E30" s="131" t="inlineStr">
+      <c r="E30" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2046,15 +2049,15 @@
       <c r="G30" s="129" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="131" t="inlineStr">
+      <c r="A31" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B31" s="131" t="n">
+      <c r="B31" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="131" t="inlineStr">
+      <c r="C31" s="132" t="inlineStr">
         <is>
           <t>Maurice Habif</t>
         </is>
@@ -2064,7 +2067,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E31" s="131" t="inlineStr">
+      <c r="E31" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2077,15 +2080,15 @@
       <c r="G31" s="129" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="131" t="inlineStr">
+      <c r="A32" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B32" s="131" t="n">
+      <c r="B32" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="131" t="inlineStr">
+      <c r="C32" s="132" t="inlineStr">
         <is>
           <t>Zach Nolan</t>
         </is>
@@ -2095,7 +2098,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E32" s="131" t="inlineStr">
+      <c r="E32" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2108,15 +2111,15 @@
       <c r="G32" s="129" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="131" t="inlineStr">
+      <c r="A33" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B33" s="131" t="n">
+      <c r="B33" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="131" t="inlineStr">
+      <c r="C33" s="132" t="inlineStr">
         <is>
           <t>Kyle Butler</t>
         </is>
@@ -2126,7 +2129,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E33" s="131" t="inlineStr">
+      <c r="E33" s="132" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2139,15 +2142,15 @@
       <c r="G33" s="129" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="131" t="inlineStr">
+      <c r="A34" s="132" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B34" s="131" t="n">
+      <c r="B34" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="131" t="inlineStr">
+      <c r="C34" s="132" t="inlineStr">
         <is>
           <t>Deme Mekras</t>
         </is>
@@ -2157,7 +2160,7 @@
           <t>Managing Partner, CEO</t>
         </is>
       </c>
-      <c r="E34" s="131" t="inlineStr">
+      <c r="E34" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2170,15 +2173,15 @@
       <c r="G34" s="129" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="131" t="inlineStr">
+      <c r="A35" s="132" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B35" s="131" t="n">
+      <c r="B35" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="131" t="inlineStr">
+      <c r="C35" s="132" t="inlineStr">
         <is>
           <t>Sam Mekras</t>
         </is>
@@ -2188,7 +2191,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E35" s="131" t="inlineStr">
+      <c r="E35" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2201,15 +2204,15 @@
       <c r="G35" s="129" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="131" t="inlineStr">
+      <c r="A36" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B36" s="131" t="n">
+      <c r="B36" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="131" t="inlineStr">
+      <c r="C36" s="132" t="inlineStr">
         <is>
           <t>Felipe Echarte</t>
         </is>
@@ -2219,7 +2222,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E36" s="131" t="inlineStr">
+      <c r="E36" s="132" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2232,15 +2235,15 @@
       <c r="G36" s="129" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="131" t="inlineStr">
+      <c r="A37" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B37" s="131" t="n">
+      <c r="B37" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="131" t="inlineStr">
+      <c r="C37" s="132" t="inlineStr">
         <is>
           <t>Joseph Thomas</t>
         </is>
@@ -2250,7 +2253,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E37" s="131" t="inlineStr">
+      <c r="E37" s="132" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2263,15 +2266,15 @@
       <c r="G37" s="129" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="131" t="inlineStr">
+      <c r="A38" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B38" s="131" t="n">
+      <c r="B38" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="131" t="inlineStr">
+      <c r="C38" s="132" t="inlineStr">
         <is>
           <t>Ray Turchi</t>
         </is>
@@ -2281,7 +2284,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E38" s="131" t="inlineStr">
+      <c r="E38" s="132" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2294,15 +2297,15 @@
       <c r="G38" s="129" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="131" t="inlineStr">
+      <c r="A39" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B39" s="131" t="n">
+      <c r="B39" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="131" t="inlineStr">
+      <c r="C39" s="132" t="inlineStr">
         <is>
           <t>Adam Marcuvitz</t>
         </is>
@@ -2312,7 +2315,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E39" s="131" t="inlineStr">
+      <c r="E39" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2325,15 +2328,15 @@
       <c r="G39" s="129" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="131" t="inlineStr">
+      <c r="A40" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B40" s="131" t="n">
+      <c r="B40" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="131" t="inlineStr">
+      <c r="C40" s="132" t="inlineStr">
         <is>
           <t>Erik Bjornson</t>
         </is>
@@ -2343,7 +2346,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E40" s="131" t="inlineStr">
+      <c r="E40" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2356,15 +2359,15 @@
       <c r="G40" s="129" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="131" t="inlineStr">
+      <c r="A41" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B41" s="131" t="n">
+      <c r="B41" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="131" t="inlineStr">
+      <c r="C41" s="132" t="inlineStr">
         <is>
           <t>Luke Wickham</t>
         </is>
@@ -2374,7 +2377,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E41" s="131" t="inlineStr">
+      <c r="E41" s="132" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2383,15 +2386,15 @@
       <c r="G41" s="129" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="131" t="inlineStr">
+      <c r="A42" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B42" s="131" t="n">
+      <c r="B42" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="131" t="inlineStr">
+      <c r="C42" s="132" t="inlineStr">
         <is>
           <t>Tyler Nilsson</t>
         </is>
@@ -2401,7 +2404,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E42" s="131" t="inlineStr">
+      <c r="E42" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2414,15 +2417,15 @@
       <c r="G42" s="129" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="131" t="inlineStr">
+      <c r="A43" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B43" s="131" t="n">
+      <c r="B43" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="131" t="inlineStr">
+      <c r="C43" s="132" t="inlineStr">
         <is>
           <t>Kyle Kundiger</t>
         </is>
@@ -2432,7 +2435,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E43" s="131" t="inlineStr">
+      <c r="E43" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2445,21 +2448,21 @@
       <c r="G43" s="129" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="131" t="inlineStr">
+      <c r="A44" s="132" t="inlineStr">
         <is>
           <t>Matthew</t>
         </is>
       </c>
-      <c r="B44" s="131" t="n">
+      <c r="B44" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="131" t="inlineStr">
+      <c r="C44" s="132" t="inlineStr">
         <is>
           <t>William Bruce</t>
         </is>
       </c>
       <c r="D44" s="129" t="inlineStr"/>
-      <c r="E44" s="131" t="inlineStr">
+      <c r="E44" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2472,15 +2475,15 @@
       <c r="G44" s="129" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="131" t="inlineStr">
+      <c r="A45" s="132" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B45" s="131" t="n">
+      <c r="B45" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="131" t="inlineStr">
+      <c r="C45" s="132" t="inlineStr">
         <is>
           <t>John Rutherford</t>
         </is>
@@ -2490,7 +2493,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E45" s="131" t="inlineStr">
+      <c r="E45" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2503,15 +2506,15 @@
       <c r="G45" s="129" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="131" t="inlineStr">
+      <c r="A46" s="132" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B46" s="131" t="n">
+      <c r="B46" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="131" t="inlineStr">
+      <c r="C46" s="132" t="inlineStr">
         <is>
           <t>Luke McCann</t>
         </is>
@@ -2521,7 +2524,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E46" s="131" t="inlineStr">
+      <c r="E46" s="132" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2534,15 +2537,15 @@
       <c r="G46" s="129" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="131" t="inlineStr">
+      <c r="A47" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B47" s="131" t="n">
+      <c r="B47" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="131" t="inlineStr">
+      <c r="C47" s="132" t="inlineStr">
         <is>
           <t>Avery Klann</t>
         </is>
@@ -2552,7 +2555,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E47" s="131" t="inlineStr">
+      <c r="E47" s="132" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2565,15 +2568,15 @@
       <c r="G47" s="129" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="131" t="inlineStr">
+      <c r="A48" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B48" s="131" t="n">
+      <c r="B48" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="131" t="inlineStr">
+      <c r="C48" s="132" t="inlineStr">
         <is>
           <t>Hampton Beebe</t>
         </is>
@@ -2583,7 +2586,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E48" s="131" t="inlineStr">
+      <c r="E48" s="132" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2596,15 +2599,15 @@
       <c r="G48" s="129" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="131" t="inlineStr">
+      <c r="A49" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B49" s="131" t="n">
+      <c r="B49" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C49" s="131" t="inlineStr">
+      <c r="C49" s="132" t="inlineStr">
         <is>
           <t>Patrick Dufour</t>
         </is>
@@ -2614,7 +2617,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E49" s="131" t="inlineStr">
+      <c r="E49" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2627,15 +2630,15 @@
       <c r="G49" s="129" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="131" t="inlineStr">
+      <c r="A50" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B50" s="131" t="n">
+      <c r="B50" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="131" t="inlineStr">
+      <c r="C50" s="132" t="inlineStr">
         <is>
           <t>Scott Ramey</t>
         </is>
@@ -2645,7 +2648,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E50" s="131" t="inlineStr">
+      <c r="E50" s="132" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2654,21 +2657,21 @@
       <c r="G50" s="129" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="131" t="inlineStr">
+      <c r="A51" s="132" t="inlineStr">
         <is>
           <t>One Commercial</t>
         </is>
       </c>
-      <c r="B51" s="131" t="n">
+      <c r="B51" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="131" t="inlineStr">
+      <c r="C51" s="132" t="inlineStr">
         <is>
           <t>Alexis Shapiro</t>
         </is>
       </c>
       <c r="D51" s="129" t="inlineStr"/>
-      <c r="E51" s="131" t="inlineStr">
+      <c r="E51" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2681,15 +2684,15 @@
       <c r="G51" s="129" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="131" t="inlineStr">
+      <c r="A52" s="132" t="inlineStr">
         <is>
           <t>ReMax</t>
         </is>
       </c>
-      <c r="B52" s="131" t="n">
+      <c r="B52" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="131" t="inlineStr">
+      <c r="C52" s="132" t="inlineStr">
         <is>
           <t>Roger Lohse</t>
         </is>
@@ -2699,7 +2702,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E52" s="131" t="inlineStr">
+      <c r="E52" s="132" t="inlineStr">
         <is>
           <t>Hollywood</t>
         </is>
@@ -2712,15 +2715,15 @@
       <c r="G52" s="129" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="131" t="inlineStr">
+      <c r="A53" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B53" s="131" t="n">
+      <c r="B53" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="131" t="inlineStr">
+      <c r="C53" s="132" t="inlineStr">
         <is>
           <t>Aaron Hargrove</t>
         </is>
@@ -2730,7 +2733,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E53" s="131" t="inlineStr">
+      <c r="E53" s="132" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2743,15 +2746,15 @@
       <c r="G53" s="129" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="131" t="inlineStr">
+      <c r="A54" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B54" s="131" t="n">
+      <c r="B54" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="131" t="inlineStr">
+      <c r="C54" s="132" t="inlineStr">
         <is>
           <t>Brian Moulder</t>
         </is>
@@ -2761,7 +2764,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E54" s="131" t="inlineStr">
+      <c r="E54" s="132" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -2774,15 +2777,15 @@
       <c r="G54" s="129" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="131" t="inlineStr">
+      <c r="A55" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B55" s="131" t="n">
+      <c r="B55" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C55" s="131" t="inlineStr">
+      <c r="C55" s="132" t="inlineStr">
         <is>
           <t>Chris Chadbourne</t>
         </is>
@@ -2792,7 +2795,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E55" s="131" t="inlineStr">
+      <c r="E55" s="132" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2805,15 +2808,15 @@
       <c r="G55" s="129" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="131" t="inlineStr">
+      <c r="A56" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B56" s="131" t="n">
+      <c r="B56" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="131" t="inlineStr">
+      <c r="C56" s="132" t="inlineStr">
         <is>
           <t>Still Hunter</t>
         </is>
@@ -2823,7 +2826,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E56" s="131" t="inlineStr">
+      <c r="E56" s="132" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -3824,15 +3827,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="131" t="n">
+      <c r="B3" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="131" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>John Phoenix</t>
         </is>
@@ -3842,7 +3845,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E3" s="131" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3855,15 +3858,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n">
+      <c r="B4" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>Louis Smart</t>
         </is>
@@ -3873,7 +3876,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="131" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3886,15 +3889,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="131" t="n">
+      <c r="B5" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="132" t="inlineStr">
         <is>
           <t>Richard Gore</t>
         </is>
@@ -3904,7 +3907,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="132" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3917,15 +3920,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B6" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="132" t="inlineStr">
         <is>
           <t>Tyler Fish</t>
         </is>
@@ -3935,7 +3938,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3948,15 +3951,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="131" t="n">
+      <c r="B7" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>Kyle Chase</t>
         </is>
@@ -3966,7 +3969,7 @@
           <t>Executive Vice President</t>
         </is>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3979,15 +3982,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="131" t="n">
+      <c r="B8" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="132" t="inlineStr">
         <is>
           <t>Paul Marley</t>
         </is>
@@ -3997,7 +4000,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4010,15 +4013,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="131" t="n">
+      <c r="B9" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="132" t="inlineStr">
         <is>
           <t>Jordan McCarley</t>
         </is>
@@ -4028,7 +4031,7 @@
           <t>Executive Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="131" t="inlineStr"/>
+      <c r="E9" s="132" t="inlineStr"/>
       <c r="F9" s="129" t="inlineStr">
         <is>
           <t>https://multifamily.cushwake.com/Offices/Charlotte/Team</t>
@@ -4037,15 +4040,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="131" t="n">
+      <c r="B10" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="132" t="inlineStr">
         <is>
           <t>Alex McDermott</t>
         </is>
@@ -4055,7 +4058,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4068,15 +4071,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="131" t="n">
+      <c r="B11" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="131" t="inlineStr">
+      <c r="C11" s="132" t="inlineStr">
         <is>
           <t>Austin Green</t>
         </is>
@@ -4086,7 +4089,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4099,15 +4102,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="131" t="n">
+      <c r="B12" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="131" t="inlineStr">
+      <c r="C12" s="132" t="inlineStr">
         <is>
           <t>William Martin</t>
         </is>
@@ -4117,7 +4120,7 @@
           <t>Capital Markets Associate</t>
         </is>
       </c>
-      <c r="E12" s="131" t="inlineStr">
+      <c r="E12" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4130,15 +4133,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="131" t="n">
+      <c r="B13" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C13" s="132" t="inlineStr">
         <is>
           <t>Casey Sherman</t>
         </is>
@@ -4148,7 +4151,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4161,15 +4164,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="inlineStr">
+      <c r="A14" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="131" t="n">
+      <c r="B14" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="131" t="inlineStr">
+      <c r="C14" s="132" t="inlineStr">
         <is>
           <t>John Gavigan</t>
         </is>
@@ -4179,7 +4182,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4192,15 +4195,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="inlineStr">
+      <c r="A15" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="131" t="n">
+      <c r="B15" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="132" t="inlineStr">
         <is>
           <t>Dean Smith</t>
         </is>
@@ -4210,7 +4213,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4223,15 +4226,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="131" t="inlineStr">
+      <c r="A16" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B16" s="131" t="n">
+      <c r="B16" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="131" t="inlineStr">
+      <c r="C16" s="132" t="inlineStr">
         <is>
           <t>John Heimburger</t>
         </is>
@@ -4241,7 +4244,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E16" s="131" t="inlineStr">
+      <c r="E16" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4254,15 +4257,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="131" t="inlineStr">
+      <c r="A17" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B17" s="131" t="n">
+      <c r="B17" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="131" t="inlineStr">
+      <c r="C17" s="132" t="inlineStr">
         <is>
           <t>Sean Wood</t>
         </is>
@@ -4272,7 +4275,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E17" s="131" t="inlineStr">
+      <c r="E17" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4285,15 +4288,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="131" t="inlineStr">
+      <c r="A18" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="131" t="n">
+      <c r="B18" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="131" t="inlineStr">
+      <c r="C18" s="132" t="inlineStr">
         <is>
           <t>Alex Okulski</t>
         </is>
@@ -4303,7 +4306,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="131" t="inlineStr">
+      <c r="E18" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4316,15 +4319,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="131" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="131" t="n">
+      <c r="B19" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="131" t="inlineStr">
+      <c r="C19" s="132" t="inlineStr">
         <is>
           <t>Rob Coleman</t>
         </is>
@@ -4334,7 +4337,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E19" s="131" t="inlineStr">
+      <c r="E19" s="132" t="inlineStr">
         <is>
           <t>Raleigh</t>
         </is>
@@ -4347,15 +4350,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="131" t="inlineStr">
+      <c r="A20" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="131" t="n">
+      <c r="B20" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="131" t="inlineStr">
+      <c r="C20" s="132" t="inlineStr">
         <is>
           <t>Michael Saclarides</t>
         </is>
@@ -4365,7 +4368,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E20" s="131" t="inlineStr">
+      <c r="E20" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4378,15 +4381,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="131" t="inlineStr">
+      <c r="A21" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="131" t="n">
+      <c r="B21" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="131" t="inlineStr">
+      <c r="C21" s="132" t="inlineStr">
         <is>
           <t>Devin Bryan</t>
         </is>
@@ -4396,7 +4399,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E21" s="131" t="inlineStr">
+      <c r="E21" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4409,15 +4412,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="131" t="inlineStr">
+      <c r="A22" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B22" s="131" t="n">
+      <c r="B22" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="131" t="inlineStr">
+      <c r="C22" s="132" t="inlineStr">
         <is>
           <t>Fletcher Dunn</t>
         </is>
@@ -4427,7 +4430,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E22" s="131" t="inlineStr">
+      <c r="E22" s="132" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -5421,21 +5424,21 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>802 Property | Steadfast Group</t>
         </is>
       </c>
-      <c r="B3" s="131" t="n">
+      <c r="B3" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="131" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>Andy Hill</t>
         </is>
       </c>
       <c r="D3" s="129" t="inlineStr"/>
-      <c r="E3" s="131" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5444,21 +5447,21 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n">
+      <c r="B4" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>Brett Carr</t>
         </is>
       </c>
       <c r="D4" s="129" t="inlineStr"/>
-      <c r="E4" s="131" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5467,21 +5470,21 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="132" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B5" s="131" t="n">
+      <c r="B5" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="132" t="inlineStr">
         <is>
           <t>David Dorris</t>
         </is>
       </c>
       <c r="D5" s="129" t="inlineStr"/>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5490,21 +5493,21 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B6" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="132" t="inlineStr">
         <is>
           <t>Tyler Mayo</t>
         </is>
       </c>
       <c r="D6" s="129" t="inlineStr"/>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5513,21 +5516,21 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="132" t="inlineStr">
         <is>
           <t>MRG Realty Partners</t>
         </is>
       </c>
-      <c r="B7" s="131" t="n">
+      <c r="B7" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>Drew Lekowski</t>
         </is>
       </c>
       <c r="D7" s="129" t="inlineStr"/>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5536,21 +5539,21 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B8" s="131" t="n">
+      <c r="B8" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="132" t="inlineStr">
         <is>
           <t>David Stollenwerk</t>
         </is>
       </c>
       <c r="D8" s="129" t="inlineStr"/>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="132" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5559,21 +5562,21 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B9" s="131" t="n">
+      <c r="B9" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="132" t="inlineStr">
         <is>
           <t>Patrick Cosgrove</t>
         </is>
       </c>
       <c r="D9" s="129" t="inlineStr"/>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="132" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5582,21 +5585,21 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B10" s="131" t="n">
+      <c r="B10" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="132" t="inlineStr">
         <is>
           <t>Austin Fragoletti</t>
         </is>
       </c>
       <c r="D10" s="129" t="inlineStr"/>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5605,21 +5608,21 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="132" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B11" s="131" t="n">
+      <c r="B11" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="131" t="inlineStr">
+      <c r="C11" s="132" t="inlineStr">
         <is>
           <t>Sam Jackson</t>
         </is>
       </c>
       <c r="D11" s="129" t="inlineStr"/>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5628,21 +5631,21 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B12" s="131" t="n">
+      <c r="B12" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="131" t="inlineStr">
+      <c r="C12" s="132" t="inlineStr">
         <is>
           <t>Vince Lefler</t>
         </is>
       </c>
       <c r="D12" s="129" t="inlineStr"/>
-      <c r="E12" s="131" t="inlineStr">
+      <c r="E12" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5651,21 +5654,21 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="132" t="inlineStr">
         <is>
           <t>Redwood Collective Acquisitions, LLC | The Kirkland Company</t>
         </is>
       </c>
-      <c r="B13" s="131" t="n">
+      <c r="B13" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C13" s="132" t="inlineStr">
         <is>
           <t>William Kirkland</t>
         </is>
       </c>
       <c r="D13" s="129" t="inlineStr"/>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="132" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5674,21 +5677,21 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="inlineStr">
+      <c r="A14" s="132" t="inlineStr">
         <is>
           <t>Stevens Group, LLC</t>
         </is>
       </c>
-      <c r="B14" s="131" t="n">
+      <c r="B14" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="131" t="inlineStr">
+      <c r="C14" s="132" t="inlineStr">
         <is>
           <t>Rusty Rust</t>
         </is>
       </c>
       <c r="D14" s="129" t="inlineStr"/>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="132" t="inlineStr">
         <is>
           <t>Antioch</t>
         </is>
@@ -5697,21 +5700,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="inlineStr">
+      <c r="A15" s="132" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B15" s="131" t="n">
+      <c r="B15" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="132" t="inlineStr">
         <is>
           <t>Miller Harris</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="132" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5720,21 +5723,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="131" t="inlineStr">
+      <c r="A16" s="132" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B16" s="131" t="n">
+      <c r="B16" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="131" t="inlineStr">
+      <c r="C16" s="132" t="inlineStr">
         <is>
           <t>Zac Wracher</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="131" t="inlineStr">
+      <c r="E16" s="132" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5743,21 +5746,21 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="131" t="inlineStr">
+      <c r="A17" s="132" t="inlineStr">
         <is>
           <t>The Parks Group Commercial</t>
         </is>
       </c>
-      <c r="B17" s="131" t="n">
+      <c r="B17" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="131" t="inlineStr">
+      <c r="C17" s="132" t="inlineStr">
         <is>
           <t>John Harney</t>
         </is>
       </c>
       <c r="D17" s="129" t="inlineStr"/>
-      <c r="E17" s="131" t="inlineStr">
+      <c r="E17" s="132" t="inlineStr">
         <is>
           <t>Murfreesboro</t>
         </is>
@@ -5766,21 +5769,21 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="131" t="inlineStr">
+      <c r="A18" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B18" s="131" t="n">
+      <c r="B18" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="131" t="inlineStr">
+      <c r="C18" s="132" t="inlineStr">
         <is>
           <t>Anne McGinn</t>
         </is>
       </c>
       <c r="D18" s="129" t="inlineStr"/>
-      <c r="E18" s="131" t="inlineStr">
+      <c r="E18" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5789,21 +5792,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="131" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="131" t="n">
+      <c r="B19" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="131" t="inlineStr">
+      <c r="C19" s="132" t="inlineStr">
         <is>
           <t>Brad Boston</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="131" t="inlineStr">
+      <c r="E19" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5812,21 +5815,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="131" t="inlineStr">
+      <c r="A20" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="131" t="n">
+      <c r="B20" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="131" t="inlineStr">
+      <c r="C20" s="132" t="inlineStr">
         <is>
           <t>Brett Kingman</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="131" t="inlineStr">
+      <c r="E20" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5835,21 +5838,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="131" t="inlineStr">
+      <c r="A21" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="131" t="n">
+      <c r="B21" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="131" t="inlineStr">
+      <c r="C21" s="132" t="inlineStr">
         <is>
           <t>Robbie O'Bryan</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="131" t="inlineStr">
+      <c r="E21" s="132" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -7619,15 +7622,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="131" t="n">
+      <c r="B3" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="131" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>Calvin Griffith</t>
         </is>
@@ -7637,7 +7640,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E3" s="131" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7650,15 +7653,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n">
+      <c r="B4" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>Peyton Cox</t>
         </is>
@@ -7668,7 +7671,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E4" s="131" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7681,15 +7684,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="131" t="n">
+      <c r="B5" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="132" t="inlineStr">
         <is>
           <t>Andrew Blackmon</t>
         </is>
@@ -7699,7 +7702,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="132" t="inlineStr">
         <is>
           <t>Hampton Roads/Richmond</t>
         </is>
@@ -7712,15 +7715,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B6" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="132" t="inlineStr">
         <is>
           <t>Garrison Gore</t>
         </is>
@@ -7730,7 +7733,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7743,15 +7746,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="131" t="n">
+      <c r="B7" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>Thomas Leachman</t>
         </is>
@@ -7761,7 +7764,7 @@
           <t>Senior Vice President, National Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7774,15 +7777,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="131" t="n">
+      <c r="B8" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="132" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -7792,7 +7795,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="132" t="inlineStr">
         <is>
           <t>Richmond (Mid-Atlantic)</t>
         </is>
@@ -7805,15 +7808,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B9" s="131" t="n">
+      <c r="B9" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="132" t="inlineStr">
         <is>
           <t>William Dickinson</t>
         </is>
@@ -7823,7 +7826,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7836,15 +7839,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="131" t="n">
+      <c r="B10" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="132" t="inlineStr">
         <is>
           <t>Jorge Rosa / Paul C. Norman, Jr.</t>
         </is>
@@ -7854,7 +7857,7 @@
           <t>Executive Managing Directors</t>
         </is>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="132" t="inlineStr">
         <is>
           <t>Based DC, covers Richmond</t>
         </is>
@@ -7863,15 +7866,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B11" s="131" t="n">
+      <c r="B11" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="131" t="inlineStr">
+      <c r="C11" s="132" t="inlineStr">
         <is>
           <t>Christopher Chadwick</t>
         </is>
@@ -7881,7 +7884,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7894,15 +7897,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B12" s="131" t="n">
+      <c r="B12" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="131" t="inlineStr">
+      <c r="C12" s="132" t="inlineStr">
         <is>
           <t>Justin Ferguson</t>
         </is>
@@ -7912,7 +7915,7 @@
           <t>Multifamily Specialist</t>
         </is>
       </c>
-      <c r="E12" s="131" t="inlineStr">
+      <c r="E12" s="132" t="inlineStr">
         <is>
           <t>Richmond (Southern VA office)</t>
         </is>
@@ -7925,15 +7928,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B13" s="131" t="n">
+      <c r="B13" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C13" s="132" t="inlineStr">
         <is>
           <t>Martin Mooradian</t>
         </is>
@@ -7943,7 +7946,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7956,15 +7959,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="inlineStr">
+      <c r="A14" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B14" s="131" t="n">
+      <c r="B14" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="131" t="inlineStr">
+      <c r="C14" s="132" t="inlineStr">
         <is>
           <t>Mark Williford</t>
         </is>
@@ -7974,7 +7977,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7987,15 +7990,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="inlineStr">
+      <c r="A15" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="131" t="n">
+      <c r="B15" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="132" t="inlineStr">
         <is>
           <t>Will Bradley</t>
         </is>
@@ -8005,7 +8008,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="132" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -8878,15 +8881,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="131" t="n">
+      <c r="B3" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="131" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>Bob Dean (Robert G. Dean III)</t>
         </is>
@@ -8896,7 +8899,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E3" s="131" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA / Suburban MD</t>
         </is>
@@ -8909,15 +8912,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n">
+      <c r="B4" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>John T. Sheridan, Jr.</t>
         </is>
@@ -8927,7 +8930,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="131" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>DC / VA / MD</t>
         </is>
@@ -8940,15 +8943,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="131" t="n">
+      <c r="B5" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="132" t="inlineStr">
         <is>
           <t>Michael Muldowney</t>
         </is>
@@ -8958,7 +8961,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="132" t="inlineStr">
         <is>
           <t>Washington, DC / MD suburbs</t>
         </is>
@@ -8971,15 +8974,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B6" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="132" t="inlineStr">
         <is>
           <t>Bill Roohan</t>
         </is>
@@ -8989,7 +8992,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="132" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
@@ -9002,15 +9005,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="131" t="n">
+      <c r="B7" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>Chandler Pace</t>
         </is>
@@ -9020,7 +9023,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9033,15 +9036,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="131" t="n">
+      <c r="B8" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="132" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -9051,7 +9054,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="132" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA</t>
         </is>
@@ -9064,15 +9067,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="131" t="n">
+      <c r="B9" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="132" t="inlineStr">
         <is>
           <t>Jorge Rosa</t>
         </is>
@@ -9082,7 +9085,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="132" t="inlineStr">
         <is>
           <t>Washington, DC / MD / VA</t>
         </is>
@@ -9095,15 +9098,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="131" t="n">
+      <c r="B10" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="132" t="inlineStr">
         <is>
           <t>Paul C. Norman, Jr.</t>
         </is>
@@ -9113,7 +9116,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="132" t="inlineStr">
         <is>
           <t>Washington, DC metro</t>
         </is>
@@ -9126,15 +9129,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="131" t="n">
+      <c r="B11" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="131" t="inlineStr">
+      <c r="C11" s="132" t="inlineStr">
         <is>
           <t>Mac Hollensteiner</t>
         </is>
@@ -9144,7 +9147,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9157,15 +9160,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B12" s="131" t="n">
+      <c r="B12" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="131" t="inlineStr">
+      <c r="C12" s="132" t="inlineStr">
         <is>
           <t>Brooke Hanson</t>
         </is>
@@ -9175,7 +9178,7 @@
           <t>Capital Markets Group</t>
         </is>
       </c>
-      <c r="E12" s="131" t="inlineStr">
+      <c r="E12" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9188,15 +9191,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="131" t="n">
+      <c r="B13" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C13" s="132" t="inlineStr">
         <is>
           <t>Andrew Weir</t>
         </is>
@@ -9206,7 +9209,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9219,15 +9222,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="inlineStr">
+      <c r="A14" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="131" t="n">
+      <c r="B14" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="131" t="inlineStr">
+      <c r="C14" s="132" t="inlineStr">
         <is>
           <t>Jamie Leachman</t>
         </is>
@@ -9237,7 +9240,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9250,15 +9253,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="inlineStr">
+      <c r="A15" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B15" s="131" t="n">
+      <c r="B15" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="132" t="inlineStr">
         <is>
           <t>Robert Jenkins</t>
         </is>
@@ -9268,7 +9271,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9281,15 +9284,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="131" t="inlineStr">
+      <c r="A16" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B16" s="131" t="n">
+      <c r="B16" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="131" t="inlineStr">
+      <c r="C16" s="132" t="inlineStr">
         <is>
           <t>Bret Thompson</t>
         </is>
@@ -9299,7 +9302,7 @@
           <t>Senior Director</t>
         </is>
       </c>
-      <c r="E16" s="131" t="inlineStr">
+      <c r="E16" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9312,15 +9315,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="131" t="inlineStr">
+      <c r="A17" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="131" t="n">
+      <c r="B17" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="131" t="inlineStr">
+      <c r="C17" s="132" t="inlineStr">
         <is>
           <t>Lorenzo M. Wooten, Jr., CCIM</t>
         </is>
@@ -9330,7 +9333,7 @@
           <t>Senior Director of Investments</t>
         </is>
       </c>
-      <c r="E17" s="131" t="inlineStr">
+      <c r="E17" s="132" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9343,15 +9346,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="131" t="inlineStr">
+      <c r="A18" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="131" t="n">
+      <c r="B18" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="131" t="inlineStr">
+      <c r="C18" s="132" t="inlineStr">
         <is>
           <t>Christine Espenshade</t>
         </is>
@@ -9361,7 +9364,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E18" s="131" t="inlineStr">
+      <c r="E18" s="132" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9374,15 +9377,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="131" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="131" t="n">
+      <c r="B19" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="131" t="inlineStr">
+      <c r="C19" s="132" t="inlineStr">
         <is>
           <t>Christopher Doerr</t>
         </is>
@@ -9392,7 +9395,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E19" s="131" t="inlineStr">
+      <c r="E19" s="132" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9405,15 +9408,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="131" t="inlineStr">
+      <c r="A20" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="131" t="n">
+      <c r="B20" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="131" t="inlineStr">
+      <c r="C20" s="132" t="inlineStr">
         <is>
           <t>William Harvey</t>
         </is>
@@ -9423,7 +9426,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E20" s="131" t="inlineStr">
+      <c r="E20" s="132" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -10292,15 +10295,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="131" t="n">
+      <c r="B3" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="131" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>Andrew Burns</t>
         </is>
@@ -10310,7 +10313,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E3" s="131" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10323,15 +10326,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n">
+      <c r="B4" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>Jake Reid</t>
         </is>
@@ -10341,7 +10344,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="131" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10354,15 +10357,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="131" t="n">
+      <c r="B5" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="132" t="inlineStr">
         <is>
           <t>Kurt McGarry</t>
         </is>
@@ -10372,7 +10375,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10385,15 +10388,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B6" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="132" t="inlineStr">
         <is>
           <t>Shea Campbell</t>
         </is>
@@ -10403,7 +10406,7 @@
           <t>Vice Chairman / Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10416,15 +10419,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B7" s="131" t="n">
+      <c r="B7" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>Craig Hey</t>
         </is>
@@ -10434,7 +10437,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10447,15 +10450,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="131" t="n">
+      <c r="B8" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="132" t="inlineStr">
         <is>
           <t>Mike Kemether</t>
         </is>
@@ -10465,7 +10468,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10478,15 +10481,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="131" t="n">
+      <c r="B9" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="132" t="inlineStr">
         <is>
           <t>Morgan Berg</t>
         </is>
@@ -10496,7 +10499,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10509,15 +10512,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="131" t="n">
+      <c r="B10" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="132" t="inlineStr">
         <is>
           <t>Robert Stickel</t>
         </is>
@@ -10527,7 +10530,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10540,15 +10543,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="131" t="inlineStr">
+      <c r="A11" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B11" s="131" t="n">
+      <c r="B11" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="131" t="inlineStr">
+      <c r="C11" s="132" t="inlineStr">
         <is>
           <t>Peter Yorck</t>
         </is>
@@ -10558,7 +10561,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E11" s="131" t="inlineStr">
+      <c r="E11" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10571,15 +10574,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="131" t="inlineStr">
+      <c r="A12" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="131" t="n">
+      <c r="B12" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="131" t="inlineStr">
+      <c r="C12" s="132" t="inlineStr">
         <is>
           <t>Dennis Mitchell</t>
         </is>
@@ -10589,7 +10592,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E12" s="131" t="inlineStr">
+      <c r="E12" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10602,15 +10605,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="131" t="inlineStr">
+      <c r="A13" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="131" t="n">
+      <c r="B13" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="131" t="inlineStr">
+      <c r="C13" s="132" t="inlineStr">
         <is>
           <t>Michael Fox</t>
         </is>
@@ -10620,7 +10623,7 @@
           <t>Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E13" s="131" t="inlineStr">
+      <c r="E13" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10633,15 +10636,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="131" t="inlineStr">
+      <c r="A14" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="131" t="n">
+      <c r="B14" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="131" t="inlineStr">
+      <c r="C14" s="132" t="inlineStr">
         <is>
           <t>John Weber</t>
         </is>
@@ -10651,7 +10654,7 @@
           <t>Investment Sales (Multifamily)</t>
         </is>
       </c>
-      <c r="E14" s="131" t="inlineStr">
+      <c r="E14" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10664,15 +10667,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="131" t="inlineStr">
+      <c r="A15" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B15" s="131" t="n">
+      <c r="B15" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="131" t="inlineStr">
+      <c r="C15" s="132" t="inlineStr">
         <is>
           <t>Marc Irvin</t>
         </is>
@@ -10682,7 +10685,7 @@
           <t>Managing Director Investments</t>
         </is>
       </c>
-      <c r="E15" s="131" t="inlineStr">
+      <c r="E15" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10695,15 +10698,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="131" t="inlineStr">
+      <c r="A16" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B16" s="131" t="n">
+      <c r="B16" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="131" t="inlineStr">
+      <c r="C16" s="132" t="inlineStr">
         <is>
           <t>Harold Shepard</t>
         </is>
@@ -10713,7 +10716,7 @@
           <t>Investment Broker</t>
         </is>
       </c>
-      <c r="E16" s="131" t="inlineStr">
+      <c r="E16" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10726,15 +10729,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="131" t="inlineStr">
+      <c r="A17" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="131" t="n">
+      <c r="B17" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="131" t="inlineStr">
+      <c r="C17" s="132" t="inlineStr">
         <is>
           <t>Joe Mitchell</t>
         </is>
@@ -10744,7 +10747,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E17" s="131" t="inlineStr">
+      <c r="E17" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10757,15 +10760,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="131" t="inlineStr">
+      <c r="A18" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B18" s="131" t="n">
+      <c r="B18" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="131" t="inlineStr">
+      <c r="C18" s="132" t="inlineStr">
         <is>
           <t>Marco Welch</t>
         </is>
@@ -10775,7 +10778,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="131" t="inlineStr">
+      <c r="E18" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10788,15 +10791,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="131" t="inlineStr">
+      <c r="A19" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B19" s="131" t="n">
+      <c r="B19" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="131" t="inlineStr">
+      <c r="C19" s="132" t="inlineStr">
         <is>
           <t>David Gutting</t>
         </is>
@@ -10806,7 +10809,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E19" s="131" t="inlineStr">
+      <c r="E19" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10819,15 +10822,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="131" t="inlineStr">
+      <c r="A20" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B20" s="131" t="n">
+      <c r="B20" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="131" t="inlineStr">
+      <c r="C20" s="132" t="inlineStr">
         <is>
           <t>Derrick Bloom</t>
         </is>
@@ -10837,7 +10840,7 @@
           <t>Vice Chairman, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E20" s="131" t="inlineStr">
+      <c r="E20" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10850,15 +10853,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="131" t="inlineStr">
+      <c r="A21" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B21" s="131" t="n">
+      <c r="B21" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="131" t="inlineStr">
+      <c r="C21" s="132" t="inlineStr">
         <is>
           <t>Brooks Colquitt</t>
         </is>
@@ -10868,7 +10871,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E21" s="131" t="inlineStr">
+      <c r="E21" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10881,15 +10884,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="131" t="inlineStr">
+      <c r="A22" s="132" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B22" s="131" t="n">
+      <c r="B22" s="132" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="131" t="inlineStr">
+      <c r="C22" s="132" t="inlineStr">
         <is>
           <t>Hunter Amos</t>
         </is>
@@ -10899,7 +10902,7 @@
           <t>Senior Managing Director, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E22" s="131" t="inlineStr">
+      <c r="E22" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10912,15 +10915,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="131" t="inlineStr">
+      <c r="A23" s="132" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B23" s="131" t="n">
+      <c r="B23" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="131" t="inlineStr">
+      <c r="C23" s="132" t="inlineStr">
         <is>
           <t>John Carr</t>
         </is>
@@ -10930,7 +10933,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="131" t="inlineStr">
+      <c r="E23" s="132" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -11834,15 +11837,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="131" t="inlineStr">
+      <c r="A3" s="132" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B3" s="131" t="n">
+      <c r="B3" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="131" t="inlineStr">
+      <c r="C3" s="132" t="inlineStr">
         <is>
           <t>Chris Phaneuf</t>
         </is>
@@ -11852,7 +11855,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E3" s="131" t="inlineStr">
+      <c r="E3" s="132" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11865,15 +11868,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="131" t="inlineStr">
+      <c r="A4" s="132" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="131" t="n">
+      <c r="B4" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="131" t="inlineStr">
+      <c r="C4" s="132" t="inlineStr">
         <is>
           <t>Adam Dunn</t>
         </is>
@@ -11883,7 +11886,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="131" t="inlineStr">
+      <c r="E4" s="132" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11896,15 +11899,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="131" t="inlineStr">
+      <c r="A5" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="131" t="n">
+      <c r="B5" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="131" t="inlineStr">
+      <c r="C5" s="132" t="inlineStr">
         <is>
           <t>Biria St. John</t>
         </is>
@@ -11914,7 +11917,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E5" s="131" t="inlineStr">
+      <c r="E5" s="132" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11927,15 +11930,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="131" t="inlineStr">
+      <c r="A6" s="132" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="131" t="n">
+      <c r="B6" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="131" t="inlineStr">
+      <c r="C6" s="132" t="inlineStr">
         <is>
           <t>Simon Butler</t>
         </is>
@@ -11945,7 +11948,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E6" s="131" t="inlineStr">
+      <c r="E6" s="132" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11958,15 +11961,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="131" t="inlineStr">
+      <c r="A7" s="132" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="131" t="n">
+      <c r="B7" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="131" t="inlineStr">
+      <c r="C7" s="132" t="inlineStr">
         <is>
           <t>David Goodhue</t>
         </is>
@@ -11976,7 +11979,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="131" t="inlineStr">
+      <c r="E7" s="132" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11989,15 +11992,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="131" t="inlineStr">
+      <c r="A8" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B8" s="131" t="n">
+      <c r="B8" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="131" t="inlineStr">
+      <c r="C8" s="132" t="inlineStr">
         <is>
           <t>John Flaherty</t>
         </is>
@@ -12007,7 +12010,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E8" s="131" t="inlineStr">
+      <c r="E8" s="132" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12020,15 +12023,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="131" t="inlineStr">
+      <c r="A9" s="132" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B9" s="131" t="n">
+      <c r="B9" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="131" t="inlineStr">
+      <c r="C9" s="132" t="inlineStr">
         <is>
           <t>Jon Bryant</t>
         </is>
@@ -12038,7 +12041,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="131" t="inlineStr">
+      <c r="E9" s="132" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12051,15 +12054,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="131" t="inlineStr">
+      <c r="A10" s="132" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B10" s="131" t="n">
+      <c r="B10" s="132" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="131" t="inlineStr">
+      <c r="C10" s="132" t="inlineStr">
         <is>
           <t>Victor Nolletti</t>
         </is>
@@ -12069,7 +12072,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="131" t="inlineStr">
+      <c r="E10" s="132" t="inlineStr">
         <is>
           <t>Boston/Northeast</t>
         </is>

--- a/Recruiting_Workbook.xlsx
+++ b/Recruiting_Workbook.xlsx
@@ -606,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -868,6 +868,9 @@
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
@@ -1209,15 +1212,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132" t="inlineStr">
+      <c r="A3" s="133" t="inlineStr">
         <is>
           <t>BRG Realty Ventures</t>
         </is>
       </c>
-      <c r="B3" s="132" t="n">
+      <c r="B3" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="133" t="inlineStr">
         <is>
           <t>Beau Beery</t>
         </is>
@@ -1227,7 +1230,7 @@
           <t>Founder</t>
         </is>
       </c>
-      <c r="E3" s="132" t="inlineStr">
+      <c r="E3" s="133" t="inlineStr">
         <is>
           <t>Gainesville</t>
         </is>
@@ -1240,15 +1243,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="133" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="132" t="n">
+      <c r="B4" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="132" t="inlineStr">
+      <c r="C4" s="133" t="inlineStr">
         <is>
           <t>Jaret Turkell</t>
         </is>
@@ -1258,7 +1261,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="132" t="inlineStr">
+      <c r="E4" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1271,15 +1274,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="132" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B5" s="132" t="n">
+      <c r="B5" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="132" t="inlineStr">
+      <c r="C5" s="133" t="inlineStr">
         <is>
           <t>Jason Stanton</t>
         </is>
@@ -1289,7 +1292,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E5" s="132" t="inlineStr">
+      <c r="E5" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1302,15 +1305,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="132" t="inlineStr">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B6" s="132" t="n">
+      <c r="B6" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="132" t="inlineStr">
+      <c r="C6" s="133" t="inlineStr">
         <is>
           <t>Matthew Mitchell</t>
         </is>
@@ -1320,7 +1323,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="132" t="inlineStr">
+      <c r="E6" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1333,15 +1336,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="133" t="inlineStr">
         <is>
           <t>Mitch Sinberg</t>
         </is>
@@ -1351,7 +1354,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="133" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -1364,15 +1367,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="132" t="inlineStr">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="132" t="inlineStr">
+      <c r="C8" s="133" t="inlineStr">
         <is>
           <t>Denny St. Romain</t>
         </is>
@@ -1382,7 +1385,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="132" t="inlineStr">
+      <c r="E8" s="133" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1395,15 +1398,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="132" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B9" s="132" t="n">
+      <c r="B9" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="132" t="inlineStr">
+      <c r="C9" s="133" t="inlineStr">
         <is>
           <t>Jubeen Vaghefi</t>
         </is>
@@ -1413,7 +1416,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="132" t="inlineStr">
+      <c r="E9" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -1426,15 +1429,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="132" t="inlineStr">
+      <c r="A10" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B10" s="132" t="n">
+      <c r="B10" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="132" t="inlineStr">
+      <c r="C10" s="133" t="inlineStr">
         <is>
           <t>Tony Ballard</t>
         </is>
@@ -1444,7 +1447,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E10" s="132" t="inlineStr">
+      <c r="E10" s="133" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1457,15 +1460,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="132" t="inlineStr">
+      <c r="A11" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B11" s="132" t="n">
+      <c r="B11" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="132" t="inlineStr">
+      <c r="C11" s="133" t="inlineStr">
         <is>
           <t>Bradley Capas</t>
         </is>
@@ -1475,7 +1478,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E11" s="132" t="inlineStr">
+      <c r="E11" s="133" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1488,15 +1491,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="132" t="inlineStr">
+      <c r="A12" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B12" s="132" t="n">
+      <c r="B12" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="132" t="inlineStr">
+      <c r="C12" s="133" t="inlineStr">
         <is>
           <t>Casey Babb</t>
         </is>
@@ -1506,7 +1509,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E12" s="132" t="inlineStr">
+      <c r="E12" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1519,15 +1522,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="132" t="inlineStr">
+      <c r="A13" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B13" s="132" t="n">
+      <c r="B13" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="132" t="inlineStr">
+      <c r="C13" s="133" t="inlineStr">
         <is>
           <t>Miles Tombrink</t>
         </is>
@@ -1537,7 +1540,7 @@
           <t>Executive VP</t>
         </is>
       </c>
-      <c r="E13" s="132" t="inlineStr">
+      <c r="E13" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1550,15 +1553,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="132" t="inlineStr">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>Collison Captial</t>
         </is>
       </c>
-      <c r="B14" s="132" t="n">
+      <c r="B14" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="132" t="inlineStr">
+      <c r="C14" s="133" t="inlineStr">
         <is>
           <t>Carter Collison</t>
         </is>
@@ -1568,7 +1571,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E14" s="132" t="inlineStr">
+      <c r="E14" s="133" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -1581,21 +1584,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="132" t="inlineStr">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B15" s="132" t="n">
+      <c r="B15" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="132" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>Alexander Isaia</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="132" t="inlineStr">
+      <c r="E15" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1608,21 +1611,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="132" t="inlineStr">
+      <c r="A16" s="133" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B16" s="132" t="n">
+      <c r="B16" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="132" t="inlineStr">
+      <c r="C16" s="133" t="inlineStr">
         <is>
           <t>Jesse Spencer</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="132" t="inlineStr">
+      <c r="E16" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1635,15 +1638,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="132" t="inlineStr">
+      <c r="A17" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B17" s="132" t="n">
+      <c r="B17" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="132" t="inlineStr">
+      <c r="C17" s="133" t="inlineStr">
         <is>
           <t>Mike Donaldson</t>
         </is>
@@ -1653,7 +1656,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E17" s="132" t="inlineStr">
+      <c r="E17" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1666,15 +1669,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="132" t="inlineStr">
+      <c r="A18" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B18" s="132" t="n">
+      <c r="B18" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="132" t="inlineStr">
+      <c r="C18" s="133" t="inlineStr">
         <is>
           <t>Nick Meoli</t>
         </is>
@@ -1684,7 +1687,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E18" s="132" t="inlineStr">
+      <c r="E18" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1697,21 +1700,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="132" t="inlineStr">
+      <c r="A19" s="133" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B19" s="132" t="n">
+      <c r="B19" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="132" t="inlineStr">
+      <c r="C19" s="133" t="inlineStr">
         <is>
           <t>Carlos Fausto</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="132" t="inlineStr">
+      <c r="E19" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1720,21 +1723,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="132" t="inlineStr">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B20" s="132" t="n">
+      <c r="B20" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="132" t="inlineStr">
+      <c r="C20" s="133" t="inlineStr">
         <is>
           <t>Elior Levi</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="132" t="inlineStr">
+      <c r="E20" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1747,21 +1750,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="132" t="inlineStr">
+      <c r="A21" s="133" t="inlineStr">
         <is>
           <t>Fausto Commercial</t>
         </is>
       </c>
-      <c r="B21" s="132" t="n">
+      <c r="B21" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="132" t="inlineStr">
+      <c r="C21" s="133" t="inlineStr">
         <is>
           <t>Mauricio Villasuso</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="132" t="inlineStr">
+      <c r="E21" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1770,15 +1773,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="132" t="inlineStr">
+      <c r="A22" s="133" t="inlineStr">
         <is>
           <t>Foundray</t>
         </is>
       </c>
-      <c r="B22" s="132" t="n">
+      <c r="B22" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="132" t="inlineStr">
+      <c r="C22" s="133" t="inlineStr">
         <is>
           <t>Andrew Green</t>
         </is>
@@ -1788,7 +1791,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E22" s="132" t="inlineStr">
+      <c r="E22" s="133" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -1801,15 +1804,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="132" t="inlineStr">
+      <c r="A23" s="133" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B23" s="132" t="n">
+      <c r="B23" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="132" t="inlineStr">
+      <c r="C23" s="133" t="inlineStr">
         <is>
           <t>Darron Kattan</t>
         </is>
@@ -1819,7 +1822,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="132" t="inlineStr">
+      <c r="E23" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1832,15 +1835,15 @@
       <c r="G23" s="129" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="132" t="inlineStr">
+      <c r="A24" s="133" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B24" s="132" t="n">
+      <c r="B24" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="132" t="inlineStr">
+      <c r="C24" s="133" t="inlineStr">
         <is>
           <t>Jonathan Barclay</t>
         </is>
@@ -1850,7 +1853,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E24" s="132" t="inlineStr">
+      <c r="E24" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1863,15 +1866,15 @@
       <c r="G24" s="129" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="132" t="inlineStr">
+      <c r="A25" s="133" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B25" s="132" t="n">
+      <c r="B25" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="132" t="inlineStr">
+      <c r="C25" s="133" t="inlineStr">
         <is>
           <t>Mark Savarese</t>
         </is>
@@ -1881,7 +1884,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E25" s="132" t="inlineStr">
+      <c r="E25" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1894,15 +1897,15 @@
       <c r="G25" s="129" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="132" t="inlineStr">
+      <c r="A26" s="133" t="inlineStr">
         <is>
           <t>Franklin Street</t>
         </is>
       </c>
-      <c r="B26" s="132" t="n">
+      <c r="B26" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="132" t="inlineStr">
+      <c r="C26" s="133" t="inlineStr">
         <is>
           <t>Ryan Wold</t>
         </is>
@@ -1912,7 +1915,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E26" s="132" t="inlineStr">
+      <c r="E26" s="133" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -1925,15 +1928,15 @@
       <c r="G26" s="129" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="132" t="inlineStr">
+      <c r="A27" s="133" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B27" s="132" t="n">
+      <c r="B27" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C27" s="132" t="inlineStr">
+      <c r="C27" s="133" t="inlineStr">
         <is>
           <t>Adam Podbelski</t>
         </is>
@@ -1943,7 +1946,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E27" s="132" t="inlineStr">
+      <c r="E27" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -1956,15 +1959,15 @@
       <c r="G27" s="129" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="132" t="inlineStr">
+      <c r="A28" s="133" t="inlineStr">
         <is>
           <t>Horvath &amp; Tremblay</t>
         </is>
       </c>
-      <c r="B28" s="132" t="n">
+      <c r="B28" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="132" t="inlineStr">
+      <c r="C28" s="133" t="inlineStr">
         <is>
           <t>Alec Bashein</t>
         </is>
@@ -1974,7 +1977,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E28" s="132" t="inlineStr">
+      <c r="E28" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -1987,15 +1990,15 @@
       <c r="G28" s="129" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="132" t="inlineStr">
+      <c r="A29" s="133" t="inlineStr">
         <is>
           <t>Hull Multifamily</t>
         </is>
       </c>
-      <c r="B29" s="132" t="n">
+      <c r="B29" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C29" s="132" t="inlineStr">
+      <c r="C29" s="133" t="inlineStr">
         <is>
           <t>Nick Hull</t>
         </is>
@@ -2005,7 +2008,7 @@
           <t>Partner</t>
         </is>
       </c>
-      <c r="E29" s="132" t="inlineStr">
+      <c r="E29" s="133" t="inlineStr">
         <is>
           <t>Naples</t>
         </is>
@@ -2018,15 +2021,15 @@
       <c r="G29" s="129" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="132" t="inlineStr">
+      <c r="A30" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B30" s="132" t="n">
+      <c r="B30" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="132" t="inlineStr">
+      <c r="C30" s="133" t="inlineStr">
         <is>
           <t>Cliff Taylor</t>
         </is>
@@ -2036,7 +2039,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E30" s="132" t="inlineStr">
+      <c r="E30" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2049,15 +2052,15 @@
       <c r="G30" s="129" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="132" t="inlineStr">
+      <c r="A31" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B31" s="132" t="n">
+      <c r="B31" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="132" t="inlineStr">
+      <c r="C31" s="133" t="inlineStr">
         <is>
           <t>Maurice Habif</t>
         </is>
@@ -2067,7 +2070,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E31" s="132" t="inlineStr">
+      <c r="E31" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2080,15 +2083,15 @@
       <c r="G31" s="129" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="132" t="inlineStr">
+      <c r="A32" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B32" s="132" t="n">
+      <c r="B32" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="132" t="inlineStr">
+      <c r="C32" s="133" t="inlineStr">
         <is>
           <t>Zach Nolan</t>
         </is>
@@ -2098,7 +2101,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E32" s="132" t="inlineStr">
+      <c r="E32" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2111,15 +2114,15 @@
       <c r="G32" s="129" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="132" t="inlineStr">
+      <c r="A33" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B33" s="132" t="n">
+      <c r="B33" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="132" t="inlineStr">
+      <c r="C33" s="133" t="inlineStr">
         <is>
           <t>Kyle Butler</t>
         </is>
@@ -2129,7 +2132,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E33" s="132" t="inlineStr">
+      <c r="E33" s="133" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2142,15 +2145,15 @@
       <c r="G33" s="129" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="132" t="inlineStr">
+      <c r="A34" s="133" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B34" s="132" t="n">
+      <c r="B34" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="132" t="inlineStr">
+      <c r="C34" s="133" t="inlineStr">
         <is>
           <t>Deme Mekras</t>
         </is>
@@ -2160,7 +2163,7 @@
           <t>Managing Partner, CEO</t>
         </is>
       </c>
-      <c r="E34" s="132" t="inlineStr">
+      <c r="E34" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2173,15 +2176,15 @@
       <c r="G34" s="129" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="132" t="inlineStr">
+      <c r="A35" s="133" t="inlineStr">
         <is>
           <t>MSP Group</t>
         </is>
       </c>
-      <c r="B35" s="132" t="n">
+      <c r="B35" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C35" s="132" t="inlineStr">
+      <c r="C35" s="133" t="inlineStr">
         <is>
           <t>Sam Mekras</t>
         </is>
@@ -2191,7 +2194,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E35" s="132" t="inlineStr">
+      <c r="E35" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2204,15 +2207,15 @@
       <c r="G35" s="129" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="132" t="inlineStr">
+      <c r="A36" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B36" s="132" t="n">
+      <c r="B36" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="132" t="inlineStr">
+      <c r="C36" s="133" t="inlineStr">
         <is>
           <t>Felipe Echarte</t>
         </is>
@@ -2222,7 +2225,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E36" s="132" t="inlineStr">
+      <c r="E36" s="133" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2235,15 +2238,15 @@
       <c r="G36" s="129" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="132" t="inlineStr">
+      <c r="A37" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B37" s="132" t="n">
+      <c r="B37" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C37" s="132" t="inlineStr">
+      <c r="C37" s="133" t="inlineStr">
         <is>
           <t>Joseph Thomas</t>
         </is>
@@ -2253,7 +2256,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E37" s="132" t="inlineStr">
+      <c r="E37" s="133" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2266,15 +2269,15 @@
       <c r="G37" s="129" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="132" t="inlineStr">
+      <c r="A38" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B38" s="132" t="n">
+      <c r="B38" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C38" s="132" t="inlineStr">
+      <c r="C38" s="133" t="inlineStr">
         <is>
           <t>Ray Turchi</t>
         </is>
@@ -2284,7 +2287,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E38" s="132" t="inlineStr">
+      <c r="E38" s="133" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2297,15 +2300,15 @@
       <c r="G38" s="129" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="132" t="inlineStr">
+      <c r="A39" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B39" s="132" t="n">
+      <c r="B39" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="132" t="inlineStr">
+      <c r="C39" s="133" t="inlineStr">
         <is>
           <t>Adam Marcuvitz</t>
         </is>
@@ -2315,7 +2318,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E39" s="132" t="inlineStr">
+      <c r="E39" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2328,15 +2331,15 @@
       <c r="G39" s="129" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="132" t="inlineStr">
+      <c r="A40" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B40" s="132" t="n">
+      <c r="B40" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="132" t="inlineStr">
+      <c r="C40" s="133" t="inlineStr">
         <is>
           <t>Erik Bjornson</t>
         </is>
@@ -2346,7 +2349,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E40" s="132" t="inlineStr">
+      <c r="E40" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2359,15 +2362,15 @@
       <c r="G40" s="129" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="132" t="inlineStr">
+      <c r="A41" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B41" s="132" t="n">
+      <c r="B41" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="132" t="inlineStr">
+      <c r="C41" s="133" t="inlineStr">
         <is>
           <t>Luke Wickham</t>
         </is>
@@ -2377,7 +2380,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E41" s="132" t="inlineStr">
+      <c r="E41" s="133" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2386,15 +2389,15 @@
       <c r="G41" s="129" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="132" t="inlineStr">
+      <c r="A42" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B42" s="132" t="n">
+      <c r="B42" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="132" t="inlineStr">
+      <c r="C42" s="133" t="inlineStr">
         <is>
           <t>Tyler Nilsson</t>
         </is>
@@ -2404,7 +2407,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E42" s="132" t="inlineStr">
+      <c r="E42" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2417,15 +2420,15 @@
       <c r="G42" s="129" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="132" t="inlineStr">
+      <c r="A43" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B43" s="132" t="n">
+      <c r="B43" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="132" t="inlineStr">
+      <c r="C43" s="133" t="inlineStr">
         <is>
           <t>Kyle Kundiger</t>
         </is>
@@ -2435,7 +2438,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E43" s="132" t="inlineStr">
+      <c r="E43" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2448,21 +2451,21 @@
       <c r="G43" s="129" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="132" t="inlineStr">
+      <c r="A44" s="133" t="inlineStr">
         <is>
           <t>Matthew</t>
         </is>
       </c>
-      <c r="B44" s="132" t="n">
+      <c r="B44" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="132" t="inlineStr">
+      <c r="C44" s="133" t="inlineStr">
         <is>
           <t>William Bruce</t>
         </is>
       </c>
       <c r="D44" s="129" t="inlineStr"/>
-      <c r="E44" s="132" t="inlineStr">
+      <c r="E44" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2475,15 +2478,15 @@
       <c r="G44" s="129" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="132" t="inlineStr">
+      <c r="A45" s="133" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B45" s="132" t="n">
+      <c r="B45" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C45" s="132" t="inlineStr">
+      <c r="C45" s="133" t="inlineStr">
         <is>
           <t>John Rutherford</t>
         </is>
@@ -2493,7 +2496,7 @@
           <t>Senior VP</t>
         </is>
       </c>
-      <c r="E45" s="132" t="inlineStr">
+      <c r="E45" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2506,15 +2509,15 @@
       <c r="G45" s="129" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="132" t="inlineStr">
+      <c r="A46" s="133" t="inlineStr">
         <is>
           <t>NAI Hallmark</t>
         </is>
       </c>
-      <c r="B46" s="132" t="n">
+      <c r="B46" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C46" s="132" t="inlineStr">
+      <c r="C46" s="133" t="inlineStr">
         <is>
           <t>Luke McCann</t>
         </is>
@@ -2524,7 +2527,7 @@
           <t>VP</t>
         </is>
       </c>
-      <c r="E46" s="132" t="inlineStr">
+      <c r="E46" s="133" t="inlineStr">
         <is>
           <t>Jacksonville</t>
         </is>
@@ -2537,15 +2540,15 @@
       <c r="G46" s="129" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="132" t="inlineStr">
+      <c r="A47" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B47" s="132" t="n">
+      <c r="B47" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C47" s="132" t="inlineStr">
+      <c r="C47" s="133" t="inlineStr">
         <is>
           <t>Avery Klann</t>
         </is>
@@ -2555,7 +2558,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E47" s="132" t="inlineStr">
+      <c r="E47" s="133" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2568,15 +2571,15 @@
       <c r="G47" s="129" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="132" t="inlineStr">
+      <c r="A48" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B48" s="132" t="n">
+      <c r="B48" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C48" s="132" t="inlineStr">
+      <c r="C48" s="133" t="inlineStr">
         <is>
           <t>Hampton Beebe</t>
         </is>
@@ -2586,7 +2589,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E48" s="132" t="inlineStr">
+      <c r="E48" s="133" t="inlineStr">
         <is>
           <t>Boca Raton</t>
         </is>
@@ -2599,15 +2602,15 @@
       <c r="G48" s="129" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="132" t="inlineStr">
+      <c r="A49" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B49" s="132" t="n">
+      <c r="B49" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C49" s="132" t="inlineStr">
+      <c r="C49" s="133" t="inlineStr">
         <is>
           <t>Patrick Dufour</t>
         </is>
@@ -2617,7 +2620,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E49" s="132" t="inlineStr">
+      <c r="E49" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2630,15 +2633,15 @@
       <c r="G49" s="129" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="132" t="inlineStr">
+      <c r="A50" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B50" s="132" t="n">
+      <c r="B50" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="132" t="inlineStr">
+      <c r="C50" s="133" t="inlineStr">
         <is>
           <t>Scott Ramey</t>
         </is>
@@ -2648,7 +2651,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E50" s="132" t="inlineStr">
+      <c r="E50" s="133" t="inlineStr">
         <is>
           <t>Orlando</t>
         </is>
@@ -2657,21 +2660,21 @@
       <c r="G50" s="129" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="132" t="inlineStr">
+      <c r="A51" s="133" t="inlineStr">
         <is>
           <t>One Commercial</t>
         </is>
       </c>
-      <c r="B51" s="132" t="n">
+      <c r="B51" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C51" s="132" t="inlineStr">
+      <c r="C51" s="133" t="inlineStr">
         <is>
           <t>Alexis Shapiro</t>
         </is>
       </c>
       <c r="D51" s="129" t="inlineStr"/>
-      <c r="E51" s="132" t="inlineStr">
+      <c r="E51" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -2684,15 +2687,15 @@
       <c r="G51" s="129" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="132" t="inlineStr">
+      <c r="A52" s="133" t="inlineStr">
         <is>
           <t>ReMax</t>
         </is>
       </c>
-      <c r="B52" s="132" t="n">
+      <c r="B52" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="132" t="inlineStr">
+      <c r="C52" s="133" t="inlineStr">
         <is>
           <t>Roger Lohse</t>
         </is>
@@ -2702,7 +2705,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E52" s="132" t="inlineStr">
+      <c r="E52" s="133" t="inlineStr">
         <is>
           <t>Hollywood</t>
         </is>
@@ -2715,15 +2718,15 @@
       <c r="G52" s="129" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="132" t="inlineStr">
+      <c r="A53" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B53" s="132" t="n">
+      <c r="B53" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="132" t="inlineStr">
+      <c r="C53" s="133" t="inlineStr">
         <is>
           <t>Aaron Hargrove</t>
         </is>
@@ -2733,7 +2736,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E53" s="132" t="inlineStr">
+      <c r="E53" s="133" t="inlineStr">
         <is>
           <t>Ft Lauderdale</t>
         </is>
@@ -2746,15 +2749,15 @@
       <c r="G53" s="129" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="132" t="inlineStr">
+      <c r="A54" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B54" s="132" t="n">
+      <c r="B54" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C54" s="132" t="inlineStr">
+      <c r="C54" s="133" t="inlineStr">
         <is>
           <t>Brian Moulder</t>
         </is>
@@ -2764,7 +2767,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E54" s="132" t="inlineStr">
+      <c r="E54" s="133" t="inlineStr">
         <is>
           <t>Winter Park</t>
         </is>
@@ -2777,15 +2780,15 @@
       <c r="G54" s="129" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="132" t="inlineStr">
+      <c r="A55" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B55" s="132" t="n">
+      <c r="B55" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C55" s="132" t="inlineStr">
+      <c r="C55" s="133" t="inlineStr">
         <is>
           <t>Chris Chadbourne</t>
         </is>
@@ -2795,7 +2798,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E55" s="132" t="inlineStr">
+      <c r="E55" s="133" t="inlineStr">
         <is>
           <t>Tampa</t>
         </is>
@@ -2808,15 +2811,15 @@
       <c r="G55" s="129" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="132" t="inlineStr">
+      <c r="A56" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B56" s="132" t="n">
+      <c r="B56" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="132" t="inlineStr">
+      <c r="C56" s="133" t="inlineStr">
         <is>
           <t>Still Hunter</t>
         </is>
@@ -2826,7 +2829,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E56" s="132" t="inlineStr">
+      <c r="E56" s="133" t="inlineStr">
         <is>
           <t>Miami</t>
         </is>
@@ -3827,15 +3830,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132" t="inlineStr">
+      <c r="A3" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="132" t="n">
+      <c r="B3" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="133" t="inlineStr">
         <is>
           <t>John Phoenix</t>
         </is>
@@ -3845,7 +3848,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E3" s="132" t="inlineStr">
+      <c r="E3" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3858,15 +3861,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="132" t="n">
+      <c r="B4" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="132" t="inlineStr">
+      <c r="C4" s="133" t="inlineStr">
         <is>
           <t>Louis Smart</t>
         </is>
@@ -3876,7 +3879,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="132" t="inlineStr">
+      <c r="E4" s="133" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3889,15 +3892,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="132" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="132" t="n">
+      <c r="B5" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="132" t="inlineStr">
+      <c r="C5" s="133" t="inlineStr">
         <is>
           <t>Richard Gore</t>
         </is>
@@ -3907,7 +3910,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="132" t="inlineStr">
+      <c r="E5" s="133" t="inlineStr">
         <is>
           <t>Charlotte/Charleston</t>
         </is>
@@ -3920,15 +3923,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="132" t="inlineStr">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="132" t="n">
+      <c r="B6" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="132" t="inlineStr">
+      <c r="C6" s="133" t="inlineStr">
         <is>
           <t>Tyler Fish</t>
         </is>
@@ -3938,7 +3941,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="132" t="inlineStr">
+      <c r="E6" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3951,15 +3954,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="133" t="inlineStr">
         <is>
           <t>Kyle Chase</t>
         </is>
@@ -3969,7 +3972,7 @@
           <t>Executive Vice President</t>
         </is>
       </c>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -3982,15 +3985,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="132" t="inlineStr">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="132" t="inlineStr">
+      <c r="C8" s="133" t="inlineStr">
         <is>
           <t>Paul Marley</t>
         </is>
@@ -4000,7 +4003,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="132" t="inlineStr">
+      <c r="E8" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4013,15 +4016,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="132" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="132" t="n">
+      <c r="B9" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="132" t="inlineStr">
+      <c r="C9" s="133" t="inlineStr">
         <is>
           <t>Jordan McCarley</t>
         </is>
@@ -4031,7 +4034,7 @@
           <t>Executive Vice Chair</t>
         </is>
       </c>
-      <c r="E9" s="132" t="inlineStr"/>
+      <c r="E9" s="133" t="inlineStr"/>
       <c r="F9" s="129" t="inlineStr">
         <is>
           <t>https://multifamily.cushwake.com/Offices/Charlotte/Team</t>
@@ -4040,15 +4043,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="132" t="inlineStr">
+      <c r="A10" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="132" t="n">
+      <c r="B10" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="132" t="inlineStr">
+      <c r="C10" s="133" t="inlineStr">
         <is>
           <t>Alex McDermott</t>
         </is>
@@ -4058,7 +4061,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="132" t="inlineStr">
+      <c r="E10" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4071,15 +4074,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="132" t="inlineStr">
+      <c r="A11" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="132" t="n">
+      <c r="B11" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="132" t="inlineStr">
+      <c r="C11" s="133" t="inlineStr">
         <is>
           <t>Austin Green</t>
         </is>
@@ -4089,7 +4092,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E11" s="132" t="inlineStr">
+      <c r="E11" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4102,15 +4105,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="132" t="inlineStr">
+      <c r="A12" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="132" t="n">
+      <c r="B12" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="132" t="inlineStr">
+      <c r="C12" s="133" t="inlineStr">
         <is>
           <t>William Martin</t>
         </is>
@@ -4120,7 +4123,7 @@
           <t>Capital Markets Associate</t>
         </is>
       </c>
-      <c r="E12" s="132" t="inlineStr">
+      <c r="E12" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4133,15 +4136,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="132" t="inlineStr">
+      <c r="A13" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="132" t="n">
+      <c r="B13" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="132" t="inlineStr">
+      <c r="C13" s="133" t="inlineStr">
         <is>
           <t>Casey Sherman</t>
         </is>
@@ -4151,7 +4154,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="132" t="inlineStr">
+      <c r="E13" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4164,15 +4167,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="132" t="inlineStr">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="132" t="n">
+      <c r="B14" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="132" t="inlineStr">
+      <c r="C14" s="133" t="inlineStr">
         <is>
           <t>John Gavigan</t>
         </is>
@@ -4182,7 +4185,7 @@
           <t>Capital Markets - Investment Sales</t>
         </is>
       </c>
-      <c r="E14" s="132" t="inlineStr">
+      <c r="E14" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4195,15 +4198,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="132" t="inlineStr">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="132" t="n">
+      <c r="B15" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="132" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>Dean Smith</t>
         </is>
@@ -4213,7 +4216,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E15" s="132" t="inlineStr">
+      <c r="E15" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4226,15 +4229,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="132" t="inlineStr">
+      <c r="A16" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B16" s="132" t="n">
+      <c r="B16" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="132" t="inlineStr">
+      <c r="C16" s="133" t="inlineStr">
         <is>
           <t>John Heimburger</t>
         </is>
@@ -4244,7 +4247,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E16" s="132" t="inlineStr">
+      <c r="E16" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4257,15 +4260,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="132" t="inlineStr">
+      <c r="A17" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B17" s="132" t="n">
+      <c r="B17" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="132" t="inlineStr">
+      <c r="C17" s="133" t="inlineStr">
         <is>
           <t>Sean Wood</t>
         </is>
@@ -4275,7 +4278,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E17" s="132" t="inlineStr">
+      <c r="E17" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4288,15 +4291,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="132" t="inlineStr">
+      <c r="A18" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="132" t="n">
+      <c r="B18" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="132" t="inlineStr">
+      <c r="C18" s="133" t="inlineStr">
         <is>
           <t>Alex Okulski</t>
         </is>
@@ -4306,7 +4309,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="132" t="inlineStr">
+      <c r="E18" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4319,15 +4322,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="132" t="inlineStr">
+      <c r="A19" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="132" t="n">
+      <c r="B19" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="132" t="inlineStr">
+      <c r="C19" s="133" t="inlineStr">
         <is>
           <t>Rob Coleman</t>
         </is>
@@ -4337,7 +4340,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E19" s="132" t="inlineStr">
+      <c r="E19" s="133" t="inlineStr">
         <is>
           <t>Raleigh</t>
         </is>
@@ -4350,15 +4353,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="132" t="inlineStr">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="132" t="n">
+      <c r="B20" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="132" t="inlineStr">
+      <c r="C20" s="133" t="inlineStr">
         <is>
           <t>Michael Saclarides</t>
         </is>
@@ -4368,7 +4371,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E20" s="132" t="inlineStr">
+      <c r="E20" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4381,15 +4384,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="132" t="inlineStr">
+      <c r="A21" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="132" t="n">
+      <c r="B21" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="132" t="inlineStr">
+      <c r="C21" s="133" t="inlineStr">
         <is>
           <t>Devin Bryan</t>
         </is>
@@ -4399,7 +4402,7 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="E21" s="132" t="inlineStr">
+      <c r="E21" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -4412,15 +4415,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="132" t="inlineStr">
+      <c r="A22" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B22" s="132" t="n">
+      <c r="B22" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="132" t="inlineStr">
+      <c r="C22" s="133" t="inlineStr">
         <is>
           <t>Fletcher Dunn</t>
         </is>
@@ -4430,7 +4433,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E22" s="132" t="inlineStr">
+      <c r="E22" s="133" t="inlineStr">
         <is>
           <t>Charlotte</t>
         </is>
@@ -5424,21 +5427,21 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132" t="inlineStr">
+      <c r="A3" s="133" t="inlineStr">
         <is>
           <t>802 Property | Steadfast Group</t>
         </is>
       </c>
-      <c r="B3" s="132" t="n">
+      <c r="B3" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="133" t="inlineStr">
         <is>
           <t>Andy Hill</t>
         </is>
       </c>
       <c r="D3" s="129" t="inlineStr"/>
-      <c r="E3" s="132" t="inlineStr">
+      <c r="E3" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5447,21 +5450,21 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="132" t="n">
+      <c r="B4" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="132" t="inlineStr">
+      <c r="C4" s="133" t="inlineStr">
         <is>
           <t>Brett Carr</t>
         </is>
       </c>
       <c r="D4" s="129" t="inlineStr"/>
-      <c r="E4" s="132" t="inlineStr">
+      <c r="E4" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5470,21 +5473,21 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="132" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>Compass</t>
         </is>
       </c>
-      <c r="B5" s="132" t="n">
+      <c r="B5" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="132" t="inlineStr">
+      <c r="C5" s="133" t="inlineStr">
         <is>
           <t>David Dorris</t>
         </is>
       </c>
       <c r="D5" s="129" t="inlineStr"/>
-      <c r="E5" s="132" t="inlineStr">
+      <c r="E5" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5493,21 +5496,21 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="132" t="inlineStr">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B6" s="132" t="n">
+      <c r="B6" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="132" t="inlineStr">
+      <c r="C6" s="133" t="inlineStr">
         <is>
           <t>Tyler Mayo</t>
         </is>
       </c>
       <c r="D6" s="129" t="inlineStr"/>
-      <c r="E6" s="132" t="inlineStr">
+      <c r="E6" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5516,21 +5519,21 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>MRG Realty Partners</t>
         </is>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="133" t="inlineStr">
         <is>
           <t>Drew Lekowski</t>
         </is>
       </c>
       <c r="D7" s="129" t="inlineStr"/>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5539,21 +5542,21 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="132" t="inlineStr">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="132" t="inlineStr">
+      <c r="C8" s="133" t="inlineStr">
         <is>
           <t>David Stollenwerk</t>
         </is>
       </c>
       <c r="D8" s="129" t="inlineStr"/>
-      <c r="E8" s="132" t="inlineStr">
+      <c r="E8" s="133" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5562,21 +5565,21 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="132" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B9" s="132" t="n">
+      <c r="B9" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="132" t="inlineStr">
+      <c r="C9" s="133" t="inlineStr">
         <is>
           <t>Patrick Cosgrove</t>
         </is>
       </c>
       <c r="D9" s="129" t="inlineStr"/>
-      <c r="E9" s="132" t="inlineStr">
+      <c r="E9" s="133" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5585,21 +5588,21 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="132" t="inlineStr">
+      <c r="A10" s="133" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B10" s="132" t="n">
+      <c r="B10" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="132" t="inlineStr">
+      <c r="C10" s="133" t="inlineStr">
         <is>
           <t>Austin Fragoletti</t>
         </is>
       </c>
       <c r="D10" s="129" t="inlineStr"/>
-      <c r="E10" s="132" t="inlineStr">
+      <c r="E10" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5608,21 +5611,21 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="132" t="inlineStr">
+      <c r="A11" s="133" t="inlineStr">
         <is>
           <t>Matthews Real Estate Investment Services</t>
         </is>
       </c>
-      <c r="B11" s="132" t="n">
+      <c r="B11" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C11" s="132" t="inlineStr">
+      <c r="C11" s="133" t="inlineStr">
         <is>
           <t>Sam Jackson</t>
         </is>
       </c>
       <c r="D11" s="129" t="inlineStr"/>
-      <c r="E11" s="132" t="inlineStr">
+      <c r="E11" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5631,21 +5634,21 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="132" t="inlineStr">
+      <c r="A12" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B12" s="132" t="n">
+      <c r="B12" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="132" t="inlineStr">
+      <c r="C12" s="133" t="inlineStr">
         <is>
           <t>Vince Lefler</t>
         </is>
       </c>
       <c r="D12" s="129" t="inlineStr"/>
-      <c r="E12" s="132" t="inlineStr">
+      <c r="E12" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5654,21 +5657,21 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="132" t="inlineStr">
+      <c r="A13" s="133" t="inlineStr">
         <is>
           <t>Redwood Collective Acquisitions, LLC | The Kirkland Company</t>
         </is>
       </c>
-      <c r="B13" s="132" t="n">
+      <c r="B13" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="132" t="inlineStr">
+      <c r="C13" s="133" t="inlineStr">
         <is>
           <t>William Kirkland</t>
         </is>
       </c>
       <c r="D13" s="129" t="inlineStr"/>
-      <c r="E13" s="132" t="inlineStr">
+      <c r="E13" s="133" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5677,21 +5680,21 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="132" t="inlineStr">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>Stevens Group, LLC</t>
         </is>
       </c>
-      <c r="B14" s="132" t="n">
+      <c r="B14" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="132" t="inlineStr">
+      <c r="C14" s="133" t="inlineStr">
         <is>
           <t>Rusty Rust</t>
         </is>
       </c>
       <c r="D14" s="129" t="inlineStr"/>
-      <c r="E14" s="132" t="inlineStr">
+      <c r="E14" s="133" t="inlineStr">
         <is>
           <t>Antioch</t>
         </is>
@@ -5700,21 +5703,21 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="132" t="inlineStr">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B15" s="132" t="n">
+      <c r="B15" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="132" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>Miller Harris</t>
         </is>
       </c>
       <c r="D15" s="129" t="inlineStr"/>
-      <c r="E15" s="132" t="inlineStr">
+      <c r="E15" s="133" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5723,21 +5726,21 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="132" t="inlineStr">
+      <c r="A16" s="133" t="inlineStr">
         <is>
           <t>The Kirkland Company</t>
         </is>
       </c>
-      <c r="B16" s="132" t="n">
+      <c r="B16" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="132" t="inlineStr">
+      <c r="C16" s="133" t="inlineStr">
         <is>
           <t>Zac Wracher</t>
         </is>
       </c>
       <c r="D16" s="129" t="inlineStr"/>
-      <c r="E16" s="132" t="inlineStr">
+      <c r="E16" s="133" t="inlineStr">
         <is>
           <t>Brentwood</t>
         </is>
@@ -5746,21 +5749,21 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="132" t="inlineStr">
+      <c r="A17" s="133" t="inlineStr">
         <is>
           <t>The Parks Group Commercial</t>
         </is>
       </c>
-      <c r="B17" s="132" t="n">
+      <c r="B17" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="132" t="inlineStr">
+      <c r="C17" s="133" t="inlineStr">
         <is>
           <t>John Harney</t>
         </is>
       </c>
       <c r="D17" s="129" t="inlineStr"/>
-      <c r="E17" s="132" t="inlineStr">
+      <c r="E17" s="133" t="inlineStr">
         <is>
           <t>Murfreesboro</t>
         </is>
@@ -5769,21 +5772,21 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="132" t="inlineStr">
+      <c r="A18" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B18" s="132" t="n">
+      <c r="B18" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="132" t="inlineStr">
+      <c r="C18" s="133" t="inlineStr">
         <is>
           <t>Anne McGinn</t>
         </is>
       </c>
       <c r="D18" s="129" t="inlineStr"/>
-      <c r="E18" s="132" t="inlineStr">
+      <c r="E18" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5792,21 +5795,21 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="132" t="inlineStr">
+      <c r="A19" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="132" t="n">
+      <c r="B19" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="132" t="inlineStr">
+      <c r="C19" s="133" t="inlineStr">
         <is>
           <t>Brad Boston</t>
         </is>
       </c>
       <c r="D19" s="129" t="inlineStr"/>
-      <c r="E19" s="132" t="inlineStr">
+      <c r="E19" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5815,21 +5818,21 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="132" t="inlineStr">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="132" t="n">
+      <c r="B20" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="132" t="inlineStr">
+      <c r="C20" s="133" t="inlineStr">
         <is>
           <t>Brett Kingman</t>
         </is>
       </c>
       <c r="D20" s="129" t="inlineStr"/>
-      <c r="E20" s="132" t="inlineStr">
+      <c r="E20" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -5838,21 +5841,21 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="132" t="inlineStr">
+      <c r="A21" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B21" s="132" t="n">
+      <c r="B21" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C21" s="132" t="inlineStr">
+      <c r="C21" s="133" t="inlineStr">
         <is>
           <t>Robbie O'Bryan</t>
         </is>
       </c>
       <c r="D21" s="129" t="inlineStr"/>
-      <c r="E21" s="132" t="inlineStr">
+      <c r="E21" s="133" t="inlineStr">
         <is>
           <t>Nashville</t>
         </is>
@@ -7622,15 +7625,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132" t="inlineStr">
+      <c r="A3" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="132" t="n">
+      <c r="B3" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="133" t="inlineStr">
         <is>
           <t>Calvin Griffith</t>
         </is>
@@ -7640,7 +7643,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E3" s="132" t="inlineStr">
+      <c r="E3" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7653,15 +7656,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="132" t="n">
+      <c r="B4" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="132" t="inlineStr">
+      <c r="C4" s="133" t="inlineStr">
         <is>
           <t>Peyton Cox</t>
         </is>
@@ -7671,7 +7674,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E4" s="132" t="inlineStr">
+      <c r="E4" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7684,15 +7687,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="132" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="132" t="n">
+      <c r="B5" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="132" t="inlineStr">
+      <c r="C5" s="133" t="inlineStr">
         <is>
           <t>Andrew Blackmon</t>
         </is>
@@ -7702,7 +7705,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E5" s="132" t="inlineStr">
+      <c r="E5" s="133" t="inlineStr">
         <is>
           <t>Hampton Roads/Richmond</t>
         </is>
@@ -7715,15 +7718,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="132" t="inlineStr">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B6" s="132" t="n">
+      <c r="B6" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="132" t="inlineStr">
+      <c r="C6" s="133" t="inlineStr">
         <is>
           <t>Garrison Gore</t>
         </is>
@@ -7733,7 +7736,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E6" s="132" t="inlineStr">
+      <c r="E6" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7746,15 +7749,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="133" t="inlineStr">
         <is>
           <t>Thomas Leachman</t>
         </is>
@@ -7764,7 +7767,7 @@
           <t>Senior Vice President, National Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7777,15 +7780,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="132" t="inlineStr">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="132" t="inlineStr">
+      <c r="C8" s="133" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -7795,7 +7798,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="132" t="inlineStr">
+      <c r="E8" s="133" t="inlineStr">
         <is>
           <t>Richmond (Mid-Atlantic)</t>
         </is>
@@ -7808,15 +7811,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="132" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B9" s="132" t="n">
+      <c r="B9" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="132" t="inlineStr">
+      <c r="C9" s="133" t="inlineStr">
         <is>
           <t>William Dickinson</t>
         </is>
@@ -7826,7 +7829,7 @@
           <t>Associate</t>
         </is>
       </c>
-      <c r="E9" s="132" t="inlineStr">
+      <c r="E9" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7839,15 +7842,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="132" t="inlineStr">
+      <c r="A10" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="132" t="n">
+      <c r="B10" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="132" t="inlineStr">
+      <c r="C10" s="133" t="inlineStr">
         <is>
           <t>Jorge Rosa / Paul C. Norman, Jr.</t>
         </is>
@@ -7857,7 +7860,7 @@
           <t>Executive Managing Directors</t>
         </is>
       </c>
-      <c r="E10" s="132" t="inlineStr">
+      <c r="E10" s="133" t="inlineStr">
         <is>
           <t>Based DC, covers Richmond</t>
         </is>
@@ -7866,15 +7869,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="132" t="inlineStr">
+      <c r="A11" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B11" s="132" t="n">
+      <c r="B11" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="132" t="inlineStr">
+      <c r="C11" s="133" t="inlineStr">
         <is>
           <t>Christopher Chadwick</t>
         </is>
@@ -7884,7 +7887,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E11" s="132" t="inlineStr">
+      <c r="E11" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7897,15 +7900,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="132" t="inlineStr">
+      <c r="A12" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B12" s="132" t="n">
+      <c r="B12" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="132" t="inlineStr">
+      <c r="C12" s="133" t="inlineStr">
         <is>
           <t>Justin Ferguson</t>
         </is>
@@ -7915,7 +7918,7 @@
           <t>Multifamily Specialist</t>
         </is>
       </c>
-      <c r="E12" s="132" t="inlineStr">
+      <c r="E12" s="133" t="inlineStr">
         <is>
           <t>Richmond (Southern VA office)</t>
         </is>
@@ -7928,15 +7931,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="132" t="inlineStr">
+      <c r="A13" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B13" s="132" t="n">
+      <c r="B13" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="132" t="inlineStr">
+      <c r="C13" s="133" t="inlineStr">
         <is>
           <t>Martin Mooradian</t>
         </is>
@@ -7946,7 +7949,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E13" s="132" t="inlineStr">
+      <c r="E13" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7959,15 +7962,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="132" t="inlineStr">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B14" s="132" t="n">
+      <c r="B14" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="132" t="inlineStr">
+      <c r="C14" s="133" t="inlineStr">
         <is>
           <t>Mark Williford</t>
         </is>
@@ -7977,7 +7980,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E14" s="132" t="inlineStr">
+      <c r="E14" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -7990,15 +7993,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="132" t="inlineStr">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B15" s="132" t="n">
+      <c r="B15" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="132" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>Will Bradley</t>
         </is>
@@ -8008,7 +8011,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="132" t="inlineStr">
+      <c r="E15" s="133" t="inlineStr">
         <is>
           <t>Richmond</t>
         </is>
@@ -8881,15 +8884,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132" t="inlineStr">
+      <c r="A3" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="132" t="n">
+      <c r="B3" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="133" t="inlineStr">
         <is>
           <t>Bob Dean (Robert G. Dean III)</t>
         </is>
@@ -8899,7 +8902,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E3" s="132" t="inlineStr">
+      <c r="E3" s="133" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA / Suburban MD</t>
         </is>
@@ -8912,15 +8915,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="132" t="n">
+      <c r="B4" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="132" t="inlineStr">
+      <c r="C4" s="133" t="inlineStr">
         <is>
           <t>John T. Sheridan, Jr.</t>
         </is>
@@ -8930,7 +8933,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="132" t="inlineStr">
+      <c r="E4" s="133" t="inlineStr">
         <is>
           <t>DC / VA / MD</t>
         </is>
@@ -8943,15 +8946,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="132" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="132" t="n">
+      <c r="B5" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="132" t="inlineStr">
+      <c r="C5" s="133" t="inlineStr">
         <is>
           <t>Michael Muldowney</t>
         </is>
@@ -8961,7 +8964,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E5" s="132" t="inlineStr">
+      <c r="E5" s="133" t="inlineStr">
         <is>
           <t>Washington, DC / MD suburbs</t>
         </is>
@@ -8974,15 +8977,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="132" t="inlineStr">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="132" t="n">
+      <c r="B6" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="132" t="inlineStr">
+      <c r="C6" s="133" t="inlineStr">
         <is>
           <t>Bill Roohan</t>
         </is>
@@ -8992,7 +8995,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="132" t="inlineStr">
+      <c r="E6" s="133" t="inlineStr">
         <is>
           <t>Baltimore</t>
         </is>
@@ -9005,15 +9008,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="133" t="inlineStr">
         <is>
           <t>Chandler Pace</t>
         </is>
@@ -9023,7 +9026,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9036,15 +9039,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="132" t="inlineStr">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="132" t="inlineStr">
+      <c r="C8" s="133" t="inlineStr">
         <is>
           <t>Will Mathews</t>
         </is>
@@ -9054,7 +9057,7 @@
           <t>Vice Chair</t>
         </is>
       </c>
-      <c r="E8" s="132" t="inlineStr">
+      <c r="E8" s="133" t="inlineStr">
         <is>
           <t>Washington, DC / NoVA</t>
         </is>
@@ -9067,15 +9070,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="132" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="132" t="n">
+      <c r="B9" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="132" t="inlineStr">
+      <c r="C9" s="133" t="inlineStr">
         <is>
           <t>Jorge Rosa</t>
         </is>
@@ -9085,7 +9088,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="132" t="inlineStr">
+      <c r="E9" s="133" t="inlineStr">
         <is>
           <t>Washington, DC / MD / VA</t>
         </is>
@@ -9098,15 +9101,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="132" t="inlineStr">
+      <c r="A10" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="132" t="n">
+      <c r="B10" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="132" t="inlineStr">
+      <c r="C10" s="133" t="inlineStr">
         <is>
           <t>Paul C. Norman, Jr.</t>
         </is>
@@ -9116,7 +9119,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="132" t="inlineStr">
+      <c r="E10" s="133" t="inlineStr">
         <is>
           <t>Washington, DC metro</t>
         </is>
@@ -9129,15 +9132,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="132" t="inlineStr">
+      <c r="A11" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B11" s="132" t="n">
+      <c r="B11" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="132" t="inlineStr">
+      <c r="C11" s="133" t="inlineStr">
         <is>
           <t>Mac Hollensteiner</t>
         </is>
@@ -9147,7 +9150,7 @@
           <t>Senior Associate</t>
         </is>
       </c>
-      <c r="E11" s="132" t="inlineStr">
+      <c r="E11" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9160,15 +9163,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="132" t="inlineStr">
+      <c r="A12" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B12" s="132" t="n">
+      <c r="B12" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="132" t="inlineStr">
+      <c r="C12" s="133" t="inlineStr">
         <is>
           <t>Brooke Hanson</t>
         </is>
@@ -9178,7 +9181,7 @@
           <t>Capital Markets Group</t>
         </is>
       </c>
-      <c r="E12" s="132" t="inlineStr">
+      <c r="E12" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9191,15 +9194,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="132" t="inlineStr">
+      <c r="A13" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="132" t="n">
+      <c r="B13" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="132" t="inlineStr">
+      <c r="C13" s="133" t="inlineStr">
         <is>
           <t>Andrew Weir</t>
         </is>
@@ -9209,7 +9212,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E13" s="132" t="inlineStr">
+      <c r="E13" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9222,15 +9225,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="132" t="inlineStr">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="132" t="n">
+      <c r="B14" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="132" t="inlineStr">
+      <c r="C14" s="133" t="inlineStr">
         <is>
           <t>Jamie Leachman</t>
         </is>
@@ -9240,7 +9243,7 @@
           <t>Senior Managing Director, DC Co-Head</t>
         </is>
       </c>
-      <c r="E14" s="132" t="inlineStr">
+      <c r="E14" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9253,15 +9256,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="132" t="inlineStr">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B15" s="132" t="n">
+      <c r="B15" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="132" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>Robert Jenkins</t>
         </is>
@@ -9271,7 +9274,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E15" s="132" t="inlineStr">
+      <c r="E15" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9284,15 +9287,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="132" t="inlineStr">
+      <c r="A16" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B16" s="132" t="n">
+      <c r="B16" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C16" s="132" t="inlineStr">
+      <c r="C16" s="133" t="inlineStr">
         <is>
           <t>Bret Thompson</t>
         </is>
@@ -9302,7 +9305,7 @@
           <t>Senior Director</t>
         </is>
       </c>
-      <c r="E16" s="132" t="inlineStr">
+      <c r="E16" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9315,15 +9318,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="132" t="inlineStr">
+      <c r="A17" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="132" t="n">
+      <c r="B17" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="132" t="inlineStr">
+      <c r="C17" s="133" t="inlineStr">
         <is>
           <t>Lorenzo M. Wooten, Jr., CCIM</t>
         </is>
@@ -9333,7 +9336,7 @@
           <t>Senior Director of Investments</t>
         </is>
       </c>
-      <c r="E17" s="132" t="inlineStr">
+      <c r="E17" s="133" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9346,15 +9349,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="132" t="inlineStr">
+      <c r="A18" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B18" s="132" t="n">
+      <c r="B18" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="132" t="inlineStr">
+      <c r="C18" s="133" t="inlineStr">
         <is>
           <t>Christine Espenshade</t>
         </is>
@@ -9364,7 +9367,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E18" s="132" t="inlineStr">
+      <c r="E18" s="133" t="inlineStr">
         <is>
           <t>Washington, DC</t>
         </is>
@@ -9377,15 +9380,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="132" t="inlineStr">
+      <c r="A19" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B19" s="132" t="n">
+      <c r="B19" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="132" t="inlineStr">
+      <c r="C19" s="133" t="inlineStr">
         <is>
           <t>Christopher Doerr</t>
         </is>
@@ -9395,7 +9398,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E19" s="132" t="inlineStr">
+      <c r="E19" s="133" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -9408,15 +9411,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="132" t="inlineStr">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B20" s="132" t="n">
+      <c r="B20" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="132" t="inlineStr">
+      <c r="C20" s="133" t="inlineStr">
         <is>
           <t>William Harvey</t>
         </is>
@@ -9426,7 +9429,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E20" s="132" t="inlineStr">
+      <c r="E20" s="133" t="inlineStr">
         <is>
           <t>Bethesda, MD</t>
         </is>
@@ -10295,15 +10298,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132" t="inlineStr">
+      <c r="A3" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B3" s="132" t="n">
+      <c r="B3" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="133" t="inlineStr">
         <is>
           <t>Andrew Burns</t>
         </is>
@@ -10313,7 +10316,7 @@
           <t>Vice President</t>
         </is>
       </c>
-      <c r="E3" s="132" t="inlineStr">
+      <c r="E3" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10326,15 +10329,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B4" s="132" t="n">
+      <c r="B4" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="132" t="inlineStr">
+      <c r="C4" s="133" t="inlineStr">
         <is>
           <t>Jake Reid</t>
         </is>
@@ -10344,7 +10347,7 @@
           <t>Senior Vice President</t>
         </is>
       </c>
-      <c r="E4" s="132" t="inlineStr">
+      <c r="E4" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10357,15 +10360,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="132" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="132" t="n">
+      <c r="B5" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="132" t="inlineStr">
+      <c r="C5" s="133" t="inlineStr">
         <is>
           <t>Kurt McGarry</t>
         </is>
@@ -10375,7 +10378,7 @@
           <t>First Vice President</t>
         </is>
       </c>
-      <c r="E5" s="132" t="inlineStr">
+      <c r="E5" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10388,15 +10391,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="132" t="inlineStr">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="132" t="n">
+      <c r="B6" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="132" t="inlineStr">
+      <c r="C6" s="133" t="inlineStr">
         <is>
           <t>Shea Campbell</t>
         </is>
@@ -10406,7 +10409,7 @@
           <t>Vice Chairman / Managing Director</t>
         </is>
       </c>
-      <c r="E6" s="132" t="inlineStr">
+      <c r="E6" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10419,15 +10422,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="133" t="inlineStr">
         <is>
           <t>Craig Hey</t>
         </is>
@@ -10437,7 +10440,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10450,15 +10453,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="132" t="inlineStr">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="132" t="inlineStr">
+      <c r="C8" s="133" t="inlineStr">
         <is>
           <t>Mike Kemether</t>
         </is>
@@ -10468,7 +10471,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E8" s="132" t="inlineStr">
+      <c r="E8" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10481,15 +10484,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="132" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B9" s="132" t="n">
+      <c r="B9" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="132" t="inlineStr">
+      <c r="C9" s="133" t="inlineStr">
         <is>
           <t>Morgan Berg</t>
         </is>
@@ -10499,7 +10502,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E9" s="132" t="inlineStr">
+      <c r="E9" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10512,15 +10515,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="132" t="inlineStr">
+      <c r="A10" s="133" t="inlineStr">
         <is>
           <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
-      <c r="B10" s="132" t="n">
+      <c r="B10" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="132" t="inlineStr">
+      <c r="C10" s="133" t="inlineStr">
         <is>
           <t>Robert Stickel</t>
         </is>
@@ -10530,7 +10533,7 @@
           <t>Sunbelt Multifamily Advisory Group</t>
         </is>
       </c>
-      <c r="E10" s="132" t="inlineStr">
+      <c r="E10" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10543,15 +10546,15 @@
       <c r="G10" s="129" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="132" t="inlineStr">
+      <c r="A11" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B11" s="132" t="n">
+      <c r="B11" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="132" t="inlineStr">
+      <c r="C11" s="133" t="inlineStr">
         <is>
           <t>Peter Yorck</t>
         </is>
@@ -10561,7 +10564,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E11" s="132" t="inlineStr">
+      <c r="E11" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10574,15 +10577,15 @@
       <c r="G11" s="129" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="132" t="inlineStr">
+      <c r="A12" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B12" s="132" t="n">
+      <c r="B12" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="132" t="inlineStr">
+      <c r="C12" s="133" t="inlineStr">
         <is>
           <t>Dennis Mitchell</t>
         </is>
@@ -10592,7 +10595,7 @@
           <t>Senior Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E12" s="132" t="inlineStr">
+      <c r="E12" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10605,15 +10608,15 @@
       <c r="G12" s="129" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="132" t="inlineStr">
+      <c r="A13" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B13" s="132" t="n">
+      <c r="B13" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="132" t="inlineStr">
+      <c r="C13" s="133" t="inlineStr">
         <is>
           <t>Michael Fox</t>
         </is>
@@ -10623,7 +10626,7 @@
           <t>Managing Director, Capital Markets</t>
         </is>
       </c>
-      <c r="E13" s="132" t="inlineStr">
+      <c r="E13" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10636,15 +10639,15 @@
       <c r="G13" s="129" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="132" t="inlineStr">
+      <c r="A14" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B14" s="132" t="n">
+      <c r="B14" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="132" t="inlineStr">
+      <c r="C14" s="133" t="inlineStr">
         <is>
           <t>John Weber</t>
         </is>
@@ -10654,7 +10657,7 @@
           <t>Investment Sales (Multifamily)</t>
         </is>
       </c>
-      <c r="E14" s="132" t="inlineStr">
+      <c r="E14" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10667,15 +10670,15 @@
       <c r="G14" s="129" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="132" t="inlineStr">
+      <c r="A15" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B15" s="132" t="n">
+      <c r="B15" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="132" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>Marc Irvin</t>
         </is>
@@ -10685,7 +10688,7 @@
           <t>Managing Director Investments</t>
         </is>
       </c>
-      <c r="E15" s="132" t="inlineStr">
+      <c r="E15" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10698,15 +10701,15 @@
       <c r="G15" s="129" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="132" t="inlineStr">
+      <c r="A16" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B16" s="132" t="n">
+      <c r="B16" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C16" s="132" t="inlineStr">
+      <c r="C16" s="133" t="inlineStr">
         <is>
           <t>Harold Shepard</t>
         </is>
@@ -10716,7 +10719,7 @@
           <t>Investment Broker</t>
         </is>
       </c>
-      <c r="E16" s="132" t="inlineStr">
+      <c r="E16" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10729,15 +10732,15 @@
       <c r="G16" s="129" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="132" t="inlineStr">
+      <c r="A17" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B17" s="132" t="n">
+      <c r="B17" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="132" t="inlineStr">
+      <c r="C17" s="133" t="inlineStr">
         <is>
           <t>Joe Mitchell</t>
         </is>
@@ -10747,7 +10750,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E17" s="132" t="inlineStr">
+      <c r="E17" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10760,15 +10763,15 @@
       <c r="G17" s="129" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="132" t="inlineStr">
+      <c r="A18" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap</t>
         </is>
       </c>
-      <c r="B18" s="132" t="n">
+      <c r="B18" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C18" s="132" t="inlineStr">
+      <c r="C18" s="133" t="inlineStr">
         <is>
           <t>Marco Welch</t>
         </is>
@@ -10778,7 +10781,7 @@
           <t>Investment Sales</t>
         </is>
       </c>
-      <c r="E18" s="132" t="inlineStr">
+      <c r="E18" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10791,15 +10794,15 @@
       <c r="G18" s="129" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="132" t="inlineStr">
+      <c r="A19" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B19" s="132" t="n">
+      <c r="B19" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C19" s="132" t="inlineStr">
+      <c r="C19" s="133" t="inlineStr">
         <is>
           <t>David Gutting</t>
         </is>
@@ -10809,7 +10812,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E19" s="132" t="inlineStr">
+      <c r="E19" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10822,15 +10825,15 @@
       <c r="G19" s="129" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="132" t="inlineStr">
+      <c r="A20" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B20" s="132" t="n">
+      <c r="B20" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="132" t="inlineStr">
+      <c r="C20" s="133" t="inlineStr">
         <is>
           <t>Derrick Bloom</t>
         </is>
@@ -10840,7 +10843,7 @@
           <t>Vice Chairman, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E20" s="132" t="inlineStr">
+      <c r="E20" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10853,15 +10856,15 @@
       <c r="G20" s="129" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="132" t="inlineStr">
+      <c r="A21" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B21" s="132" t="n">
+      <c r="B21" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="132" t="inlineStr">
+      <c r="C21" s="133" t="inlineStr">
         <is>
           <t>Brooks Colquitt</t>
         </is>
@@ -10871,7 +10874,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E21" s="132" t="inlineStr">
+      <c r="E21" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10884,15 +10887,15 @@
       <c r="G21" s="129" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="132" t="inlineStr">
+      <c r="A22" s="133" t="inlineStr">
         <is>
           <t>Newmark</t>
         </is>
       </c>
-      <c r="B22" s="132" t="n">
+      <c r="B22" s="133" t="n">
         <v>4</v>
       </c>
-      <c r="C22" s="132" t="inlineStr">
+      <c r="C22" s="133" t="inlineStr">
         <is>
           <t>Hunter Amos</t>
         </is>
@@ -10902,7 +10905,7 @@
           <t>Senior Managing Director, Multifamily Capital Markets</t>
         </is>
       </c>
-      <c r="E22" s="132" t="inlineStr">
+      <c r="E22" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -10915,15 +10918,15 @@
       <c r="G22" s="129" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="132" t="inlineStr">
+      <c r="A23" s="133" t="inlineStr">
         <is>
           <t>Walker &amp; Dunlop</t>
         </is>
       </c>
-      <c r="B23" s="132" t="n">
+      <c r="B23" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="132" t="inlineStr">
+      <c r="C23" s="133" t="inlineStr">
         <is>
           <t>John Carr</t>
         </is>
@@ -10933,7 +10936,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E23" s="132" t="inlineStr">
+      <c r="E23" s="133" t="inlineStr">
         <is>
           <t>Atlanta</t>
         </is>
@@ -11837,15 +11840,15 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132" t="inlineStr">
+      <c r="A3" s="133" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B3" s="132" t="n">
+      <c r="B3" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="132" t="inlineStr">
+      <c r="C3" s="133" t="inlineStr">
         <is>
           <t>Chris Phaneuf</t>
         </is>
@@ -11855,7 +11858,7 @@
           <t>Senior Managing Director</t>
         </is>
       </c>
-      <c r="E3" s="132" t="inlineStr">
+      <c r="E3" s="133" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11868,15 +11871,15 @@
       <c r="G3" s="129" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="132" t="inlineStr">
+      <c r="A4" s="133" t="inlineStr">
         <is>
           <t>Berkadia</t>
         </is>
       </c>
-      <c r="B4" s="132" t="n">
+      <c r="B4" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="132" t="inlineStr">
+      <c r="C4" s="133" t="inlineStr">
         <is>
           <t>Adam Dunn</t>
         </is>
@@ -11886,7 +11889,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E4" s="132" t="inlineStr">
+      <c r="E4" s="133" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11899,15 +11902,15 @@
       <c r="G4" s="129" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="132" t="inlineStr">
+      <c r="A5" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B5" s="132" t="n">
+      <c r="B5" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="132" t="inlineStr">
+      <c r="C5" s="133" t="inlineStr">
         <is>
           <t>Biria St. John</t>
         </is>
@@ -11917,7 +11920,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E5" s="132" t="inlineStr">
+      <c r="E5" s="133" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11930,15 +11933,15 @@
       <c r="G5" s="129" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="132" t="inlineStr">
+      <c r="A6" s="133" t="inlineStr">
         <is>
           <t>CBRE</t>
         </is>
       </c>
-      <c r="B6" s="132" t="n">
+      <c r="B6" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="132" t="inlineStr">
+      <c r="C6" s="133" t="inlineStr">
         <is>
           <t>Simon Butler</t>
         </is>
@@ -11948,7 +11951,7 @@
           <t>Vice Chairman</t>
         </is>
       </c>
-      <c r="E6" s="132" t="inlineStr">
+      <c r="E6" s="133" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11961,15 +11964,15 @@
       <c r="G6" s="129" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="132" t="inlineStr">
+      <c r="A7" s="133" t="inlineStr">
         <is>
           <t>Colliers</t>
         </is>
       </c>
-      <c r="B7" s="132" t="n">
+      <c r="B7" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="132" t="inlineStr">
+      <c r="C7" s="133" t="inlineStr">
         <is>
           <t>David Goodhue</t>
         </is>
@@ -11979,7 +11982,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E7" s="132" t="inlineStr">
+      <c r="E7" s="133" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -11992,15 +11995,15 @@
       <c r="G7" s="129" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="132" t="inlineStr">
+      <c r="A8" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B8" s="132" t="n">
+      <c r="B8" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="132" t="inlineStr">
+      <c r="C8" s="133" t="inlineStr">
         <is>
           <t>John Flaherty</t>
         </is>
@@ -12010,7 +12013,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E8" s="132" t="inlineStr">
+      <c r="E8" s="133" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12023,15 +12026,15 @@
       <c r="G8" s="129" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="132" t="inlineStr">
+      <c r="A9" s="133" t="inlineStr">
         <is>
           <t>JLL</t>
         </is>
       </c>
-      <c r="B9" s="132" t="n">
+      <c r="B9" s="133" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="132" t="inlineStr">
+      <c r="C9" s="133" t="inlineStr">
         <is>
           <t>Jon Bryant</t>
         </is>
@@ -12041,7 +12044,7 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E9" s="132" t="inlineStr">
+      <c r="E9" s="133" t="inlineStr">
         <is>
           <t>Boston</t>
         </is>
@@ -12054,15 +12057,15 @@
       <c r="G9" s="129" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="132" t="inlineStr">
+      <c r="A10" s="133" t="inlineStr">
         <is>
           <t>Marcus &amp; Millichap (IPA)</t>
         </is>
       </c>
-      <c r="B10" s="132" t="n">
+      <c r="B10" s="133" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="132" t="inlineStr">
+      <c r="C10" s="133" t="inlineStr">
         <is>
           <t>Victor Nolletti</t>
         </is>
@@ -12072,7 +12075,7 @@
           <t>Executive Managing Director</t>
         </is>
       </c>
-      <c r="E10" s="132" t="inlineStr">
+      <c r="E10" s="133" t="inlineStr">
         <is>
           <t>Boston/Northeast</t>
         </is>
